--- a/Outcome/Appendix/Supplementary Appendix 2.xlsx
+++ b/Outcome/Appendix/Supplementary Appendix 2.xlsx
@@ -527,13 +527,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1.23301962108318</v>
+        <v>1.23301962109243</v>
       </c>
       <c r="D2" t="n">
-        <v>55.528539575172</v>
+        <v>55.5285395755817</v>
       </c>
       <c r="E2" t="n">
-        <v>5.88845567025808</v>
+        <v>5.88845567030091</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -547,13 +547,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>0.328256932424622</v>
+        <v>0.328256932436989</v>
       </c>
       <c r="D3" t="n">
-        <v>10.2023883201261</v>
+        <v>10.2023883202068</v>
       </c>
       <c r="E3" t="n">
-        <v>2.99152012068339</v>
+        <v>2.99152012070815</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -567,13 +567,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0338951129652909</v>
+        <v>0.0338951129654803</v>
       </c>
       <c r="D4" t="n">
-        <v>3.57986366975095</v>
+        <v>3.57986367009192</v>
       </c>
       <c r="E4" t="n">
-        <v>0.155324385166575</v>
+        <v>0.155324385168972</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.997685607874534</v>
+        <v>0.997685607874219</v>
       </c>
       <c r="D5" t="n">
-        <v>0.274243163677609</v>
+        <v>0.274243163679718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.782368882183025</v>
+        <v>0.782368882179963</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -687,13 +687,13 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>29.0608131441137</v>
+        <v>29.0608131451206</v>
       </c>
       <c r="D10" t="n">
-        <v>52.9029899686028</v>
+        <v>52.90298998582</v>
       </c>
       <c r="E10" t="n">
-        <v>30.955125066671</v>
+        <v>30.9551250689194</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -707,13 +707,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>5.78711296015141</v>
+        <v>5.78711295984221</v>
       </c>
       <c r="D11" t="n">
-        <v>8.62997245588797</v>
+        <v>8.62997245816932</v>
       </c>
       <c r="E11" t="n">
-        <v>6.05825927857958</v>
+        <v>6.05825927856207</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -727,13 +727,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>2.75378294382229</v>
+        <v>2.75378294360329</v>
       </c>
       <c r="D12" t="n">
-        <v>8.60424999765873</v>
+        <v>8.60425000104316</v>
       </c>
       <c r="E12" t="n">
-        <v>2.99581236429423</v>
+        <v>2.99581236421191</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -747,13 +747,13 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.154666963605844</v>
+        <v>0.154666963604775</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0432755417969345</v>
+        <v>0.0432755420543069</v>
       </c>
       <c r="E13" t="n">
-        <v>0.112173694411386</v>
+        <v>0.11217369439571</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -847,13 +847,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>20.5891904294886</v>
+        <v>20.9923800034918</v>
       </c>
       <c r="D18" t="n">
-        <v>56.1696248332545</v>
+        <v>54.4421345126448</v>
       </c>
       <c r="E18" t="n">
-        <v>23.6613009108323</v>
+        <v>23.8853717486398</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
@@ -867,13 +867,13 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>4.17977650899485</v>
+        <v>4.27232293399538</v>
       </c>
       <c r="D19" t="n">
-        <v>8.84927996001348</v>
+        <v>8.46319129955678</v>
       </c>
       <c r="E19" t="n">
-        <v>4.7634962004919</v>
+        <v>4.77857722110977</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -887,13 +887,13 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>1.66789551189572</v>
+        <v>1.73530719459671</v>
       </c>
       <c r="D20" t="n">
-        <v>6.19393287421957</v>
+        <v>5.58516253984328</v>
       </c>
       <c r="E20" t="n">
-        <v>1.94562048702547</v>
+        <v>1.9921169151793</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -907,13 +907,13 @@
         <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>0.608744850307328</v>
+        <v>0.583750488468492</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00713155369840567</v>
+        <v>0.050594240710402</v>
       </c>
       <c r="E21" t="n">
-        <v>0.475112451792045</v>
+        <v>0.47461659037045</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -927,13 +927,13 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>31.1437299648149</v>
+        <v>31.208295767028</v>
       </c>
       <c r="D22" t="n">
-        <v>68.3055773845994</v>
+        <v>66.6113717725436</v>
       </c>
       <c r="E22" t="n">
-        <v>34.0649437396454</v>
+        <v>33.994844223519</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -947,13 +947,13 @@
         <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>6.09287725192898</v>
+        <v>6.09982289195867</v>
       </c>
       <c r="D23" t="n">
-        <v>11.4678904180151</v>
+        <v>11.0307055387353</v>
       </c>
       <c r="E23" t="n">
-        <v>6.67206158307781</v>
+        <v>6.62045896562463</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -967,13 +967,13 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.81555649718417</v>
+        <v>0.816764076214328</v>
       </c>
       <c r="D24" t="n">
-        <v>5.33196570549171</v>
+        <v>5.76619167505798</v>
       </c>
       <c r="E24" t="n">
-        <v>1.82401304627021</v>
+        <v>1.80376441244197</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -987,13 +987,13 @@
         <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>0.153997382406132</v>
+        <v>0.153450743634041</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0204948895058072</v>
+        <v>0.0302974776452862</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0934574759898859</v>
+        <v>0.097918313120614</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -1007,13 +1007,13 @@
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>11.1696942083524</v>
+        <v>11.1698750942955</v>
       </c>
       <c r="D26" t="n">
-        <v>26.7449517194033</v>
+        <v>26.7447993876685</v>
       </c>
       <c r="E26" t="n">
-        <v>13.7564415194099</v>
+        <v>13.756566749616</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
@@ -1027,13 +1027,13 @@
         <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>4.24673756579247</v>
+        <v>4.24679212206558</v>
       </c>
       <c r="D27" t="n">
-        <v>12.9563906757586</v>
+        <v>12.9563727767502</v>
       </c>
       <c r="E27" t="n">
-        <v>6.54414503889599</v>
+        <v>6.54416939117421</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
@@ -1047,13 +1047,13 @@
         <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>0.570510512197653</v>
+        <v>0.570525687593858</v>
       </c>
       <c r="D28" t="n">
-        <v>1.55265442140614</v>
+        <v>1.55265799071138</v>
       </c>
       <c r="E28" t="n">
-        <v>0.744756890740374</v>
+        <v>0.744768813590943</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
@@ -1067,13 +1067,13 @@
         <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>0.876386732944878</v>
+        <v>0.876385297401375</v>
       </c>
       <c r="D29" t="n">
-        <v>0.697341691741616</v>
+        <v>0.697320435767054</v>
       </c>
       <c r="E29" t="n">
-        <v>0.786404543822977</v>
+        <v>0.786404189379806</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
@@ -1327,13 +1327,13 @@
         <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0202012883944</v>
+        <v>16.5254055928401</v>
       </c>
       <c r="D42" t="n">
-        <v>14.1998148580282</v>
+        <v>14.5349866898399</v>
       </c>
       <c r="E42" t="n">
-        <v>16.5507658877691</v>
+        <v>16.1816530691126</v>
       </c>
       <c r="F42" t="s">
         <v>17</v>
@@ -1347,13 +1347,13 @@
         <v>9</v>
       </c>
       <c r="C43" t="n">
-        <v>5.84334300320536</v>
+        <v>5.72603681776519</v>
       </c>
       <c r="D43" t="n">
-        <v>11.0293744921351</v>
+        <v>11.1133756514146</v>
       </c>
       <c r="E43" t="n">
-        <v>6.97101443519061</v>
+        <v>6.91169990516999</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
@@ -1367,13 +1367,13 @@
         <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>0.800738825998403</v>
+        <v>0.793767173196446</v>
       </c>
       <c r="D44" t="n">
-        <v>0.906140878504825</v>
+        <v>0.937029800310451</v>
       </c>
       <c r="E44" t="n">
-        <v>0.828239484498199</v>
+        <v>0.827889686189926</v>
       </c>
       <c r="F44" t="s">
         <v>17</v>
@@ -1387,13 +1387,13 @@
         <v>11</v>
       </c>
       <c r="C45" t="n">
-        <v>0.756557271562782</v>
+        <v>0.765153524238436</v>
       </c>
       <c r="D45" t="n">
-        <v>0.827072300934548</v>
+        <v>0.832773586878806</v>
       </c>
       <c r="E45" t="n">
-        <v>0.736177358120237</v>
+        <v>0.742720126216355</v>
       </c>
       <c r="F45" t="s">
         <v>17</v>
@@ -1407,13 +1407,13 @@
         <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>32.7726812154301</v>
+        <v>33.2652616282362</v>
       </c>
       <c r="D46" t="n">
-        <v>18.9097630935002</v>
+        <v>18.2883954253596</v>
       </c>
       <c r="E46" t="n">
-        <v>30.7833327454476</v>
+        <v>31.116725583077</v>
       </c>
       <c r="F46" t="s">
         <v>17</v>
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>8.58968714989254</v>
+        <v>8.64929356897166</v>
       </c>
       <c r="D47" t="n">
-        <v>12.6859095454658</v>
+        <v>12.7339440149755</v>
       </c>
       <c r="E47" t="n">
-        <v>9.27784557726705</v>
+        <v>9.33477057362876</v>
       </c>
       <c r="F47" t="s">
         <v>17</v>
@@ -1447,13 +1447,13 @@
         <v>10</v>
       </c>
       <c r="C48" t="n">
-        <v>0.963437681093619</v>
+        <v>0.976440477363988</v>
       </c>
       <c r="D48" t="n">
-        <v>1.38416961972711</v>
+        <v>1.3396183720967</v>
       </c>
       <c r="E48" t="n">
-        <v>1.38453930218192</v>
+        <v>1.32477302900544</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
@@ -1467,13 +1467,13 @@
         <v>11</v>
       </c>
       <c r="C49" t="n">
-        <v>0.483201390647028</v>
+        <v>0.481165691983628</v>
       </c>
       <c r="D49" t="n">
-        <v>0.796755288293293</v>
+        <v>0.795022334931817</v>
       </c>
       <c r="E49" t="n">
-        <v>0.507775823602591</v>
+        <v>0.50290978134094</v>
       </c>
       <c r="F49" t="s">
         <v>17</v>
@@ -1487,13 +1487,13 @@
         <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>17.708554375318</v>
+        <v>17.7085143726513</v>
       </c>
       <c r="D50" t="n">
-        <v>25.0781048937161</v>
+        <v>25.0780986096672</v>
       </c>
       <c r="E50" t="n">
-        <v>18.3249492490161</v>
+        <v>18.3249120563292</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>78.7106982408175</v>
+        <v>78.7105309074327</v>
       </c>
       <c r="D51" t="n">
-        <v>80.6946658519694</v>
+        <v>80.6946302691027</v>
       </c>
       <c r="E51" t="n">
-        <v>78.8840169408604</v>
+        <v>78.8838608533918</v>
       </c>
       <c r="F51" t="s">
         <v>18</v>
@@ -1527,13 +1527,13 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.873867460398392</v>
+        <v>0.87386998529041</v>
       </c>
       <c r="D52" t="n">
-        <v>1.37170096769294</v>
+        <v>1.37170056875932</v>
       </c>
       <c r="E52" t="n">
-        <v>0.906802099121992</v>
+        <v>0.906804599593969</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -1547,13 +1547,13 @@
         <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>0.816674947714524</v>
+        <v>0.81667570350186</v>
       </c>
       <c r="D53" t="n">
-        <v>0.669260704883477</v>
+        <v>0.669260785335087</v>
       </c>
       <c r="E53" t="n">
-        <v>0.801698854633199</v>
+        <v>0.801699623576038</v>
       </c>
       <c r="F53" t="s">
         <v>18</v>
@@ -1807,13 +1807,13 @@
         <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>14.2262166102362</v>
+        <v>14.1834076123827</v>
       </c>
       <c r="D66" t="n">
-        <v>24.8717880271978</v>
+        <v>24.953323007338</v>
       </c>
       <c r="E66" t="n">
-        <v>15.1146032295774</v>
+        <v>15.0821564840243</v>
       </c>
       <c r="F66" t="s">
         <v>18</v>
@@ -1827,13 +1827,13 @@
         <v>9</v>
       </c>
       <c r="C67" t="n">
-        <v>61.6211081214522</v>
+        <v>61.5781907802574</v>
       </c>
       <c r="D67" t="n">
-        <v>78.6329983070843</v>
+        <v>78.8346575812711</v>
       </c>
       <c r="E67" t="n">
-        <v>63.2206860931204</v>
+        <v>63.2031973359992</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
@@ -1847,13 +1847,13 @@
         <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>0.621994940056975</v>
+        <v>0.620830212902934</v>
       </c>
       <c r="D68" t="n">
-        <v>1.20667367415378</v>
+        <v>1.19271782614802</v>
       </c>
       <c r="E68" t="n">
-        <v>0.659615940599936</v>
+        <v>0.658151542779473</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="C69" t="n">
-        <v>0.880667424325483</v>
+        <v>0.880833735977529</v>
       </c>
       <c r="D69" t="n">
-        <v>0.648220290927611</v>
+        <v>0.641668061180595</v>
       </c>
       <c r="E69" t="n">
-        <v>0.868919601733589</v>
+        <v>0.869006975984739</v>
       </c>
       <c r="F69" t="s">
         <v>18</v>
@@ -1887,13 +1887,13 @@
         <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>26.9031015985062</v>
+        <v>26.8734063552776</v>
       </c>
       <c r="D70" t="n">
-        <v>28.8972732063396</v>
+        <v>31.4251770475851</v>
       </c>
       <c r="E70" t="n">
-        <v>27.057644684506</v>
+        <v>27.2236284135297</v>
       </c>
       <c r="F70" t="s">
         <v>18</v>
@@ -1907,13 +1907,13 @@
         <v>9</v>
       </c>
       <c r="C71" t="n">
-        <v>95.9470275485193</v>
+        <v>96.1580716709376</v>
       </c>
       <c r="D71" t="n">
-        <v>99.4170688357926</v>
+        <v>120.263840415764</v>
       </c>
       <c r="E71" t="n">
-        <v>96.2235626785805</v>
+        <v>98.228901590745</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -1927,13 +1927,13 @@
         <v>10</v>
       </c>
       <c r="C72" t="n">
-        <v>0.847818272570056</v>
+        <v>0.849338173450988</v>
       </c>
       <c r="D72" t="n">
-        <v>1.12445379925921</v>
+        <v>1.22077058223117</v>
       </c>
       <c r="E72" t="n">
-        <v>0.770791915458776</v>
+        <v>0.770231134483079</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -1947,13 +1947,13 @@
         <v>11</v>
       </c>
       <c r="C73" t="n">
-        <v>0.738046395847473</v>
+        <v>0.73803737192566</v>
       </c>
       <c r="D73" t="n">
-        <v>0.623302043628679</v>
+        <v>0.630233645345383</v>
       </c>
       <c r="E73" t="n">
-        <v>0.727034093670567</v>
+        <v>0.718660993551442</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
@@ -1967,13 +1967,13 @@
         <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>70.9788710821728</v>
+        <v>70.9789219662069</v>
       </c>
       <c r="D74" t="n">
-        <v>46.6056112830514</v>
+        <v>46.6053613029043</v>
       </c>
       <c r="E74" t="n">
-        <v>68.7636595289938</v>
+        <v>68.7636830681562</v>
       </c>
       <c r="F74" t="s">
         <v>19</v>
@@ -1987,13 +1987,13 @@
         <v>9</v>
       </c>
       <c r="C75" t="n">
-        <v>674.729210030362</v>
+        <v>674.733996380595</v>
       </c>
       <c r="D75" t="n">
-        <v>626.346898374241</v>
+        <v>626.336749319741</v>
       </c>
       <c r="E75" t="n">
-        <v>670.478616669912</v>
+        <v>670.482133117047</v>
       </c>
       <c r="F75" t="s">
         <v>19</v>
@@ -2007,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="C76" t="n">
-        <v>1.644946153574</v>
+        <v>1.64496547245704</v>
       </c>
       <c r="D76" t="n">
-        <v>9.28461406854573</v>
+        <v>9.28415621710209</v>
       </c>
       <c r="E76" t="n">
-        <v>1.88372765224826</v>
+        <v>1.88373956798221</v>
       </c>
       <c r="F76" t="s">
         <v>19</v>
@@ -2027,13 +2027,13 @@
         <v>11</v>
       </c>
       <c r="C77" t="n">
-        <v>0.855866522392539</v>
+        <v>0.855866581636508</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0665489295869437</v>
+        <v>0.0665476145005746</v>
       </c>
       <c r="E77" t="n">
-        <v>0.825862943533696</v>
+        <v>0.825864141197365</v>
       </c>
       <c r="F77" t="s">
         <v>19</v>
@@ -2125,13 +2125,13 @@
         <v>7</v>
       </c>
       <c r="C82" t="n">
-        <v>90.4612125140176</v>
+        <v>90.4612125140201</v>
       </c>
       <c r="D82" t="n">
-        <v>104.736008190612</v>
+        <v>104.736008190628</v>
       </c>
       <c r="E82" t="n">
-        <v>91.6513894697456</v>
+        <v>91.6513894697493</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
@@ -2145,13 +2145,13 @@
         <v>9</v>
       </c>
       <c r="C83" t="n">
-        <v>1383.78566636658</v>
+        <v>1383.78566636705</v>
       </c>
       <c r="D83" t="n">
-        <v>3081.92660454795</v>
+        <v>3081.92660454913</v>
       </c>
       <c r="E83" t="n">
-        <v>1595.88766453485</v>
+        <v>1595.88766453542</v>
       </c>
       <c r="F83" t="s">
         <v>19</v>
@@ -2165,13 +2165,13 @@
         <v>10</v>
       </c>
       <c r="C84" t="n">
-        <v>0.978687121162785</v>
+        <v>0.978687121162624</v>
       </c>
       <c r="D84" t="n">
-        <v>1.46213453399072</v>
+        <v>1.46213453399029</v>
       </c>
       <c r="E84" t="n">
-        <v>1.12112819214292</v>
+        <v>1.12112819214271</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
@@ -2185,13 +2185,13 @@
         <v>11</v>
       </c>
       <c r="C85" t="n">
-        <v>0.440908295955884</v>
+        <v>0.44090829595576</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0273791554215037</v>
+        <v>0.0273791554214635</v>
       </c>
       <c r="E85" t="n">
-        <v>0.394445831536402</v>
+        <v>0.39444583153629</v>
       </c>
       <c r="F85" t="s">
         <v>19</v>
@@ -2285,13 +2285,13 @@
         <v>7</v>
       </c>
       <c r="C90" t="n">
-        <v>76.0949036818936</v>
+        <v>75.9558426009811</v>
       </c>
       <c r="D90" t="n">
-        <v>82.849412874076</v>
+        <v>83.3528799525876</v>
       </c>
       <c r="E90" t="n">
-        <v>76.709719464179</v>
+        <v>76.6290658656654</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C91" t="n">
-        <v>780.455876698443</v>
+        <v>785.841698220485</v>
       </c>
       <c r="D91" t="n">
-        <v>1529.71134372717</v>
+        <v>1549.44803175099</v>
       </c>
       <c r="E91" t="n">
-        <v>875.49524577322</v>
+        <v>882.998260559835</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -2325,13 +2325,13 @@
         <v>10</v>
       </c>
       <c r="C92" t="n">
-        <v>1.87682146929337</v>
+        <v>1.8621732965155</v>
       </c>
       <c r="D92" t="n">
-        <v>2.62711882486457</v>
+        <v>2.65389548197655</v>
       </c>
       <c r="E92" t="n">
-        <v>2.06520293306001</v>
+        <v>2.06028178422762</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -2345,13 +2345,13 @@
         <v>11</v>
       </c>
       <c r="C93" t="n">
-        <v>0.741440847228941</v>
+        <v>0.73973565246496</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0521103311354169</v>
+        <v>0.0440978942496756</v>
       </c>
       <c r="E93" t="n">
-        <v>0.690294511429618</v>
+        <v>0.688485617888164</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -2368,7 +2368,7 @@
         <v>#NUM!</v>
       </c>
       <c r="D94" t="n">
-        <v>57.3589202935496</v>
+        <v>55.8756623969715</v>
       </c>
       <c r="E94" t="e">
         <v>#NUM!</v>
@@ -2385,13 +2385,13 @@
         <v>9</v>
       </c>
       <c r="C95" t="n">
-        <v>936.361806528053</v>
+        <v>934.704289133132</v>
       </c>
       <c r="D95" t="n">
-        <v>943.603505357268</v>
+        <v>794.435647192716</v>
       </c>
       <c r="E95" t="n">
-        <v>936.972250369809</v>
+        <v>923.832936786325</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -2405,13 +2405,13 @@
         <v>10</v>
       </c>
       <c r="C96" t="n">
-        <v>2.52783567655154</v>
+        <v>2.52824035172956</v>
       </c>
       <c r="D96" t="n">
-        <v>3.83652861186275</v>
+        <v>4.26130827335366</v>
       </c>
       <c r="E96" t="n">
-        <v>0.832085313925118</v>
+        <v>0.820377895791886</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -2425,13 +2425,13 @@
         <v>11</v>
       </c>
       <c r="C97" t="n">
-        <v>0.654956331842508</v>
+        <v>0.656230432828636</v>
       </c>
       <c r="D97" t="n">
-        <v>0.386266850485962</v>
+        <v>0.0506025756009338</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6418308203625</v>
+        <v>0.648774434081722</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -2445,13 +2445,13 @@
         <v>7</v>
       </c>
       <c r="C98" t="n">
-        <v>15.5747194298861</v>
+        <v>15.5746635862909</v>
       </c>
       <c r="D98" t="n">
-        <v>17.6031894425221</v>
+        <v>17.5790259914823</v>
       </c>
       <c r="E98" t="n">
-        <v>15.7450220702174</v>
+        <v>15.7429573406976</v>
       </c>
       <c r="F98" t="s">
         <v>20</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="C99" t="n">
-        <v>139.185183292621</v>
+        <v>139.217634067322</v>
       </c>
       <c r="D99" t="n">
-        <v>170.517756700365</v>
+        <v>170.084540129265</v>
       </c>
       <c r="E99" t="n">
-        <v>142.066799314914</v>
+        <v>142.052647326715</v>
       </c>
       <c r="F99" t="s">
         <v>20</v>
@@ -2485,13 +2485,13 @@
         <v>10</v>
       </c>
       <c r="C100" t="n">
-        <v>0.933187903698241</v>
+        <v>0.933741506334525</v>
       </c>
       <c r="D100" t="n">
-        <v>1.1873378311903</v>
+        <v>1.18475897270626</v>
       </c>
       <c r="E100" t="n">
-        <v>0.951678340690628</v>
+        <v>0.952003516732542</v>
       </c>
       <c r="F100" t="s">
         <v>20</v>
@@ -2505,13 +2505,13 @@
         <v>11</v>
       </c>
       <c r="C101" t="n">
-        <v>0.804427451337275</v>
+        <v>0.8043915111898</v>
       </c>
       <c r="D101" t="n">
-        <v>0.742065967125039</v>
+        <v>0.742756935175081</v>
       </c>
       <c r="E101" t="n">
-        <v>0.788282014285708</v>
+        <v>0.788328196387851</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
@@ -2525,13 +2525,13 @@
         <v>7</v>
       </c>
       <c r="C102" t="n">
-        <v>11.3615490787218</v>
+        <v>11.3615490787243</v>
       </c>
       <c r="D102" t="n">
-        <v>11.4256001700517</v>
+        <v>11.4256001700594</v>
       </c>
       <c r="E102" t="n">
-        <v>11.3672846186734</v>
+        <v>11.3672846186763</v>
       </c>
       <c r="F102" t="s">
         <v>20</v>
@@ -2545,13 +2545,13 @@
         <v>9</v>
       </c>
       <c r="C103" t="n">
-        <v>96.4158485285292</v>
+        <v>96.4158485285337</v>
       </c>
       <c r="D103" t="n">
-        <v>98.9924855983515</v>
+        <v>98.9924855983867</v>
       </c>
       <c r="E103" t="n">
-        <v>96.6219739932718</v>
+        <v>96.6219739932788</v>
       </c>
       <c r="F103" t="s">
         <v>20</v>
@@ -2565,13 +2565,13 @@
         <v>10</v>
       </c>
       <c r="C104" t="n">
-        <v>0.553543445285296</v>
+        <v>0.553543445285359</v>
       </c>
       <c r="D104" t="n">
-        <v>0.535054433417316</v>
+        <v>0.535054433417657</v>
       </c>
       <c r="E104" t="n">
-        <v>0.555382749963788</v>
+        <v>0.55538274996387</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -2585,13 +2585,13 @@
         <v>11</v>
       </c>
       <c r="C105" t="n">
-        <v>0.907835022515628</v>
+        <v>0.907835022515621</v>
       </c>
       <c r="D105" t="n">
-        <v>0.928536933408825</v>
+        <v>0.92853693340881</v>
       </c>
       <c r="E105" t="n">
-        <v>0.904940757068618</v>
+        <v>0.904940757068607</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -2605,13 +2605,13 @@
         <v>7</v>
       </c>
       <c r="C106" t="n">
-        <v>10.4345802266062</v>
+        <v>10.4345802200485</v>
       </c>
       <c r="D106" t="n">
-        <v>20.5038576119204</v>
+        <v>20.5038577157211</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2104650289306</v>
+        <v>11.2104650308618</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
@@ -2625,13 +2625,13 @@
         <v>9</v>
       </c>
       <c r="C107" t="n">
-        <v>95.1354032386165</v>
+        <v>95.1354031690905</v>
       </c>
       <c r="D107" t="n">
-        <v>184.409569544192</v>
+        <v>184.409570281052</v>
       </c>
       <c r="E107" t="n">
-        <v>104.751211100317</v>
+        <v>104.751211141876</v>
       </c>
       <c r="F107" t="s">
         <v>20</v>
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C108" t="n">
-        <v>0.496149361585827</v>
+        <v>0.496149361340901</v>
       </c>
       <c r="D108" t="n">
-        <v>1.0350814142961</v>
+        <v>1.03508141876023</v>
       </c>
       <c r="E108" t="n">
-        <v>0.545467154880289</v>
+        <v>0.545467155091645</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -2665,13 +2665,13 @@
         <v>11</v>
       </c>
       <c r="C109" t="n">
-        <v>0.909809749541644</v>
+        <v>0.909809749667041</v>
       </c>
       <c r="D109" t="n">
-        <v>0.910737857479734</v>
+        <v>0.910737857580875</v>
       </c>
       <c r="E109" t="n">
-        <v>0.89200454053218</v>
+        <v>0.892004540467767</v>
       </c>
       <c r="F109" t="s">
         <v>20</v>
@@ -2725,13 +2725,13 @@
         <v>10</v>
       </c>
       <c r="C112" t="n">
-        <v>0.521861667177203</v>
+        <v>0.521861667177204</v>
       </c>
       <c r="D112" t="n">
         <v>0.814266145904816</v>
       </c>
       <c r="E112" t="n">
-        <v>0.551280509609858</v>
+        <v>0.551280509609859</v>
       </c>
       <c r="F112" t="s">
         <v>20</v>
@@ -2751,7 +2751,7 @@
         <v>0.92714116869568</v>
       </c>
       <c r="E113" t="n">
-        <v>0.910279780417459</v>
+        <v>0.910279780417458</v>
       </c>
       <c r="F113" t="s">
         <v>20</v>
@@ -2765,13 +2765,13 @@
         <v>7</v>
       </c>
       <c r="C114" t="n">
-        <v>10.7701755509316</v>
+        <v>10.7865001594596</v>
       </c>
       <c r="D114" t="n">
-        <v>15.8094175704243</v>
+        <v>15.7339027340358</v>
       </c>
       <c r="E114" t="n">
-        <v>11.1912262165877</v>
+        <v>11.1998974017271</v>
       </c>
       <c r="F114" t="s">
         <v>20</v>
@@ -2785,13 +2785,13 @@
         <v>9</v>
       </c>
       <c r="C115" t="n">
-        <v>94.0129690276127</v>
+        <v>94.0018084030001</v>
       </c>
       <c r="D115" t="n">
-        <v>141.564369158955</v>
+        <v>141.009190063482</v>
       </c>
       <c r="E115" t="n">
-        <v>98.8624005454819</v>
+        <v>98.7864334310879</v>
       </c>
       <c r="F115" t="s">
         <v>20</v>
@@ -2805,13 +2805,13 @@
         <v>10</v>
       </c>
       <c r="C116" t="n">
-        <v>0.549509336461385</v>
+        <v>0.550938299028341</v>
       </c>
       <c r="D116" t="n">
-        <v>0.832153656427771</v>
+        <v>0.829724567939687</v>
       </c>
       <c r="E116" t="n">
-        <v>0.578143287100503</v>
+        <v>0.579117600823159</v>
       </c>
       <c r="F116" t="s">
         <v>20</v>
@@ -2825,13 +2825,13 @@
         <v>11</v>
       </c>
       <c r="C117" t="n">
-        <v>0.910349705041002</v>
+        <v>0.91038717629648</v>
       </c>
       <c r="D117" t="n">
-        <v>0.902008886694681</v>
+        <v>0.899725328073692</v>
       </c>
       <c r="E117" t="n">
-        <v>0.89775241316138</v>
+        <v>0.897877043111647</v>
       </c>
       <c r="F117" t="s">
         <v>20</v>
@@ -2845,13 +2845,13 @@
         <v>7</v>
       </c>
       <c r="C118" t="n">
-        <v>15.9508504042733</v>
+        <v>15.9913319802953</v>
       </c>
       <c r="D118" t="n">
-        <v>10.2924188860647</v>
+        <v>11.1628647891083</v>
       </c>
       <c r="E118" t="n">
-        <v>15.5167741516505</v>
+        <v>15.6196166364939</v>
       </c>
       <c r="F118" t="s">
         <v>20</v>
@@ -2865,13 +2865,13 @@
         <v>9</v>
       </c>
       <c r="C119" t="n">
-        <v>122.447812191736</v>
+        <v>122.533310144875</v>
       </c>
       <c r="D119" t="n">
-        <v>85.5352706719215</v>
+        <v>84.8140247713293</v>
       </c>
       <c r="E119" t="n">
-        <v>120.015232341458</v>
+        <v>120.050685903001</v>
       </c>
       <c r="F119" t="s">
         <v>20</v>
@@ -2885,13 +2885,13 @@
         <v>10</v>
       </c>
       <c r="C120" t="n">
-        <v>0.702015496496915</v>
+        <v>0.703800025647177</v>
       </c>
       <c r="D120" t="n">
-        <v>0.523057602653131</v>
+        <v>0.609805733170449</v>
       </c>
       <c r="E120" t="n">
-        <v>0.690068251444166</v>
+        <v>0.689730536451864</v>
       </c>
       <c r="F120" t="s">
         <v>20</v>
@@ -2905,13 +2905,13 @@
         <v>11</v>
       </c>
       <c r="C121" t="n">
-        <v>0.851791603656986</v>
+        <v>0.851890033063187</v>
       </c>
       <c r="D121" t="n">
-        <v>0.925675577910574</v>
+        <v>0.941321307298549</v>
       </c>
       <c r="E121" t="n">
-        <v>0.854180818355326</v>
+        <v>0.85332884483527</v>
       </c>
       <c r="F121" t="s">
         <v>20</v>
@@ -2925,13 +2925,13 @@
         <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>20.1820393444905</v>
+        <v>20.181512607146</v>
       </c>
       <c r="D122" t="n">
-        <v>30.0311097251261</v>
+        <v>30.0330499476578</v>
       </c>
       <c r="E122" t="n">
-        <v>21.0015269267064</v>
+        <v>21.0012058159972</v>
       </c>
       <c r="F122" t="s">
         <v>21</v>
@@ -2945,13 +2945,13 @@
         <v>9</v>
       </c>
       <c r="C123" t="n">
-        <v>368.110759882932</v>
+        <v>368.092971012386</v>
       </c>
       <c r="D123" t="n">
-        <v>87.3383858152465</v>
+        <v>87.3411490013563</v>
       </c>
       <c r="E123" t="n">
-        <v>353.338876922238</v>
+        <v>353.321945537006</v>
       </c>
       <c r="F123" t="s">
         <v>21</v>
@@ -2965,13 +2965,13 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>0.76446671153973</v>
+        <v>0.764395608578802</v>
       </c>
       <c r="D124" t="n">
-        <v>2.96446311805832</v>
+        <v>2.96448946725164</v>
       </c>
       <c r="E124" t="n">
-        <v>0.777812255481033</v>
+        <v>0.777741317216882</v>
       </c>
       <c r="F124" t="s">
         <v>21</v>
@@ -2985,13 +2985,13 @@
         <v>11</v>
       </c>
       <c r="C125" t="n">
-        <v>0.874957545184883</v>
+        <v>0.874966413550006</v>
       </c>
       <c r="D125" t="n">
-        <v>0.829977180575318</v>
+        <v>0.829926341539692</v>
       </c>
       <c r="E125" t="n">
-        <v>0.884032593090085</v>
+        <v>0.884040943073007</v>
       </c>
       <c r="F125" t="s">
         <v>21</v>
@@ -3165,13 +3165,13 @@
         <v>7</v>
       </c>
       <c r="C134" t="n">
-        <v>17.3119054968524</v>
+        <v>17.3119054968047</v>
       </c>
       <c r="D134" t="n">
-        <v>28.8913577867154</v>
+        <v>28.8913577869424</v>
       </c>
       <c r="E134" t="n">
-        <v>18.2004851553736</v>
+        <v>18.200485155347</v>
       </c>
       <c r="F134" t="s">
         <v>21</v>
@@ -3185,13 +3185,13 @@
         <v>9</v>
       </c>
       <c r="C135" t="n">
-        <v>362.919582947935</v>
+        <v>362.919582947709</v>
       </c>
       <c r="D135" t="n">
-        <v>67.2317931017711</v>
+        <v>67.2317931018623</v>
       </c>
       <c r="E135" t="n">
-        <v>349.179158446665</v>
+        <v>349.179158446449</v>
       </c>
       <c r="F135" t="s">
         <v>21</v>
@@ -3205,13 +3205,13 @@
         <v>10</v>
       </c>
       <c r="C136" t="n">
-        <v>0.587802329958999</v>
+        <v>0.587802329957576</v>
       </c>
       <c r="D136" t="n">
-        <v>1.32493887634901</v>
+        <v>1.32493887635629</v>
       </c>
       <c r="E136" t="n">
-        <v>0.594145880978335</v>
+        <v>0.594145880976988</v>
       </c>
       <c r="F136" t="s">
         <v>21</v>
@@ -3225,13 +3225,13 @@
         <v>11</v>
       </c>
       <c r="C137" t="n">
-        <v>0.904041554757334</v>
+        <v>0.90404155475746</v>
       </c>
       <c r="D137" t="n">
-        <v>0.878314002676812</v>
+        <v>0.878314002676652</v>
       </c>
       <c r="E137" t="n">
-        <v>0.91036512777389</v>
+        <v>0.910365127774008</v>
       </c>
       <c r="F137" t="s">
         <v>21</v>
@@ -3245,13 +3245,13 @@
         <v>7</v>
       </c>
       <c r="C138" t="n">
-        <v>15.9412818329553</v>
+        <v>15.9263306961753</v>
       </c>
       <c r="D138" t="n">
-        <v>30.6582301644772</v>
+        <v>30.6914893943086</v>
       </c>
       <c r="E138" t="n">
-        <v>17.1653290441643</v>
+        <v>17.1543963686711</v>
       </c>
       <c r="F138" t="s">
         <v>21</v>
@@ -3265,13 +3265,13 @@
         <v>9</v>
       </c>
       <c r="C139" t="n">
-        <v>283.958432570776</v>
+        <v>283.533576033445</v>
       </c>
       <c r="D139" t="n">
-        <v>75.1542010362643</v>
+        <v>75.2107934318188</v>
       </c>
       <c r="E139" t="n">
-        <v>272.732389645359</v>
+        <v>272.328208615357</v>
       </c>
       <c r="F139" t="s">
         <v>21</v>
@@ -3285,13 +3285,13 @@
         <v>10</v>
       </c>
       <c r="C140" t="n">
-        <v>0.541056529986035</v>
+        <v>0.54042984031905</v>
       </c>
       <c r="D140" t="n">
-        <v>1.87986405890429</v>
+        <v>1.88157376948252</v>
       </c>
       <c r="E140" t="n">
-        <v>0.551921161536425</v>
+        <v>0.551322602272809</v>
       </c>
       <c r="F140" t="s">
         <v>21</v>
@@ -3305,13 +3305,13 @@
         <v>11</v>
       </c>
       <c r="C141" t="n">
-        <v>0.923661287933413</v>
+        <v>0.923890777002251</v>
       </c>
       <c r="D141" t="n">
-        <v>0.923957477894624</v>
+        <v>0.924043098315977</v>
       </c>
       <c r="E141" t="n">
-        <v>0.929183702061526</v>
+        <v>0.929395222454469</v>
       </c>
       <c r="F141" t="s">
         <v>21</v>
@@ -3325,13 +3325,13 @@
         <v>7</v>
       </c>
       <c r="C142" t="n">
-        <v>56.8158124331481</v>
+        <v>53.6406299331496</v>
       </c>
       <c r="D142" t="n">
-        <v>81.5300431219824</v>
+        <v>114.413287635245</v>
       </c>
       <c r="E142" t="n">
-        <v>58.7182847955742</v>
+        <v>58.3162524686063</v>
       </c>
       <c r="F142" t="s">
         <v>21</v>
@@ -3345,13 +3345,13 @@
         <v>9</v>
       </c>
       <c r="C143" t="n">
-        <v>795.144647396256</v>
+        <v>789.232575354711</v>
       </c>
       <c r="D143" t="n">
-        <v>510.562021246667</v>
+        <v>345.509707009833</v>
       </c>
       <c r="E143" t="n">
-        <v>776.966488894774</v>
+        <v>764.302053315292</v>
       </c>
       <c r="F143" t="s">
         <v>21</v>
@@ -3365,13 +3365,13 @@
         <v>10</v>
       </c>
       <c r="C144" t="n">
-        <v>1.14945267327413</v>
+        <v>1.11806889460522</v>
       </c>
       <c r="D144" t="n">
-        <v>1.39621559408765</v>
+        <v>1.22558668940045</v>
       </c>
       <c r="E144" t="n">
-        <v>0.862977643569144</v>
+        <v>0.821277354637108</v>
       </c>
       <c r="F144" t="s">
         <v>21</v>
@@ -3385,13 +3385,13 @@
         <v>11</v>
       </c>
       <c r="C145" t="n">
-        <v>0.650309815902607</v>
+        <v>0.652269013673568</v>
       </c>
       <c r="D145" t="n">
-        <v>0.826700944502449</v>
+        <v>0.789614359918581</v>
       </c>
       <c r="E145" t="n">
-        <v>0.656472472430233</v>
+        <v>0.66746082850017</v>
       </c>
       <c r="F145" t="s">
         <v>21</v>
@@ -3405,13 +3405,13 @@
         <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>3.66556336867135</v>
+        <v>3.66556336727325</v>
       </c>
       <c r="D146" t="n">
-        <v>40.4964864976157</v>
+        <v>40.4964865391937</v>
       </c>
       <c r="E146" t="n">
-        <v>6.73469594669719</v>
+        <v>6.73469594888042</v>
       </c>
       <c r="F146" t="s">
         <v>22</v>
@@ -3425,13 +3425,13 @@
         <v>9</v>
       </c>
       <c r="C147" t="n">
-        <v>293.972909629426</v>
+        <v>293.972910068571</v>
       </c>
       <c r="D147" t="n">
-        <v>3789.46398949683</v>
+        <v>3789.46399161284</v>
       </c>
       <c r="E147" t="n">
-        <v>1129.53341609044</v>
+        <v>1129.53341678679</v>
       </c>
       <c r="F147" t="s">
         <v>22</v>
@@ -3445,13 +3445,13 @@
         <v>10</v>
       </c>
       <c r="C148" t="n">
-        <v>0.142924815855832</v>
+        <v>0.142924815937701</v>
       </c>
       <c r="D148" t="n">
-        <v>3.16570310587253</v>
+        <v>3.16570311149174</v>
       </c>
       <c r="E148" t="n">
-        <v>0.347706961863665</v>
+        <v>0.347706962160377</v>
       </c>
       <c r="F148" t="s">
         <v>22</v>
@@ -3465,13 +3465,13 @@
         <v>11</v>
       </c>
       <c r="C149" t="n">
-        <v>0.993755017071016</v>
+        <v>0.993755017054555</v>
       </c>
       <c r="D149" t="n">
-        <v>0.806709378463206</v>
+        <v>0.806709376196164</v>
       </c>
       <c r="E149" t="n">
-        <v>0.911443566071824</v>
+        <v>0.911443565951127</v>
       </c>
       <c r="F149" t="s">
         <v>22</v>
@@ -3565,13 +3565,13 @@
         <v>7</v>
       </c>
       <c r="C154" t="n">
-        <v>13.8479500598018</v>
+        <v>13.8479500657638</v>
       </c>
       <c r="D154" t="n">
-        <v>55.2405779361247</v>
+        <v>55.2405775402202</v>
       </c>
       <c r="E154" t="n">
-        <v>17.0318606817423</v>
+        <v>17.0318606567914</v>
       </c>
       <c r="F154" t="s">
         <v>22</v>
@@ -3585,13 +3585,13 @@
         <v>9</v>
       </c>
       <c r="C155" t="n">
-        <v>1140.30258174008</v>
+        <v>1140.30257941079</v>
       </c>
       <c r="D155" t="n">
-        <v>4394.61417913082</v>
+        <v>4394.61414843796</v>
       </c>
       <c r="E155" t="n">
-        <v>1638.84139327322</v>
+        <v>1638.8413854462</v>
       </c>
       <c r="F155" t="s">
         <v>22</v>
@@ -3605,13 +3605,13 @@
         <v>10</v>
       </c>
       <c r="C156" t="n">
-        <v>0.527658019141569</v>
+        <v>0.527658019703741</v>
       </c>
       <c r="D156" t="n">
-        <v>3.32086544103351</v>
+        <v>3.32086539368808</v>
       </c>
       <c r="E156" t="n">
-        <v>0.731055040487234</v>
+        <v>0.731055039291654</v>
       </c>
       <c r="F156" t="s">
         <v>22</v>
@@ -3625,13 +3625,13 @@
         <v>11</v>
       </c>
       <c r="C157" t="n">
-        <v>0.891484537217936</v>
+        <v>0.89148453732544</v>
       </c>
       <c r="D157" t="n">
-        <v>0.892243785327971</v>
+        <v>0.892243787498917</v>
       </c>
       <c r="E157" t="n">
-        <v>0.813154141202849</v>
+        <v>0.81315414273246</v>
       </c>
       <c r="F157" t="s">
         <v>22</v>
@@ -3725,13 +3725,13 @@
         <v>7</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9370552413529</v>
+        <v>10.6544674956046</v>
       </c>
       <c r="D162" t="n">
-        <v>21.7833303662862</v>
+        <v>21.0675519377589</v>
       </c>
       <c r="E162" t="n">
-        <v>11.8408226943563</v>
+        <v>11.5220920308579</v>
       </c>
       <c r="F162" t="s">
         <v>22</v>
@@ -3745,13 +3745,13 @@
         <v>9</v>
       </c>
       <c r="C163" t="n">
-        <v>804.147079867327</v>
+        <v>789.281126171736</v>
       </c>
       <c r="D163" t="n">
-        <v>1908.57206892966</v>
+        <v>1878.28998449932</v>
       </c>
       <c r="E163" t="n">
-        <v>946.729137368053</v>
+        <v>930.067579615865</v>
       </c>
       <c r="F163" t="s">
         <v>22</v>
@@ -3765,13 +3765,13 @@
         <v>10</v>
       </c>
       <c r="C164" t="n">
-        <v>0.414378528612908</v>
+        <v>0.40535452043789</v>
       </c>
       <c r="D164" t="n">
-        <v>0.863862436675558</v>
+        <v>0.832824095730684</v>
       </c>
       <c r="E164" t="n">
-        <v>0.474977397237497</v>
+        <v>0.463504874763667</v>
       </c>
       <c r="F164" t="s">
         <v>22</v>
@@ -3785,13 +3785,13 @@
         <v>11</v>
       </c>
       <c r="C165" t="n">
-        <v>0.946569987694724</v>
+        <v>0.948715171146854</v>
       </c>
       <c r="D165" t="n">
-        <v>0.931367042251191</v>
+        <v>0.940051934143188</v>
       </c>
       <c r="E165" t="n">
-        <v>0.939597405224498</v>
+        <v>0.94216681455108</v>
       </c>
       <c r="F165" t="s">
         <v>22</v>
@@ -3805,13 +3805,13 @@
         <v>7</v>
       </c>
       <c r="C166" t="n">
-        <v>23.9926121041888</v>
+        <v>24.6244220416459</v>
       </c>
       <c r="D166" t="n">
-        <v>28.0501678252103</v>
+        <v>55.2389392070141</v>
       </c>
       <c r="E166" t="n">
-        <v>24.3046691990439</v>
+        <v>26.97924825304</v>
       </c>
       <c r="F166" t="s">
         <v>22</v>
@@ -3825,13 +3825,13 @@
         <v>9</v>
       </c>
       <c r="C167" t="n">
-        <v>1469.77772743563</v>
+        <v>1496.12031928784</v>
       </c>
       <c r="D167" t="n">
-        <v>3289.91934769342</v>
+        <v>4462.14224313847</v>
       </c>
       <c r="E167" t="n">
-        <v>1681.25630224285</v>
+        <v>1896.76896651183</v>
       </c>
       <c r="F167" t="s">
         <v>22</v>
@@ -3845,13 +3845,13 @@
         <v>10</v>
       </c>
       <c r="C168" t="n">
-        <v>0.778704288227804</v>
+        <v>0.77879758984509</v>
       </c>
       <c r="D168" t="n">
-        <v>2.27070914046505</v>
+        <v>3.53316953234448</v>
       </c>
       <c r="E168" t="n">
-        <v>0.887227177300069</v>
+        <v>0.935402233086888</v>
       </c>
       <c r="F168" t="s">
         <v>22</v>
@@ -3865,13 +3865,13 @@
         <v>11</v>
       </c>
       <c r="C169" t="n">
-        <v>0.805604185947489</v>
+        <v>0.806151272324991</v>
       </c>
       <c r="D169" t="n">
-        <v>0.963386606891054</v>
+        <v>0.869868558809088</v>
       </c>
       <c r="E169" t="n">
-        <v>0.772741933117093</v>
+        <v>0.71847700851606</v>
       </c>
       <c r="F169" t="s">
         <v>22</v>
@@ -3885,13 +3885,13 @@
         <v>7</v>
       </c>
       <c r="C170" t="n">
-        <v>19.4873538551905</v>
+        <v>19.4873538542042</v>
       </c>
       <c r="D170" t="n">
-        <v>42.5451720761274</v>
+        <v>42.5451720919761</v>
       </c>
       <c r="E170" t="n">
-        <v>21.5834403649665</v>
+        <v>21.5834403653779</v>
       </c>
       <c r="F170" t="s">
         <v>23</v>
@@ -3905,13 +3905,13 @@
         <v>9</v>
       </c>
       <c r="C171" t="n">
-        <v>1.69670508435692</v>
+        <v>1.69670508430679</v>
       </c>
       <c r="D171" t="n">
-        <v>2.25164474393151</v>
+        <v>2.2516447440335</v>
       </c>
       <c r="E171" t="n">
-        <v>1.75633211369903</v>
+        <v>1.75633211366494</v>
       </c>
       <c r="F171" t="s">
         <v>23</v>
@@ -3925,13 +3925,13 @@
         <v>10</v>
       </c>
       <c r="C172" t="n">
-        <v>0.766704173290215</v>
+        <v>0.766704173333068</v>
       </c>
       <c r="D172" t="n">
-        <v>1.64981024453674</v>
+        <v>1.64981024871676</v>
       </c>
       <c r="E172" t="n">
-        <v>0.819806471691855</v>
+        <v>0.819806471855886</v>
       </c>
       <c r="F172" t="s">
         <v>23</v>
@@ -3945,13 +3945,13 @@
         <v>11</v>
       </c>
       <c r="C173" t="n">
-        <v>0.811807515956667</v>
+        <v>0.811807516030525</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0127017943188208</v>
+        <v>0.0127017941586391</v>
       </c>
       <c r="E173" t="n">
-        <v>0.801170669024477</v>
+        <v>0.801170669086956</v>
       </c>
       <c r="F173" t="s">
         <v>23</v>
@@ -4203,13 +4203,13 @@
         <v>7</v>
       </c>
       <c r="C186" t="n">
-        <v>30.617349587456</v>
+        <v>31.6395347529986</v>
       </c>
       <c r="D186" t="n">
-        <v>37.6445110708436</v>
+        <v>37.2990707597871</v>
       </c>
       <c r="E186" t="n">
-        <v>31.3343128315023</v>
+        <v>32.2582847973886</v>
       </c>
       <c r="F186" t="s">
         <v>23</v>
@@ -4223,13 +4223,13 @@
         <v>9</v>
       </c>
       <c r="C187" t="n">
-        <v>2.6172815622921</v>
+        <v>2.72051778370846</v>
       </c>
       <c r="D187" t="n">
-        <v>1.77044837604541</v>
+        <v>1.74332681948456</v>
       </c>
       <c r="E187" t="n">
-        <v>2.56048179079002</v>
+        <v>2.65573725101522</v>
       </c>
       <c r="F187" t="s">
         <v>23</v>
@@ -4243,13 +4243,13 @@
         <v>10</v>
       </c>
       <c r="C188" t="n">
-        <v>4.55578057260744</v>
+        <v>5.63005479713773</v>
       </c>
       <c r="D188" t="n">
-        <v>4.69095586431297</v>
+        <v>5.24249467867584</v>
       </c>
       <c r="E188" t="n">
-        <v>4.56472022230344</v>
+        <v>5.59294317456272</v>
       </c>
       <c r="F188" t="s">
         <v>23</v>
@@ -4263,13 +4263,13 @@
         <v>11</v>
       </c>
       <c r="C189" t="n">
-        <v>0.465250502050393</v>
+        <v>0.412511293761655</v>
       </c>
       <c r="D189" t="n">
-        <v>0.0137071355163179</v>
+        <v>0.00662236319944801</v>
       </c>
       <c r="E189" t="n">
-        <v>0.509904618230681</v>
+        <v>0.463393209984043</v>
       </c>
       <c r="F189" t="s">
         <v>23</v>
@@ -4283,13 +4283,13 @@
         <v>7</v>
       </c>
       <c r="C190" t="n">
-        <v>37.577688142663</v>
+        <v>37.8993421854841</v>
       </c>
       <c r="D190" t="n">
-        <v>43.8858717568288</v>
+        <v>44.231106124393</v>
       </c>
       <c r="E190" t="n">
-        <v>38.1571182302549</v>
+        <v>38.5076009702332</v>
       </c>
       <c r="F190" t="s">
         <v>23</v>
@@ -4303,13 +4303,13 @@
         <v>9</v>
       </c>
       <c r="C191" t="n">
-        <v>3.57305497239314</v>
+        <v>3.58303757812502</v>
       </c>
       <c r="D191" t="n">
-        <v>1.93952233814471</v>
+        <v>2.10774796326001</v>
       </c>
       <c r="E191" t="n">
-        <v>3.47645449476225</v>
+        <v>3.49432306135166</v>
       </c>
       <c r="F191" t="s">
         <v>23</v>
@@ -4323,13 +4323,13 @@
         <v>10</v>
       </c>
       <c r="C192" t="n">
-        <v>0.851084622478052</v>
+        <v>0.853274341751291</v>
       </c>
       <c r="D192" t="n">
-        <v>2.25045745777983</v>
+        <v>1.9452557012652</v>
       </c>
       <c r="E192" t="n">
-        <v>1.9596431188822</v>
+        <v>1.86480880305826</v>
       </c>
       <c r="F192" t="s">
         <v>23</v>
@@ -4343,13 +4343,13 @@
         <v>11</v>
       </c>
       <c r="C193" t="n">
-        <v>0.137623431254086</v>
+        <v>0.145428124740817</v>
       </c>
       <c r="D193" t="n">
-        <v>0.0000297369165823294</v>
+        <v>0.00126075239236357</v>
       </c>
       <c r="E193" t="n">
-        <v>0.190744463398633</v>
+        <v>0.190519107169493</v>
       </c>
       <c r="F193" t="s">
         <v>23</v>
@@ -4363,13 +4363,13 @@
         <v>7</v>
       </c>
       <c r="C194" t="n">
-        <v>84.2201474135731</v>
+        <v>84.2201248442918</v>
       </c>
       <c r="D194" t="n">
-        <v>44.5348705586173</v>
+        <v>44.5349054215047</v>
       </c>
       <c r="E194" t="n">
-        <v>81.0169526792611</v>
+        <v>81.0169348685256</v>
       </c>
       <c r="F194" t="s">
         <v>24</v>
@@ -4383,13 +4383,13 @@
         <v>9</v>
       </c>
       <c r="C195" t="n">
-        <v>2.88905001110848</v>
+        <v>2.88904804533734</v>
       </c>
       <c r="D195" t="n">
-        <v>3.94633677954689</v>
+        <v>3.94634103136137</v>
       </c>
       <c r="E195" t="n">
-        <v>2.99857928117501</v>
+        <v>2.99857803100138</v>
       </c>
       <c r="F195" t="s">
         <v>24</v>
@@ -4403,13 +4403,13 @@
         <v>10</v>
       </c>
       <c r="C196" t="n">
-        <v>2.15161975896003</v>
+        <v>2.15161733141877</v>
       </c>
       <c r="D196" t="n">
-        <v>9.59453493208022</v>
+        <v>9.59459956601261</v>
       </c>
       <c r="E196" t="n">
-        <v>2.33575423741873</v>
+        <v>2.33575260397904</v>
       </c>
       <c r="F196" t="s">
         <v>24</v>
@@ -4423,13 +4423,13 @@
         <v>11</v>
       </c>
       <c r="C197" t="n">
-        <v>0.669351364981823</v>
+        <v>0.669351690765137</v>
       </c>
       <c r="D197" t="n">
-        <v>0.0138874641988361</v>
+        <v>0.0138876291711211</v>
       </c>
       <c r="E197" t="n">
-        <v>0.619765692437391</v>
+        <v>0.619765953836343</v>
       </c>
       <c r="F197" t="s">
         <v>24</v>
@@ -4677,13 +4677,13 @@
         <v>7</v>
       </c>
       <c r="C210" t="n">
-        <v>88.2019720470111</v>
+        <v>88.1520611372834</v>
       </c>
       <c r="D210" t="n">
-        <v>71.7678956287245</v>
+        <v>72.2596755287451</v>
       </c>
       <c r="E210" t="n">
-        <v>86.9455516182839</v>
+        <v>86.940538950845</v>
       </c>
       <c r="F210" t="s">
         <v>24</v>
@@ -4697,13 +4697,13 @@
         <v>9</v>
       </c>
       <c r="C211" t="n">
-        <v>3.13180690079841</v>
+        <v>3.1093976664007</v>
       </c>
       <c r="D211" t="n">
-        <v>7.55781152147587</v>
+        <v>7.63153534913743</v>
       </c>
       <c r="E211" t="n">
-        <v>3.72391173212021</v>
+        <v>3.7194187317445</v>
       </c>
       <c r="F211" t="s">
         <v>24</v>
@@ -4717,13 +4717,13 @@
         <v>10</v>
       </c>
       <c r="C212" t="n">
-        <v>3.89520949606524</v>
+        <v>3.96162096696909</v>
       </c>
       <c r="D212" t="n">
-        <v>74.8895465040134</v>
+        <v>50.24513186207</v>
       </c>
       <c r="E212" t="n">
-        <v>5.06040170906299</v>
+        <v>5.09594979863929</v>
       </c>
       <c r="F212" t="s">
         <v>24</v>
@@ -4737,13 +4737,13 @@
         <v>11</v>
       </c>
       <c r="C213" t="n">
-        <v>0.630457133861494</v>
+        <v>0.635200581905016</v>
       </c>
       <c r="D213" t="n">
-        <v>0.00521899327840679</v>
+        <v>0.0157589403704838</v>
       </c>
       <c r="E213" t="n">
-        <v>0.456684330965255</v>
+        <v>0.460476405219323</v>
       </c>
       <c r="F213" t="s">
         <v>24</v>
@@ -4757,13 +4757,13 @@
         <v>7</v>
       </c>
       <c r="C214" t="n">
-        <v>83.9495128054845</v>
+        <v>83.1355690536957</v>
       </c>
       <c r="D214" t="n">
-        <v>111.157621433329</v>
+        <v>99.8696110053737</v>
       </c>
       <c r="E214" t="n">
-        <v>86.1219443115271</v>
+        <v>84.5099228741013</v>
       </c>
       <c r="F214" t="s">
         <v>24</v>
@@ -4777,13 +4777,13 @@
         <v>9</v>
       </c>
       <c r="C215" t="n">
-        <v>2.94258646052923</v>
+        <v>2.91743558016922</v>
       </c>
       <c r="D215" t="n">
-        <v>17.3672630930871</v>
+        <v>13.6622736530063</v>
       </c>
       <c r="E215" t="n">
-        <v>5.60845529201123</v>
+        <v>4.73484385252627</v>
       </c>
       <c r="F215" t="s">
         <v>24</v>
@@ -4797,13 +4797,13 @@
         <v>10</v>
       </c>
       <c r="C216" t="n">
-        <v>0.873490763080527</v>
+        <v>0.863950207067332</v>
       </c>
       <c r="D216" t="n">
-        <v>16.7621523919176</v>
+        <v>11.3796444075182</v>
       </c>
       <c r="E216" t="n">
-        <v>3.89057124673369</v>
+        <v>3.14572439235806</v>
       </c>
       <c r="F216" t="s">
         <v>24</v>
@@ -4817,13 +4817,13 @@
         <v>11</v>
       </c>
       <c r="C217" t="n">
-        <v>0.607070611689008</v>
+        <v>0.613099113661599</v>
       </c>
       <c r="D217" t="n">
-        <v>0.000930638427535172</v>
+        <v>0.00441472411929373</v>
       </c>
       <c r="E217" t="n">
-        <v>0.331650977557163</v>
+        <v>0.383014160730507</v>
       </c>
       <c r="F217" t="s">
         <v>24</v>
@@ -4837,13 +4837,13 @@
         <v>7</v>
       </c>
       <c r="C218" t="n">
-        <v>27.4858008762133</v>
+        <v>27.4858008873056</v>
       </c>
       <c r="D218" t="n">
-        <v>29.9090177652731</v>
+        <v>29.9090172498438</v>
       </c>
       <c r="E218" t="n">
-        <v>27.6949759081167</v>
+        <v>27.6949758752001</v>
       </c>
       <c r="F218" t="s">
         <v>25</v>
@@ -4857,13 +4857,13 @@
         <v>9</v>
       </c>
       <c r="C219" t="n">
-        <v>11.8365261872966</v>
+        <v>11.8365262092307</v>
       </c>
       <c r="D219" t="n">
-        <v>12.1424481155544</v>
+        <v>12.1424481401422</v>
       </c>
       <c r="E219" t="n">
-        <v>11.8628481088766</v>
+        <v>11.8628481318452</v>
       </c>
       <c r="F219" t="s">
         <v>25</v>
@@ -4877,13 +4877,13 @@
         <v>10</v>
       </c>
       <c r="C220" t="n">
-        <v>1.83838246331172</v>
+        <v>1.83838249046876</v>
       </c>
       <c r="D220" t="n">
-        <v>7.04871498811814</v>
+        <v>7.04871475356691</v>
       </c>
       <c r="E220" t="n">
-        <v>1.98394043411076</v>
+        <v>1.98394045796367</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -4897,13 +4897,13 @@
         <v>11</v>
       </c>
       <c r="C221" t="n">
-        <v>0.616196633138742</v>
+        <v>0.616196630731336</v>
       </c>
       <c r="D221" t="n">
-        <v>0.0168344076365964</v>
+        <v>0.0168344134469117</v>
       </c>
       <c r="E221" t="n">
-        <v>0.590483554013507</v>
+        <v>0.590483550260853</v>
       </c>
       <c r="F221" t="s">
         <v>25</v>
@@ -5153,13 +5153,13 @@
         <v>7</v>
       </c>
       <c r="C234" t="n">
-        <v>30.0303330984048</v>
+        <v>29.7412802212229</v>
       </c>
       <c r="D234" t="n">
-        <v>29.4520603718806</v>
+        <v>29.6003602382755</v>
       </c>
       <c r="E234" t="n">
-        <v>29.9939019577191</v>
+        <v>29.7412208717148</v>
       </c>
       <c r="F234" t="s">
         <v>25</v>
@@ -5173,13 +5173,13 @@
         <v>9</v>
       </c>
       <c r="C235" t="n">
-        <v>12.8666460966963</v>
+        <v>12.7234144794429</v>
       </c>
       <c r="D235" t="n">
-        <v>11.6447991400758</v>
+        <v>11.6808002437501</v>
       </c>
       <c r="E235" t="n">
-        <v>12.7687745071313</v>
+        <v>12.6396802084975</v>
       </c>
       <c r="F235" t="s">
         <v>25</v>
@@ -5193,13 +5193,13 @@
         <v>10</v>
       </c>
       <c r="C236" t="n">
-        <v>1.74830178368633</v>
+        <v>1.74558243973038</v>
       </c>
       <c r="D236" t="n">
-        <v>14.9454676940744</v>
+        <v>15.2426932987221</v>
       </c>
       <c r="E236" t="n">
-        <v>1.89950551070571</v>
+        <v>1.89909069259705</v>
       </c>
       <c r="F236" t="s">
         <v>25</v>
@@ -5213,13 +5213,13 @@
         <v>11</v>
       </c>
       <c r="C237" t="n">
-        <v>0.543635979955995</v>
+        <v>0.551503189428077</v>
       </c>
       <c r="D237" t="n">
-        <v>0.0950683887232778</v>
+        <v>0.0484903723521403</v>
       </c>
       <c r="E237" t="n">
-        <v>0.526277334694018</v>
+        <v>0.53347393761858</v>
       </c>
       <c r="F237" t="s">
         <v>25</v>
@@ -5233,13 +5233,13 @@
         <v>7</v>
       </c>
       <c r="C238" t="n">
-        <v>43.3110438411032</v>
+        <v>35.9545687860852</v>
       </c>
       <c r="D238" t="n">
-        <v>48.1660740286525</v>
+        <v>27.6560852012121</v>
       </c>
       <c r="E238" t="n">
-        <v>43.7044008798572</v>
+        <v>35.3251668833662</v>
       </c>
       <c r="F238" t="s">
         <v>25</v>
@@ -5253,13 +5253,13 @@
         <v>9</v>
       </c>
       <c r="C239" t="n">
-        <v>14.1894763136102</v>
+        <v>13.0599452924902</v>
       </c>
       <c r="D239" t="n">
-        <v>23.0063180257973</v>
+        <v>11.4453792701009</v>
       </c>
       <c r="E239" t="n">
-        <v>15.0620833022131</v>
+        <v>12.943113351837</v>
       </c>
       <c r="F239" t="s">
         <v>25</v>
@@ -5273,13 +5273,13 @@
         <v>10</v>
       </c>
       <c r="C240" t="n">
-        <v>1.13639980506365</v>
+        <v>1.01311626324388</v>
       </c>
       <c r="D240" t="n">
-        <v>5.8254762624167</v>
+        <v>2.10925765615693</v>
       </c>
       <c r="E240" t="n">
-        <v>1.71651709429334</v>
+        <v>1.26146918750958</v>
       </c>
       <c r="F240" t="s">
         <v>25</v>
@@ -5293,13 +5293,13 @@
         <v>11</v>
       </c>
       <c r="C241" t="n">
-        <v>0.477377308114771</v>
+        <v>0.52941516414353</v>
       </c>
       <c r="D241" t="n">
-        <v>0.05992747157962</v>
+        <v>0.0969470766885995</v>
       </c>
       <c r="E241" t="n">
-        <v>0.429167981185455</v>
+        <v>0.514690955550096</v>
       </c>
       <c r="F241" t="s">
         <v>25</v>
@@ -5313,13 +5313,13 @@
         <v>7</v>
       </c>
       <c r="C242" t="n">
-        <v>19.9243466342209</v>
+        <v>19.9243466211263</v>
       </c>
       <c r="D242" t="n">
-        <v>18.9240029111893</v>
+        <v>18.9240021598939</v>
       </c>
       <c r="E242" t="n">
-        <v>19.8421540190514</v>
+        <v>19.8421539444419</v>
       </c>
       <c r="F242" t="s">
         <v>26</v>
@@ -5333,13 +5333,13 @@
         <v>9</v>
       </c>
       <c r="C243" t="n">
-        <v>104.596672719668</v>
+        <v>104.596672647046</v>
       </c>
       <c r="D243" t="n">
-        <v>117.730985475538</v>
+        <v>117.730980081582</v>
       </c>
       <c r="E243" t="n">
-        <v>105.760289122873</v>
+        <v>105.760288556215</v>
       </c>
       <c r="F243" t="s">
         <v>26</v>
@@ -5353,13 +5353,13 @@
         <v>10</v>
       </c>
       <c r="C244" t="n">
-        <v>1.10265977958016</v>
+        <v>1.10265978260819</v>
       </c>
       <c r="D244" t="n">
-        <v>2.82833446365151</v>
+        <v>2.82833435087698</v>
       </c>
       <c r="E244" t="n">
-        <v>1.18207601250334</v>
+        <v>1.18207600826627</v>
       </c>
       <c r="F244" t="s">
         <v>26</v>
@@ -5373,13 +5373,13 @@
         <v>11</v>
       </c>
       <c r="C245" t="n">
-        <v>0.776354194689195</v>
+        <v>0.77635419526886</v>
       </c>
       <c r="D245" t="n">
-        <v>0.52654929091932</v>
+        <v>0.526549302330258</v>
       </c>
       <c r="E245" t="n">
-        <v>0.770144397264812</v>
+        <v>0.770144399313918</v>
       </c>
       <c r="F245" t="s">
         <v>26</v>
@@ -5629,13 +5629,13 @@
         <v>7</v>
       </c>
       <c r="C258" t="n">
-        <v>19.5007209412547</v>
+        <v>19.5097010616883</v>
       </c>
       <c r="D258" t="n">
-        <v>52.1714767206009</v>
+        <v>52.5256463028136</v>
       </c>
       <c r="E258" t="n">
-        <v>22.2249344224745</v>
+        <v>22.2626789651674</v>
       </c>
       <c r="F258" t="s">
         <v>26</v>
@@ -5649,13 +5649,13 @@
         <v>9</v>
       </c>
       <c r="C259" t="n">
-        <v>102.034480191341</v>
+        <v>102.256227687797</v>
       </c>
       <c r="D259" t="n">
-        <v>339.080671910569</v>
+        <v>342.219466237299</v>
       </c>
       <c r="E259" t="n">
-        <v>138.312030429243</v>
+        <v>139.104285877521</v>
       </c>
       <c r="F259" t="s">
         <v>26</v>
@@ -5669,13 +5669,13 @@
         <v>10</v>
       </c>
       <c r="C260" t="n">
-        <v>1.0237138538715</v>
+        <v>1.02425390152865</v>
       </c>
       <c r="D260" t="n">
-        <v>11.29929733562</v>
+        <v>10.9737784246023</v>
       </c>
       <c r="E260" t="n">
-        <v>1.44564938626998</v>
+        <v>1.4482943471332</v>
       </c>
       <c r="F260" t="s">
         <v>26</v>
@@ -5689,13 +5689,13 @@
         <v>11</v>
       </c>
       <c r="C261" t="n">
-        <v>0.786678818283551</v>
+        <v>0.78589328720627</v>
       </c>
       <c r="D261" t="n">
-        <v>0.313889439327507</v>
+        <v>0.304455971001738</v>
       </c>
       <c r="E261" t="n">
-        <v>0.697324776940006</v>
+        <v>0.695732828303995</v>
       </c>
       <c r="F261" t="s">
         <v>26</v>
@@ -5709,13 +5709,13 @@
         <v>7</v>
       </c>
       <c r="C262" t="n">
-        <v>31.0155321298865</v>
+        <v>30.7509136526267</v>
       </c>
       <c r="D262" t="n">
-        <v>58.2542425838741</v>
+        <v>58.9602722552726</v>
       </c>
       <c r="E262" t="n">
-        <v>33.1123125294407</v>
+        <v>32.9223522043231</v>
       </c>
       <c r="F262" t="s">
         <v>26</v>
@@ -5729,13 +5729,13 @@
         <v>9</v>
       </c>
       <c r="C263" t="n">
-        <v>108.570482139423</v>
+        <v>108.506331460734</v>
       </c>
       <c r="D263" t="n">
-        <v>392.33573895813</v>
+        <v>403.568459038297</v>
       </c>
       <c r="E263" t="n">
-        <v>150.755681670076</v>
+        <v>152.977946313304</v>
       </c>
       <c r="F263" t="s">
         <v>26</v>
@@ -5749,13 +5749,13 @@
         <v>10</v>
       </c>
       <c r="C264" t="n">
-        <v>1.11083031203022</v>
+        <v>1.1033001842027</v>
       </c>
       <c r="D264" t="n">
-        <v>11.2690825842654</v>
+        <v>8.91782392437817</v>
       </c>
       <c r="E264" t="n">
-        <v>1.24252753614442</v>
+        <v>1.20545137578501</v>
       </c>
       <c r="F264" t="s">
         <v>26</v>
@@ -5769,13 +5769,13 @@
         <v>11</v>
       </c>
       <c r="C265" t="n">
-        <v>0.751079698569155</v>
+        <v>0.75433333736142</v>
       </c>
       <c r="D265" t="n">
-        <v>0.371160688379869</v>
+        <v>0.14240792392019</v>
       </c>
       <c r="E265" t="n">
-        <v>0.666256389630684</v>
+        <v>0.66544448621774</v>
       </c>
       <c r="F265" t="s">
         <v>26</v>
@@ -5789,13 +5789,13 @@
         <v>7</v>
       </c>
       <c r="C266" t="n">
-        <v>12.4023297480423</v>
+        <v>12.4029220612177</v>
       </c>
       <c r="D266" t="n">
-        <v>27.9995952294475</v>
+        <v>27.989037988184</v>
       </c>
       <c r="E266" t="n">
-        <v>13.6980553842826</v>
+        <v>13.6977185178949</v>
       </c>
       <c r="F266" t="s">
         <v>27</v>
@@ -5809,13 +5809,13 @@
         <v>9</v>
       </c>
       <c r="C267" t="n">
-        <v>170.948940898728</v>
+        <v>170.937063930182</v>
       </c>
       <c r="D267" t="n">
-        <v>64.0146618254462</v>
+        <v>64.0013702404647</v>
       </c>
       <c r="E267" t="n">
-        <v>164.708299327463</v>
+        <v>164.696569969545</v>
       </c>
       <c r="F267" t="s">
         <v>27</v>
@@ -5829,13 +5829,13 @@
         <v>10</v>
       </c>
       <c r="C268" t="n">
-        <v>0.904520993837004</v>
+        <v>0.904363825378849</v>
       </c>
       <c r="D268" t="n">
-        <v>6.98671990181055</v>
+        <v>6.9856178685665</v>
       </c>
       <c r="E268" t="n">
-        <v>0.944431155562461</v>
+        <v>0.944253245085875</v>
       </c>
       <c r="F268" t="s">
         <v>27</v>
@@ -5849,13 +5849,13 @@
         <v>11</v>
       </c>
       <c r="C269" t="n">
-        <v>0.905339283350668</v>
+        <v>0.905337406831082</v>
       </c>
       <c r="D269" t="n">
-        <v>0.554147729698816</v>
+        <v>0.554114083447233</v>
       </c>
       <c r="E269" t="n">
-        <v>0.909489343496953</v>
+        <v>0.909488469868603</v>
       </c>
       <c r="F269" t="s">
         <v>27</v>
@@ -6109,13 +6109,13 @@
         <v>7</v>
       </c>
       <c r="C282" t="n">
-        <v>8.93076580129492</v>
+        <v>8.929098426752</v>
       </c>
       <c r="D282" t="n">
-        <v>26.5489609553236</v>
+        <v>26.5954292232831</v>
       </c>
       <c r="E282" t="n">
-        <v>10.3957152815116</v>
+        <v>10.398059398337</v>
       </c>
       <c r="F282" t="s">
         <v>27</v>
@@ -6129,13 +6129,13 @@
         <v>9</v>
       </c>
       <c r="C283" t="n">
-        <v>104.604990756107</v>
+        <v>104.433265805542</v>
       </c>
       <c r="D283" t="n">
-        <v>60.2460705876829</v>
+        <v>60.2505534088074</v>
       </c>
       <c r="E283" t="n">
-        <v>101.646255384172</v>
+        <v>101.484482040548</v>
       </c>
       <c r="F283" t="s">
         <v>27</v>
@@ -6149,13 +6149,13 @@
         <v>10</v>
       </c>
       <c r="C284" t="n">
-        <v>0.584946369812051</v>
+        <v>0.583501890087322</v>
       </c>
       <c r="D284" t="n">
-        <v>4.73126979238259</v>
+        <v>4.69984259231056</v>
       </c>
       <c r="E284" t="n">
-        <v>0.622256926097098</v>
+        <v>0.620725388813185</v>
       </c>
       <c r="F284" t="s">
         <v>27</v>
@@ -6169,13 +6169,13 @@
         <v>11</v>
       </c>
       <c r="C285" t="n">
-        <v>0.965228429555099</v>
+        <v>0.965438223571538</v>
       </c>
       <c r="D285" t="n">
-        <v>0.492819559746283</v>
+        <v>0.491911560943271</v>
       </c>
       <c r="E285" t="n">
-        <v>0.966258306437198</v>
+        <v>0.966465602031347</v>
       </c>
       <c r="F285" t="s">
         <v>27</v>
@@ -6189,13 +6189,13 @@
         <v>7</v>
       </c>
       <c r="C286" t="n">
-        <v>28.4987605599006</v>
+        <v>28.3132425416339</v>
       </c>
       <c r="D286" t="n">
-        <v>23.2838444744176</v>
+        <v>36.7880585563002</v>
       </c>
       <c r="E286" t="n">
-        <v>28.0973100728576</v>
+        <v>28.9633730232076</v>
       </c>
       <c r="F286" t="s">
         <v>27</v>
@@ -6209,13 +6209,13 @@
         <v>9</v>
       </c>
       <c r="C287" t="n">
-        <v>173.02404505474</v>
+        <v>172.758869979549</v>
       </c>
       <c r="D287" t="n">
-        <v>57.2054719785513</v>
+        <v>75.9545430643907</v>
       </c>
       <c r="E287" t="n">
-        <v>166.991289105253</v>
+        <v>167.311256827295</v>
       </c>
       <c r="F287" t="s">
         <v>27</v>
@@ -6229,13 +6229,13 @@
         <v>10</v>
       </c>
       <c r="C288" t="n">
-        <v>1.08444567365642</v>
+        <v>1.07620491261893</v>
       </c>
       <c r="D288" t="n">
-        <v>1.98279069741803</v>
+        <v>2.15691183672255</v>
       </c>
       <c r="E288" t="n">
-        <v>0.832925824601086</v>
+        <v>0.827356468920876</v>
       </c>
       <c r="F288" t="s">
         <v>27</v>
@@ -6249,13 +6249,13 @@
         <v>11</v>
       </c>
       <c r="C289" t="n">
-        <v>0.903378672204654</v>
+        <v>0.903716872291992</v>
       </c>
       <c r="D289" t="n">
-        <v>0.109448389669724</v>
+        <v>0.067301170943288</v>
       </c>
       <c r="E289" t="n">
-        <v>0.90762269008004</v>
+        <v>0.90790275722648</v>
       </c>
       <c r="F289" t="s">
         <v>27</v>
@@ -6269,13 +6269,13 @@
         <v>7</v>
       </c>
       <c r="C290" t="n">
-        <v>9.94926847246549</v>
+        <v>9.94926855299266</v>
       </c>
       <c r="D290" t="n">
-        <v>35.1282769322331</v>
+        <v>35.1282765590949</v>
       </c>
       <c r="E290" t="n">
-        <v>12.0477044784776</v>
+        <v>12.0477045211986</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -6289,13 +6289,13 @@
         <v>9</v>
       </c>
       <c r="C291" t="n">
-        <v>1538.83734587715</v>
+        <v>1538.83738362997</v>
       </c>
       <c r="D291" t="n">
-        <v>3278.16910562922</v>
+        <v>3278.16854972222</v>
       </c>
       <c r="E291" t="n">
-        <v>1751.07253337202</v>
+        <v>1751.07247705744</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -6309,13 +6309,13 @@
         <v>10</v>
       </c>
       <c r="C292" t="n">
-        <v>0.446351802702294</v>
+        <v>0.446351878253712</v>
       </c>
       <c r="D292" t="n">
-        <v>1.11561602710387</v>
+        <v>1.11561603872641</v>
       </c>
       <c r="E292" t="n">
-        <v>0.509140938714863</v>
+        <v>0.509141008544101</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -6329,13 +6329,13 @@
         <v>11</v>
       </c>
       <c r="C293" t="n">
-        <v>0.882335019542597</v>
+        <v>0.882335035147841</v>
       </c>
       <c r="D293" t="n">
-        <v>0.864028994761883</v>
+        <v>0.864029010787868</v>
       </c>
       <c r="E293" t="n">
-        <v>0.811802594968922</v>
+        <v>0.811802616759772</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -6589,13 +6589,13 @@
         <v>7</v>
       </c>
       <c r="C306" t="n">
-        <v>8.71006686473152</v>
+        <v>8.34670113931623</v>
       </c>
       <c r="D306" t="n">
-        <v>40.6745776327873</v>
+        <v>38.7625892791574</v>
       </c>
       <c r="E306" t="n">
-        <v>11.3740042664158</v>
+        <v>10.8815877217716</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -6609,13 +6609,13 @@
         <v>9</v>
       </c>
       <c r="C307" t="n">
-        <v>1092.89986833401</v>
+        <v>1103.56218189043</v>
       </c>
       <c r="D307" t="n">
-        <v>7285.32886513336</v>
+        <v>5960.71958743075</v>
       </c>
       <c r="E307" t="n">
-        <v>2349.03415355733</v>
+        <v>2019.22420907085</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -6629,13 +6629,13 @@
         <v>10</v>
       </c>
       <c r="C308" t="n">
-        <v>0.327159094037267</v>
+        <v>0.333366684229607</v>
       </c>
       <c r="D308" t="n">
-        <v>1.01871076606496</v>
+        <v>1.04646041745019</v>
       </c>
       <c r="E308" t="n">
-        <v>0.440385576230302</v>
+        <v>0.435025537278986</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -6649,13 +6649,13 @@
         <v>11</v>
       </c>
       <c r="C309" t="n">
-        <v>0.93114251102364</v>
+        <v>0.93424425545203</v>
       </c>
       <c r="D309" t="n">
-        <v>0.885340225770157</v>
+        <v>0.896771778704888</v>
       </c>
       <c r="E309" t="n">
-        <v>0.721114281096443</v>
+        <v>0.766295571827648</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -6669,13 +6669,13 @@
         <v>7</v>
       </c>
       <c r="C310" t="n">
-        <v>26.3555056009133</v>
+        <v>26.2051257217934</v>
       </c>
       <c r="D310" t="n">
-        <v>37.1607216921043</v>
+        <v>43.5542258218498</v>
       </c>
       <c r="E310" t="n">
-        <v>27.1865897540154</v>
+        <v>27.5395462127526</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -6689,13 +6689,13 @@
         <v>9</v>
       </c>
       <c r="C311" t="n">
-        <v>2185.7824823939</v>
+        <v>2183.41987877234</v>
       </c>
       <c r="D311" t="n">
-        <v>2621.91587562007</v>
+        <v>2543.08347722101</v>
       </c>
       <c r="E311" t="n">
-        <v>2222.37548511347</v>
+        <v>2213.16454125186</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -6709,13 +6709,13 @@
         <v>10</v>
       </c>
       <c r="C312" t="n">
-        <v>0.78428641143877</v>
+        <v>0.7821038279199</v>
       </c>
       <c r="D312" t="n">
-        <v>1.26759976970404</v>
+        <v>1.26835667099576</v>
       </c>
       <c r="E312" t="n">
-        <v>0.685689617639074</v>
+        <v>0.683360428490109</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -6729,13 +6729,13 @@
         <v>11</v>
       </c>
       <c r="C313" t="n">
-        <v>0.751872117855715</v>
+        <v>0.752649913276639</v>
       </c>
       <c r="D313" t="n">
-        <v>0.955232613596312</v>
+        <v>0.986673682166393</v>
       </c>
       <c r="E313" t="n">
-        <v>0.737477912824442</v>
+        <v>0.740569486304167</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -6749,13 +6749,13 @@
         <v>7</v>
       </c>
       <c r="C314" t="n">
-        <v>39.9454712888373</v>
+        <v>39.9454712566906</v>
       </c>
       <c r="D314" t="n">
-        <v>114.979896460011</v>
+        <v>114.979896577512</v>
       </c>
       <c r="E314" t="n">
-        <v>46.4379299482376</v>
+        <v>46.4379299295983</v>
       </c>
       <c r="F314" t="s">
         <v>29</v>
@@ -6769,13 +6769,13 @@
         <v>9</v>
       </c>
       <c r="C315" t="n">
-        <v>3.36752599239888</v>
+        <v>3.36752599128992</v>
       </c>
       <c r="D315" t="n">
-        <v>4.8209885564357</v>
+        <v>4.82098855783693</v>
       </c>
       <c r="E315" t="n">
-        <v>3.50363418701977</v>
+        <v>3.50363418619815</v>
       </c>
       <c r="F315" t="s">
         <v>29</v>
@@ -6789,13 +6789,13 @@
         <v>10</v>
       </c>
       <c r="C316" t="n">
-        <v>1.13036227392197</v>
+        <v>1.13036227115289</v>
       </c>
       <c r="D316" t="n">
-        <v>13.1879231482955</v>
+        <v>13.1879231225185</v>
       </c>
       <c r="E316" t="n">
-        <v>1.30147246568846</v>
+        <v>1.30147246273331</v>
       </c>
       <c r="F316" t="s">
         <v>29</v>
@@ -6809,13 +6809,13 @@
         <v>11</v>
       </c>
       <c r="C317" t="n">
-        <v>0.853964902194714</v>
+        <v>0.85396490233397</v>
       </c>
       <c r="D317" t="n">
-        <v>0.0774529073714584</v>
+        <v>0.0774529073015438</v>
       </c>
       <c r="E317" t="n">
-        <v>0.832837979089992</v>
+        <v>0.832837979185403</v>
       </c>
       <c r="F317" t="s">
         <v>29</v>
@@ -6907,13 +6907,13 @@
         <v>7</v>
       </c>
       <c r="C322" t="n">
-        <v>58.1819011348644</v>
+        <v>58.1819011348652</v>
       </c>
       <c r="D322" t="n">
         <v>80.4773176642031</v>
       </c>
       <c r="E322" t="n">
-        <v>60.0460216676867</v>
+        <v>60.0460216676875</v>
       </c>
       <c r="F322" t="s">
         <v>29</v>
@@ -6927,7 +6927,7 @@
         <v>9</v>
       </c>
       <c r="C323" t="n">
-        <v>4.42592596051654</v>
+        <v>4.42592596051655</v>
       </c>
       <c r="D323" t="n">
         <v>3.87059311877828</v>
@@ -6947,13 +6947,13 @@
         <v>10</v>
       </c>
       <c r="C324" t="n">
-        <v>2.73068255714958</v>
+        <v>2.73068255714938</v>
       </c>
       <c r="D324" t="n">
-        <v>113.058636995659</v>
+        <v>113.058636995653</v>
       </c>
       <c r="E324" t="n">
-        <v>2.95370493320544</v>
+        <v>2.95370493320523</v>
       </c>
       <c r="F324" t="s">
         <v>29</v>
@@ -6967,13 +6967,13 @@
         <v>11</v>
       </c>
       <c r="C325" t="n">
-        <v>0.717172931367507</v>
+        <v>0.717172931367508</v>
       </c>
       <c r="D325" t="n">
-        <v>0.0212052971954805</v>
+        <v>0.0212052971954807</v>
       </c>
       <c r="E325" t="n">
-        <v>0.711110243867643</v>
+        <v>0.711110243867644</v>
       </c>
       <c r="F325" t="s">
         <v>29</v>
@@ -7067,13 +7067,13 @@
         <v>7</v>
       </c>
       <c r="C330" t="n">
-        <v>51.0780775512644</v>
+        <v>50.8127389345885</v>
       </c>
       <c r="D330" t="n">
-        <v>82.7143662815323</v>
+        <v>84.1647476855149</v>
       </c>
       <c r="E330" t="n">
-        <v>53.8767383898804</v>
+        <v>53.7560649282778</v>
       </c>
       <c r="F330" t="s">
         <v>29</v>
@@ -7087,13 +7087,13 @@
         <v>9</v>
       </c>
       <c r="C331" t="n">
-        <v>3.86674240201512</v>
+        <v>3.83060030654334</v>
       </c>
       <c r="D331" t="n">
-        <v>4.04688382618264</v>
+        <v>4.05934057272183</v>
       </c>
       <c r="E331" t="n">
-        <v>3.87729277818486</v>
+        <v>3.84531902357586</v>
       </c>
       <c r="F331" t="s">
         <v>29</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="C332" t="n">
-        <v>3.19742274873819</v>
+        <v>3.05633269391807</v>
       </c>
       <c r="D332" t="n">
-        <v>11.6515574384649</v>
+        <v>12.4939664416464</v>
       </c>
       <c r="E332" t="n">
-        <v>3.44777054681476</v>
+        <v>3.31018125007899</v>
       </c>
       <c r="F332" t="s">
         <v>29</v>
@@ -7127,13 +7127,13 @@
         <v>11</v>
       </c>
       <c r="C333" t="n">
-        <v>0.79808629322619</v>
+        <v>0.801904655228665</v>
       </c>
       <c r="D333" t="n">
-        <v>0.0867557322591837</v>
+        <v>0.104589451917385</v>
       </c>
       <c r="E333" t="n">
-        <v>0.786981839065087</v>
+        <v>0.79054853262469</v>
       </c>
       <c r="F333" t="s">
         <v>29</v>
@@ -7147,13 +7147,13 @@
         <v>7</v>
       </c>
       <c r="C334" t="n">
-        <v>72.6440157324844</v>
+        <v>72.099768420929</v>
       </c>
       <c r="D334" t="n">
-        <v>67.2514444238214</v>
+        <v>64.954971036869</v>
       </c>
       <c r="E334" t="n">
-        <v>72.3543325804144</v>
+        <v>71.6794418562494</v>
       </c>
       <c r="F334" t="s">
         <v>29</v>
@@ -7167,13 +7167,13 @@
         <v>9</v>
       </c>
       <c r="C335" t="n">
-        <v>4.83313564549568</v>
+        <v>4.83757917602363</v>
       </c>
       <c r="D335" t="n">
-        <v>3.70789602934779</v>
+        <v>3.6518653556395</v>
       </c>
       <c r="E335" t="n">
-        <v>4.75536998318494</v>
+        <v>4.75598775378914</v>
       </c>
       <c r="F335" t="s">
         <v>29</v>
@@ -7187,13 +7187,13 @@
         <v>10</v>
       </c>
       <c r="C336" t="n">
-        <v>0.881280850708999</v>
+        <v>0.88155555006794</v>
       </c>
       <c r="D336" t="n">
-        <v>1.32275865515011</v>
+        <v>1.40946258710616</v>
       </c>
       <c r="E336" t="n">
-        <v>1.06040886797526</v>
+        <v>1.04850549957186</v>
       </c>
       <c r="F336" t="s">
         <v>29</v>
@@ -7207,13 +7207,13 @@
         <v>11</v>
       </c>
       <c r="C337" t="n">
-        <v>0.689889884431726</v>
+        <v>0.688318044066123</v>
       </c>
       <c r="D337" t="n">
-        <v>0.00630240442861484</v>
+        <v>0.000821295857565829</v>
       </c>
       <c r="E337" t="n">
-        <v>0.683847834486338</v>
+        <v>0.682924683242756</v>
       </c>
       <c r="F337" t="s">
         <v>29</v>
@@ -7227,13 +7227,13 @@
         <v>7</v>
       </c>
       <c r="C338" t="n">
-        <v>23.5656360144871</v>
+        <v>23.5656355840209</v>
       </c>
       <c r="D338" t="n">
-        <v>41.5419352381425</v>
+        <v>41.541937243117</v>
       </c>
       <c r="E338" t="n">
-        <v>25.0485491336662</v>
+        <v>25.0485488597305</v>
       </c>
       <c r="F338" t="s">
         <v>30</v>
@@ -7247,13 +7247,13 @@
         <v>9</v>
       </c>
       <c r="C339" t="n">
-        <v>16.4626469095753</v>
+        <v>16.4626468042807</v>
       </c>
       <c r="D339" t="n">
-        <v>23.9935598960196</v>
+        <v>23.9935601905122</v>
       </c>
       <c r="E339" t="n">
-        <v>17.2091944424593</v>
+        <v>17.2091943840232</v>
       </c>
       <c r="F339" t="s">
         <v>30</v>
@@ -7267,13 +7267,13 @@
         <v>10</v>
       </c>
       <c r="C340" t="n">
-        <v>2.44926762265029</v>
+        <v>2.44926727874784</v>
       </c>
       <c r="D340" t="n">
-        <v>11.0164262861721</v>
+        <v>11.0164257768261</v>
       </c>
       <c r="E340" t="n">
-        <v>2.66882892509124</v>
+        <v>2.66882856642558</v>
       </c>
       <c r="F340" t="s">
         <v>30</v>
@@ -7287,13 +7287,13 @@
         <v>11</v>
       </c>
       <c r="C341" t="n">
-        <v>0.841488800341066</v>
+        <v>0.841488800674903</v>
       </c>
       <c r="D341" t="n">
-        <v>0.414851648321845</v>
+        <v>0.414851675981611</v>
       </c>
       <c r="E341" t="n">
-        <v>0.82148691846284</v>
+        <v>0.821486918914636</v>
       </c>
       <c r="F341" t="s">
         <v>30</v>
@@ -7547,13 +7547,13 @@
         <v>7</v>
       </c>
       <c r="C354" t="n">
-        <v>22.4557982197914</v>
+        <v>22.3453647337989</v>
       </c>
       <c r="D354" t="n">
-        <v>27.7200691347633</v>
+        <v>27.9313982238636</v>
       </c>
       <c r="E354" t="n">
-        <v>22.8981309060356</v>
+        <v>22.814530553566</v>
       </c>
       <c r="F354" t="s">
         <v>30</v>
@@ -7567,13 +7567,13 @@
         <v>9</v>
       </c>
       <c r="C355" t="n">
-        <v>14.0474517469286</v>
+        <v>13.9783932376202</v>
       </c>
       <c r="D355" t="n">
-        <v>17.7799046423182</v>
+        <v>18.0145176329823</v>
       </c>
       <c r="E355" t="n">
-        <v>14.3908295130626</v>
+        <v>14.3532975286817</v>
       </c>
       <c r="F355" t="s">
         <v>30</v>
@@ -7587,13 +7587,13 @@
         <v>10</v>
       </c>
       <c r="C356" t="n">
-        <v>1.61116379835117</v>
+        <v>1.62482971893137</v>
       </c>
       <c r="D356" t="n">
-        <v>3.38335157483166</v>
+        <v>3.51737377949933</v>
       </c>
       <c r="E356" t="n">
-        <v>1.66202325393246</v>
+        <v>1.6798000061632</v>
       </c>
       <c r="F356" t="s">
         <v>30</v>
@@ -7607,13 +7607,13 @@
         <v>11</v>
       </c>
       <c r="C357" t="n">
-        <v>0.88372008101211</v>
+        <v>0.884873941451563</v>
       </c>
       <c r="D357" t="n">
-        <v>0.649516880767107</v>
+        <v>0.650246475108855</v>
       </c>
       <c r="E357" t="n">
-        <v>0.872830456773558</v>
+        <v>0.873520733968525</v>
       </c>
       <c r="F357" t="s">
         <v>30</v>
@@ -7627,13 +7627,13 @@
         <v>7</v>
       </c>
       <c r="C358" t="n">
-        <v>29.1640279935893</v>
+        <v>28.1490879522214</v>
       </c>
       <c r="D358" t="n">
-        <v>28.6668936553761</v>
+        <v>25.1540621534846</v>
       </c>
       <c r="E358" t="n">
-        <v>29.1402560435413</v>
+        <v>27.9291177904781</v>
       </c>
       <c r="F358" t="s">
         <v>30</v>
@@ -7647,13 +7647,13 @@
         <v>9</v>
       </c>
       <c r="C359" t="n">
-        <v>17.7176308034035</v>
+        <v>17.6368106827245</v>
       </c>
       <c r="D359" t="n">
-        <v>13.6528599218062</v>
+        <v>12.9431945055389</v>
       </c>
       <c r="E359" t="n">
-        <v>17.4394933870502</v>
+        <v>17.3208845147701</v>
       </c>
       <c r="F359" t="s">
         <v>30</v>
@@ -7667,13 +7667,13 @@
         <v>10</v>
       </c>
       <c r="C360" t="n">
-        <v>0.7785275951707</v>
+        <v>0.765980737403246</v>
       </c>
       <c r="D360" t="n">
-        <v>1.91719862971154</v>
+        <v>1.69430280803343</v>
       </c>
       <c r="E360" t="n">
-        <v>0.893919591938985</v>
+        <v>0.871940323172192</v>
       </c>
       <c r="F360" t="s">
         <v>30</v>
@@ -7687,13 +7687,13 @@
         <v>11</v>
       </c>
       <c r="C361" t="n">
-        <v>0.827374333365867</v>
+        <v>0.828934546470541</v>
       </c>
       <c r="D361" t="n">
-        <v>0.630117499790497</v>
+        <v>0.699233975986158</v>
       </c>
       <c r="E361" t="n">
-        <v>0.82454747855395</v>
+        <v>0.827363787555287</v>
       </c>
       <c r="F361" t="s">
         <v>30</v>
@@ -7707,13 +7707,13 @@
         <v>7</v>
       </c>
       <c r="C362" t="n">
-        <v>13.534347349086</v>
+        <v>13.5343473485205</v>
       </c>
       <c r="D362" t="n">
-        <v>7.1578525737188</v>
+        <v>7.1578525861216</v>
       </c>
       <c r="E362" t="n">
-        <v>13.0047669312453</v>
+        <v>13.0047669317603</v>
       </c>
       <c r="F362" t="s">
         <v>31</v>
@@ -7727,13 +7727,13 @@
         <v>9</v>
       </c>
       <c r="C363" t="n">
-        <v>9.58377630581015</v>
+        <v>9.58377630447927</v>
       </c>
       <c r="D363" t="n">
-        <v>9.46464653452706</v>
+        <v>9.46464655579824</v>
       </c>
       <c r="E363" t="n">
-        <v>9.57555099152441</v>
+        <v>9.57555099211331</v>
       </c>
       <c r="F363" t="s">
         <v>31</v>
@@ -7747,13 +7747,13 @@
         <v>10</v>
       </c>
       <c r="C364" t="n">
-        <v>1.74047438978389</v>
+        <v>1.74047438812206</v>
       </c>
       <c r="D364" t="n">
-        <v>1.05368506135935</v>
+        <v>1.05368506000712</v>
       </c>
       <c r="E364" t="n">
-        <v>1.64671294050034</v>
+        <v>1.64671293874847</v>
       </c>
       <c r="F364" t="s">
         <v>31</v>
@@ -7767,13 +7767,13 @@
         <v>11</v>
       </c>
       <c r="C365" t="n">
-        <v>0.853125654481047</v>
+        <v>0.853125654497093</v>
       </c>
       <c r="D365" t="n">
-        <v>0.102848993677774</v>
+        <v>0.102848993369181</v>
       </c>
       <c r="E365" t="n">
-        <v>0.8816718407576</v>
+        <v>0.881671840740343</v>
       </c>
       <c r="F365" t="s">
         <v>31</v>
@@ -8027,13 +8027,13 @@
         <v>7</v>
       </c>
       <c r="C378" t="n">
-        <v>11.988383794281</v>
+        <v>11.9657601820755</v>
       </c>
       <c r="D378" t="n">
-        <v>10.6327452569984</v>
+        <v>10.7961498192745</v>
       </c>
       <c r="E378" t="n">
-        <v>11.8816020098716</v>
+        <v>11.8748399680959</v>
       </c>
       <c r="F378" t="s">
         <v>31</v>
@@ -8047,13 +8047,13 @@
         <v>9</v>
       </c>
       <c r="C379" t="n">
-        <v>8.69145788992324</v>
+        <v>8.67050524839956</v>
       </c>
       <c r="D379" t="n">
-        <v>14.077828081419</v>
+        <v>14.2882477085281</v>
       </c>
       <c r="E379" t="n">
-        <v>9.27064365804141</v>
+        <v>9.27969567656853</v>
       </c>
       <c r="F379" t="s">
         <v>31</v>
@@ -8067,13 +8067,13 @@
         <v>10</v>
       </c>
       <c r="C380" t="n">
-        <v>2.23128763305705</v>
+        <v>2.22319577515732</v>
       </c>
       <c r="D380" t="n">
-        <v>3.0494587674696</v>
+        <v>2.88691538108305</v>
       </c>
       <c r="E380" t="n">
-        <v>2.24978303766852</v>
+        <v>2.22889963108581</v>
       </c>
       <c r="F380" t="s">
         <v>31</v>
@@ -8087,13 +8087,13 @@
         <v>11</v>
       </c>
       <c r="C381" t="n">
-        <v>0.881673216237175</v>
+        <v>0.882294558558489</v>
       </c>
       <c r="D381" t="n">
-        <v>0.120865880013061</v>
+        <v>0.119584398069745</v>
       </c>
       <c r="E381" t="n">
-        <v>0.89145988655446</v>
+        <v>0.891434078024848</v>
       </c>
       <c r="F381" t="s">
         <v>31</v>
@@ -8107,13 +8107,13 @@
         <v>7</v>
       </c>
       <c r="C382" t="n">
-        <v>13.9553660375354</v>
+        <v>13.9547276531248</v>
       </c>
       <c r="D382" t="n">
-        <v>12.2295521230371</v>
+        <v>11.3953802617618</v>
       </c>
       <c r="E382" t="n">
-        <v>13.8286480165694</v>
+        <v>13.7638979117456</v>
       </c>
       <c r="F382" t="s">
         <v>31</v>
@@ -8127,13 +8127,13 @@
         <v>9</v>
       </c>
       <c r="C383" t="n">
-        <v>9.42620010577596</v>
+        <v>9.42337194328017</v>
       </c>
       <c r="D383" t="n">
-        <v>15.8136290610469</v>
+        <v>14.4842373557081</v>
       </c>
       <c r="E383" t="n">
-        <v>10.0725207757554</v>
+        <v>9.91401136998441</v>
       </c>
       <c r="F383" t="s">
         <v>31</v>
@@ -8147,13 +8147,13 @@
         <v>10</v>
       </c>
       <c r="C384" t="n">
-        <v>0.681635679831258</v>
+        <v>0.681693635866311</v>
       </c>
       <c r="D384" t="n">
-        <v>4.47116946596625</v>
+        <v>3.46847797391463</v>
       </c>
       <c r="E384" t="n">
-        <v>1.41406087932353</v>
+        <v>1.39181110529908</v>
       </c>
       <c r="F384" t="s">
         <v>31</v>
@@ -8167,13 +8167,13 @@
         <v>11</v>
       </c>
       <c r="C385" t="n">
-        <v>0.863592757374017</v>
+        <v>0.863824417615633</v>
       </c>
       <c r="D385" t="n">
-        <v>0.101795893505413</v>
+        <v>0.168653315950643</v>
       </c>
       <c r="E385" t="n">
-        <v>0.880022992035467</v>
+        <v>0.882434793691936</v>
       </c>
       <c r="F385" t="s">
         <v>31</v>
@@ -8187,13 +8187,13 @@
         <v>7</v>
       </c>
       <c r="C386" t="n">
-        <v>11.3797899415746</v>
+        <v>11.3797898998031</v>
       </c>
       <c r="D386" t="n">
-        <v>7.28563078627162</v>
+        <v>7.28563101278436</v>
       </c>
       <c r="E386" t="n">
-        <v>11.0406111382775</v>
+        <v>11.0406111188622</v>
       </c>
       <c r="F386" t="s">
         <v>32</v>
@@ -8207,13 +8207,13 @@
         <v>9</v>
       </c>
       <c r="C387" t="n">
-        <v>21.912736841319</v>
+        <v>21.9127367409449</v>
       </c>
       <c r="D387" t="n">
-        <v>16.0646667166634</v>
+        <v>16.0646667047263</v>
       </c>
       <c r="E387" t="n">
-        <v>21.4855254113769</v>
+        <v>21.4855253171238</v>
       </c>
       <c r="F387" t="s">
         <v>32</v>
@@ -8227,13 +8227,13 @@
         <v>10</v>
       </c>
       <c r="C388" t="n">
-        <v>2.33251494682805</v>
+        <v>2.33251490511695</v>
       </c>
       <c r="D388" t="n">
-        <v>3.87963133268864</v>
+        <v>3.87963127793987</v>
       </c>
       <c r="E388" t="n">
-        <v>2.40235910515354</v>
+        <v>2.40235906477685</v>
       </c>
       <c r="F388" t="s">
         <v>32</v>
@@ -8247,13 +8247,13 @@
         <v>11</v>
       </c>
       <c r="C389" t="n">
-        <v>0.736264105687684</v>
+        <v>0.736264106853572</v>
       </c>
       <c r="D389" t="n">
-        <v>0.0732282095659751</v>
+        <v>0.0732281961697488</v>
       </c>
       <c r="E389" t="n">
-        <v>0.731887989088188</v>
+        <v>0.731887990059567</v>
       </c>
       <c r="F389" t="s">
         <v>32</v>
@@ -8347,13 +8347,13 @@
         <v>7</v>
       </c>
       <c r="C394" t="n">
-        <v>11.82169063598</v>
+        <v>11.8216906359802</v>
       </c>
       <c r="D394" t="n">
-        <v>7.49628895356065</v>
+        <v>7.49628895356055</v>
       </c>
       <c r="E394" t="n">
-        <v>11.490015083029</v>
+        <v>11.4900150830292</v>
       </c>
       <c r="F394" t="s">
         <v>32</v>
@@ -8367,13 +8367,13 @@
         <v>9</v>
       </c>
       <c r="C395" t="n">
-        <v>21.797678919459</v>
+        <v>21.7976789194583</v>
       </c>
       <c r="D395" t="n">
-        <v>18.9173625821633</v>
+        <v>18.9173625821621</v>
       </c>
       <c r="E395" t="n">
-        <v>21.5874144737299</v>
+        <v>21.5874144737292</v>
       </c>
       <c r="F395" t="s">
         <v>32</v>
@@ -8387,13 +8387,13 @@
         <v>10</v>
       </c>
       <c r="C396" t="n">
-        <v>1.69623148225573</v>
+        <v>1.6962314822558</v>
       </c>
       <c r="D396" t="n">
-        <v>1.86412963969322</v>
+        <v>1.86412963969346</v>
       </c>
       <c r="E396" t="n">
-        <v>1.70402280567969</v>
+        <v>1.70402280567978</v>
       </c>
       <c r="F396" t="s">
         <v>32</v>
@@ -8407,13 +8407,13 @@
         <v>11</v>
       </c>
       <c r="C397" t="n">
-        <v>0.779435571771509</v>
+        <v>0.779435571771518</v>
       </c>
       <c r="D397" t="n">
-        <v>0.0198196154310015</v>
+        <v>0.0198196154310265</v>
       </c>
       <c r="E397" t="n">
-        <v>0.773285974206587</v>
+        <v>0.773285974206597</v>
       </c>
       <c r="F397" t="s">
         <v>32</v>
@@ -8507,13 +8507,13 @@
         <v>7</v>
       </c>
       <c r="C402" t="n">
-        <v>10.0751668448029</v>
+        <v>10.0725825534005</v>
       </c>
       <c r="D402" t="n">
-        <v>9.12899351149022</v>
+        <v>9.1825666540353</v>
       </c>
       <c r="E402" t="n">
-        <v>9.99908768259349</v>
+        <v>10.0011830791532</v>
       </c>
       <c r="F402" t="s">
         <v>32</v>
@@ -8527,13 +8527,13 @@
         <v>9</v>
       </c>
       <c r="C403" t="n">
-        <v>19.2020463714912</v>
+        <v>19.1896560642307</v>
       </c>
       <c r="D403" t="n">
-        <v>18.318145275617</v>
+        <v>18.3173861929654</v>
       </c>
       <c r="E403" t="n">
-        <v>19.1315499681047</v>
+        <v>19.1201197999851</v>
       </c>
       <c r="F403" t="s">
         <v>32</v>
@@ -8547,13 +8547,13 @@
         <v>10</v>
       </c>
       <c r="C404" t="n">
-        <v>1.36682688907395</v>
+        <v>1.39112715069623</v>
       </c>
       <c r="D404" t="n">
-        <v>1.53241232523795</v>
+        <v>1.56890991617619</v>
       </c>
       <c r="E404" t="n">
-        <v>1.36543117749956</v>
+        <v>1.3903253599133</v>
       </c>
       <c r="F404" t="s">
         <v>32</v>
@@ -8567,13 +8567,13 @@
         <v>11</v>
       </c>
       <c r="C405" t="n">
-        <v>0.798599414969033</v>
+        <v>0.798569272807619</v>
       </c>
       <c r="D405" t="n">
-        <v>0.0432343666538703</v>
+        <v>0.041445430073302</v>
       </c>
       <c r="E405" t="n">
-        <v>0.788346386467097</v>
+        <v>0.788197819886782</v>
       </c>
       <c r="F405" t="s">
         <v>32</v>
@@ -8587,13 +8587,13 @@
         <v>7</v>
       </c>
       <c r="C406" t="n">
-        <v>12.3040045087802</v>
+        <v>12.3533984856777</v>
       </c>
       <c r="D406" t="n">
-        <v>13.5739211797147</v>
+        <v>13.3710177992571</v>
       </c>
       <c r="E406" t="n">
-        <v>12.4048716786142</v>
+        <v>12.4348585773616</v>
       </c>
       <c r="F406" t="s">
         <v>32</v>
@@ -8607,13 +8607,13 @@
         <v>9</v>
       </c>
       <c r="C407" t="n">
-        <v>21.6195647740518</v>
+        <v>21.5756696881643</v>
       </c>
       <c r="D407" t="n">
-        <v>25.2310896157355</v>
+        <v>24.553157776967</v>
       </c>
       <c r="E407" t="n">
-        <v>21.9232550094025</v>
+        <v>21.8239135429031</v>
       </c>
       <c r="F407" t="s">
         <v>32</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="C408" t="n">
-        <v>0.725380282139478</v>
+        <v>0.730332378138927</v>
       </c>
       <c r="D408" t="n">
-        <v>1.70316213719753</v>
+        <v>1.59765118308194</v>
       </c>
       <c r="E408" t="n">
-        <v>1.13535740767995</v>
+        <v>1.07447737767141</v>
       </c>
       <c r="F408" t="s">
         <v>32</v>
@@ -8647,13 +8647,13 @@
         <v>11</v>
       </c>
       <c r="C409" t="n">
-        <v>0.788275482839785</v>
+        <v>0.788079525429412</v>
       </c>
       <c r="D409" t="n">
-        <v>0.0258421920460791</v>
+        <v>0.0394846602827847</v>
       </c>
       <c r="E409" t="n">
-        <v>0.777246681131314</v>
+        <v>0.777982377145599</v>
       </c>
       <c r="F409" t="s">
         <v>32</v>
@@ -8667,13 +8667,13 @@
         <v>7</v>
       </c>
       <c r="C410" t="n">
-        <v>11.0594198692973</v>
+        <v>11.0594198715436</v>
       </c>
       <c r="D410" t="n">
-        <v>8.53794215127183</v>
+        <v>8.53794217171117</v>
       </c>
       <c r="E410" t="n">
-        <v>10.849956979651</v>
+        <v>10.8499569834134</v>
       </c>
       <c r="F410" t="s">
         <v>33</v>
@@ -8687,13 +8687,13 @@
         <v>9</v>
       </c>
       <c r="C411" t="n">
-        <v>28.2418298502102</v>
+        <v>28.2418298494483</v>
       </c>
       <c r="D411" t="n">
-        <v>41.6166645015247</v>
+        <v>41.6166645073467</v>
       </c>
       <c r="E411" t="n">
-        <v>29.5884040672036</v>
+        <v>29.5884040672852</v>
       </c>
       <c r="F411" t="s">
         <v>33</v>
@@ -8707,13 +8707,13 @@
         <v>10</v>
       </c>
       <c r="C412" t="n">
-        <v>0.974672524187996</v>
+        <v>0.974672522484329</v>
       </c>
       <c r="D412" t="n">
-        <v>1.94124806385782</v>
+        <v>1.94124805499939</v>
       </c>
       <c r="E412" t="n">
-        <v>0.999734997976106</v>
+        <v>0.999734996192709</v>
       </c>
       <c r="F412" t="s">
         <v>33</v>
@@ -8727,13 +8727,13 @@
         <v>11</v>
       </c>
       <c r="C413" t="n">
-        <v>0.934888551155988</v>
+        <v>0.934888551137082</v>
       </c>
       <c r="D413" t="n">
-        <v>0.789690213447116</v>
+        <v>0.78969021248204</v>
       </c>
       <c r="E413" t="n">
-        <v>0.932381119204792</v>
+        <v>0.932381119171347</v>
       </c>
       <c r="F413" t="s">
         <v>33</v>
@@ -8827,13 +8827,13 @@
         <v>7</v>
       </c>
       <c r="C418" t="n">
-        <v>9.41640725119898</v>
+        <v>9.41640724495099</v>
       </c>
       <c r="D418" t="n">
-        <v>11.8352415700605</v>
+        <v>11.8352416490051</v>
       </c>
       <c r="E418" t="n">
-        <v>9.60447414647245</v>
+        <v>9.6044741467776</v>
       </c>
       <c r="F418" t="s">
         <v>33</v>
@@ -8847,13 +8847,13 @@
         <v>9</v>
       </c>
       <c r="C419" t="n">
-        <v>24.6552888020974</v>
+        <v>24.6552888378471</v>
       </c>
       <c r="D419" t="n">
-        <v>50.964283136125</v>
+        <v>50.9642834211225</v>
       </c>
       <c r="E419" t="n">
-        <v>27.5950264657854</v>
+        <v>27.5950265358529</v>
       </c>
       <c r="F419" t="s">
         <v>33</v>
@@ -8867,13 +8867,13 @@
         <v>10</v>
       </c>
       <c r="C420" t="n">
-        <v>0.627673798950453</v>
+        <v>0.627673798267311</v>
       </c>
       <c r="D420" t="n">
-        <v>1.22137949994866</v>
+        <v>1.22137950732538</v>
       </c>
       <c r="E420" t="n">
-        <v>0.655148583445538</v>
+        <v>0.655148583516654</v>
       </c>
       <c r="F420" t="s">
         <v>33</v>
@@ -8887,13 +8887,13 @@
         <v>11</v>
       </c>
       <c r="C421" t="n">
-        <v>0.957889981904201</v>
+        <v>0.957889981855974</v>
       </c>
       <c r="D421" t="n">
-        <v>0.69038994587055</v>
+        <v>0.690389944561757</v>
       </c>
       <c r="E421" t="n">
-        <v>0.953933414158385</v>
+        <v>0.953933414056948</v>
       </c>
       <c r="F421" t="s">
         <v>33</v>
@@ -8987,13 +8987,13 @@
         <v>7</v>
       </c>
       <c r="C426" t="n">
-        <v>9.39933462056188</v>
+        <v>9.40104204763154</v>
       </c>
       <c r="D426" t="n">
-        <v>8.51376669939588</v>
+        <v>8.63523061984825</v>
       </c>
       <c r="E426" t="n">
-        <v>9.32655672110468</v>
+        <v>9.33824373802463</v>
       </c>
       <c r="F426" t="s">
         <v>33</v>
@@ -9007,13 +9007,13 @@
         <v>9</v>
       </c>
       <c r="C427" t="n">
-        <v>23.5368385387325</v>
+        <v>23.5660092702791</v>
       </c>
       <c r="D427" t="n">
-        <v>37.4238679024518</v>
+        <v>38.0964116794361</v>
       </c>
       <c r="E427" t="n">
-        <v>24.9939164236696</v>
+        <v>25.1036696567614</v>
       </c>
       <c r="F427" t="s">
         <v>33</v>
@@ -9027,13 +9027,13 @@
         <v>10</v>
       </c>
       <c r="C428" t="n">
-        <v>0.720016081919364</v>
+        <v>0.718683443063562</v>
       </c>
       <c r="D428" t="n">
-        <v>1.18891900066124</v>
+        <v>1.20226601651146</v>
       </c>
       <c r="E428" t="n">
-        <v>0.728642635048708</v>
+        <v>0.729001347369527</v>
       </c>
       <c r="F428" t="s">
         <v>33</v>
@@ -9047,13 +9047,13 @@
         <v>11</v>
       </c>
       <c r="C429" t="n">
-        <v>0.955034336010378</v>
+        <v>0.954962342822392</v>
       </c>
       <c r="D429" t="n">
-        <v>0.719557551490021</v>
+        <v>0.706500976055094</v>
       </c>
       <c r="E429" t="n">
-        <v>0.952291151072987</v>
+        <v>0.951932947416612</v>
       </c>
       <c r="F429" t="s">
         <v>33</v>
@@ -9067,13 +9067,13 @@
         <v>7</v>
       </c>
       <c r="C430" t="n">
-        <v>12.496329047644</v>
+        <v>12.2514715042012</v>
       </c>
       <c r="D430" t="n">
-        <v>7.37172572912723</v>
+        <v>7.69080529290252</v>
       </c>
       <c r="E430" t="n">
-        <v>12.1022196426228</v>
+        <v>11.9011261144766</v>
       </c>
       <c r="F430" t="s">
         <v>33</v>
@@ -9087,13 +9087,13 @@
         <v>9</v>
       </c>
       <c r="C431" t="n">
-        <v>28.0350682267018</v>
+        <v>27.4207363305394</v>
       </c>
       <c r="D431" t="n">
-        <v>31.2381709351071</v>
+        <v>33.046130920504</v>
       </c>
       <c r="E431" t="n">
-        <v>28.2942599024759</v>
+        <v>27.8959737293461</v>
       </c>
       <c r="F431" t="s">
         <v>33</v>
@@ -9107,13 +9107,13 @@
         <v>10</v>
       </c>
       <c r="C432" t="n">
-        <v>0.596778557448603</v>
+        <v>0.574223655875093</v>
       </c>
       <c r="D432" t="n">
-        <v>0.797091237446748</v>
+        <v>0.817733453023361</v>
       </c>
       <c r="E432" t="n">
-        <v>0.832726759884514</v>
+        <v>0.771474456453841</v>
       </c>
       <c r="F432" t="s">
         <v>33</v>
@@ -9127,13 +9127,13 @@
         <v>11</v>
       </c>
       <c r="C433" t="n">
-        <v>0.941123351518556</v>
+        <v>0.943686725642113</v>
       </c>
       <c r="D433" t="n">
-        <v>0.774610047938611</v>
+        <v>0.759310101926652</v>
       </c>
       <c r="E433" t="n">
-        <v>0.943534630152124</v>
+        <v>0.94534999337509</v>
       </c>
       <c r="F433" t="s">
         <v>33</v>
@@ -9147,13 +9147,13 @@
         <v>7</v>
       </c>
       <c r="C434" t="n">
-        <v>6.73739701235901</v>
+        <v>6.73739192327233</v>
       </c>
       <c r="D434" t="n">
-        <v>6.90338811134769</v>
+        <v>6.90336983993142</v>
       </c>
       <c r="E434" t="n">
-        <v>6.75131379229225</v>
+        <v>6.75130760468439</v>
       </c>
       <c r="F434" t="s">
         <v>34</v>
@@ -9167,13 +9167,13 @@
         <v>9</v>
       </c>
       <c r="C435" t="n">
-        <v>44.5737660675558</v>
+        <v>44.5737201072595</v>
       </c>
       <c r="D435" t="n">
-        <v>52.335929919178</v>
+        <v>52.3358213767794</v>
       </c>
       <c r="E435" t="n">
-        <v>45.2753464270169</v>
+        <v>45.275294508497</v>
       </c>
       <c r="F435" t="s">
         <v>34</v>
@@ -9187,13 +9187,13 @@
         <v>10</v>
       </c>
       <c r="C436" t="n">
-        <v>0.557904422242986</v>
+        <v>0.55790375392459</v>
       </c>
       <c r="D436" t="n">
-        <v>0.51979729984202</v>
+        <v>0.519794542109876</v>
       </c>
       <c r="E436" t="n">
-        <v>0.535642347226499</v>
+        <v>0.535641470803326</v>
       </c>
       <c r="F436" t="s">
         <v>34</v>
@@ -9207,13 +9207,13 @@
         <v>11</v>
       </c>
       <c r="C437" t="n">
-        <v>0.816759561440832</v>
+        <v>0.816759844900401</v>
       </c>
       <c r="D437" t="n">
-        <v>0.770406187575601</v>
+        <v>0.770407867255365</v>
       </c>
       <c r="E437" t="n">
-        <v>0.812083777499919</v>
+        <v>0.81208417780905</v>
       </c>
       <c r="F437" t="s">
         <v>34</v>
@@ -9307,13 +9307,13 @@
         <v>7</v>
       </c>
       <c r="C442" t="n">
-        <v>8.01634722828372</v>
+        <v>8.01634722836795</v>
       </c>
       <c r="D442" t="n">
-        <v>11.628849156808</v>
+        <v>11.6288491344411</v>
       </c>
       <c r="E442" t="n">
-        <v>8.29508795168157</v>
+        <v>8.29508795003881</v>
       </c>
       <c r="F442" t="s">
         <v>34</v>
@@ -9327,13 +9327,13 @@
         <v>9</v>
       </c>
       <c r="C443" t="n">
-        <v>471.363103626036</v>
+        <v>471.363103624479</v>
       </c>
       <c r="D443" t="n">
-        <v>91.8709562176752</v>
+        <v>91.8709561639424</v>
       </c>
       <c r="E443" t="n">
-        <v>453.58842769052</v>
+        <v>453.588427688187</v>
       </c>
       <c r="F443" t="s">
         <v>34</v>
@@ -9347,13 +9347,13 @@
         <v>10</v>
       </c>
       <c r="C444" t="n">
-        <v>0.468087778075467</v>
+        <v>0.468087778184026</v>
       </c>
       <c r="D444" t="n">
-        <v>0.694317984435997</v>
+        <v>0.694317981000199</v>
       </c>
       <c r="E444" t="n">
-        <v>0.471769069683102</v>
+        <v>0.471769069639827</v>
       </c>
       <c r="F444" t="s">
         <v>34</v>
@@ -9367,13 +9367,13 @@
         <v>11</v>
       </c>
       <c r="C445" t="n">
-        <v>0.0812670106251721</v>
+        <v>0.081267010602818</v>
       </c>
       <c r="D445" t="n">
-        <v>0.782872834511288</v>
+        <v>0.782872834177916</v>
       </c>
       <c r="E445" t="n">
-        <v>0.0877265202213668</v>
+        <v>0.0877265201965009</v>
       </c>
       <c r="F445" t="s">
         <v>34</v>
@@ -9467,13 +9467,13 @@
         <v>7</v>
       </c>
       <c r="C450" t="n">
-        <v>6.65986110207097</v>
+        <v>6.65793381068174</v>
       </c>
       <c r="D450" t="n">
-        <v>7.42463108734994</v>
+        <v>7.42213303581217</v>
       </c>
       <c r="E450" t="n">
-        <v>6.72452313584165</v>
+        <v>6.72254829389611</v>
       </c>
       <c r="F450" t="s">
         <v>34</v>
@@ -9487,13 +9487,13 @@
         <v>9</v>
       </c>
       <c r="C451" t="n">
-        <v>118.944319953735</v>
+        <v>118.417617483784</v>
       </c>
       <c r="D451" t="n">
-        <v>57.8171265343896</v>
+        <v>57.5305298863959</v>
       </c>
       <c r="E451" t="n">
-        <v>115.099921252011</v>
+        <v>114.588976012403</v>
       </c>
       <c r="F451" t="s">
         <v>34</v>
@@ -9507,13 +9507,13 @@
         <v>10</v>
       </c>
       <c r="C452" t="n">
-        <v>0.514830261213192</v>
+        <v>0.513906299644305</v>
       </c>
       <c r="D452" t="n">
-        <v>0.5589732218859</v>
+        <v>0.557828252494828</v>
       </c>
       <c r="E452" t="n">
-        <v>0.503039807435931</v>
+        <v>0.502278557555325</v>
       </c>
       <c r="F452" t="s">
         <v>34</v>
@@ -9527,13 +9527,13 @@
         <v>11</v>
       </c>
       <c r="C453" t="n">
-        <v>0.396331936654001</v>
+        <v>0.400860604250055</v>
       </c>
       <c r="D453" t="n">
-        <v>0.835316431336216</v>
+        <v>0.835007912538983</v>
       </c>
       <c r="E453" t="n">
-        <v>0.424775742816375</v>
+        <v>0.428797933220428</v>
       </c>
       <c r="F453" t="s">
         <v>34</v>
@@ -9547,13 +9547,13 @@
         <v>7</v>
       </c>
       <c r="C454" t="n">
-        <v>8.0169547940508</v>
+        <v>8.04404168402614</v>
       </c>
       <c r="D454" t="n">
-        <v>6.66695522156492</v>
+        <v>7.05591225255069</v>
       </c>
       <c r="E454" t="n">
-        <v>7.9137777012541</v>
+        <v>7.96889427114862</v>
       </c>
       <c r="F454" t="s">
         <v>34</v>
@@ -9567,13 +9567,13 @@
         <v>9</v>
       </c>
       <c r="C455" t="n">
-        <v>53.4145529821825</v>
+        <v>52.8597094046276</v>
       </c>
       <c r="D455" t="n">
-        <v>57.3259259755593</v>
+        <v>58.6944704222602</v>
       </c>
       <c r="E455" t="n">
-        <v>53.7306806095356</v>
+        <v>53.3365068361092</v>
       </c>
       <c r="F455" t="s">
         <v>34</v>
@@ -9587,13 +9587,13 @@
         <v>10</v>
       </c>
       <c r="C456" t="n">
-        <v>0.48691435171133</v>
+        <v>0.485883400227184</v>
       </c>
       <c r="D456" t="n">
-        <v>0.531102095189403</v>
+        <v>0.539052241100236</v>
       </c>
       <c r="E456" t="n">
-        <v>0.643051780106331</v>
+        <v>0.61706187976227</v>
       </c>
       <c r="F456" t="s">
         <v>34</v>
@@ -9607,13 +9607,13 @@
         <v>11</v>
       </c>
       <c r="C457" t="n">
-        <v>0.761620948679172</v>
+        <v>0.765949176099863</v>
       </c>
       <c r="D457" t="n">
-        <v>0.797886054586872</v>
+        <v>0.788163026441996</v>
       </c>
       <c r="E457" t="n">
-        <v>0.763141945603716</v>
+        <v>0.767298487918993</v>
       </c>
       <c r="F457" t="s">
         <v>34</v>
@@ -9627,13 +9627,13 @@
         <v>7</v>
       </c>
       <c r="C458" t="n">
-        <v>18.1430978537374</v>
+        <v>18.1430379852629</v>
       </c>
       <c r="D458" t="n">
-        <v>52.9279716208306</v>
+        <v>52.9286227826168</v>
       </c>
       <c r="E458" t="n">
-        <v>21.0428630497567</v>
+        <v>21.0428624323547</v>
       </c>
       <c r="F458" t="s">
         <v>35</v>
@@ -9647,13 +9647,13 @@
         <v>9</v>
       </c>
       <c r="C459" t="n">
-        <v>53.5022207475393</v>
+        <v>53.5020485627101</v>
       </c>
       <c r="D459" t="n">
-        <v>667.638256154627</v>
+        <v>667.645982209867</v>
       </c>
       <c r="E459" t="n">
-        <v>199.446524703043</v>
+        <v>199.448637926963</v>
       </c>
       <c r="F459" t="s">
         <v>35</v>
@@ -9667,13 +9667,13 @@
         <v>10</v>
       </c>
       <c r="C460" t="n">
-        <v>1.12502647032741</v>
+        <v>1.12501466182361</v>
       </c>
       <c r="D460" t="n">
-        <v>1.5048526120055</v>
+        <v>1.50486715972902</v>
       </c>
       <c r="E460" t="n">
-        <v>1.21354283137349</v>
+        <v>1.21354225026015</v>
       </c>
       <c r="F460" t="s">
         <v>35</v>
@@ -9687,13 +9687,13 @@
         <v>11</v>
       </c>
       <c r="C461" t="n">
-        <v>0.884788263345703</v>
+        <v>0.884788979717534</v>
       </c>
       <c r="D461" t="n">
-        <v>0.460139751544687</v>
+        <v>0.46013687630265</v>
       </c>
       <c r="E461" t="n">
-        <v>0.774222359907354</v>
+        <v>0.774222560887119</v>
       </c>
       <c r="F461" t="s">
         <v>35</v>
@@ -9787,13 +9787,13 @@
         <v>7</v>
       </c>
       <c r="C466" t="n">
-        <v>15.9148713279418</v>
+        <v>15.9148713276819</v>
       </c>
       <c r="D466" t="n">
-        <v>5.48181431510491</v>
+        <v>5.48181431914167</v>
       </c>
       <c r="E466" t="n">
-        <v>15.1116388836963</v>
+        <v>15.1116388837669</v>
       </c>
       <c r="F466" t="s">
         <v>35</v>
@@ -9807,13 +9807,13 @@
         <v>9</v>
       </c>
       <c r="C467" t="n">
-        <v>49.6210217841136</v>
+        <v>49.6210217848437</v>
       </c>
       <c r="D467" t="n">
-        <v>57.6670520607665</v>
+        <v>57.6670520870205</v>
       </c>
       <c r="E467" t="n">
-        <v>50.2799570981198</v>
+        <v>50.2799571010946</v>
       </c>
       <c r="F467" t="s">
         <v>35</v>
@@ -9827,13 +9827,13 @@
         <v>10</v>
       </c>
       <c r="C468" t="n">
-        <v>0.952533733885335</v>
+        <v>0.952533733802507</v>
       </c>
       <c r="D468" t="n">
-        <v>0.694420828593157</v>
+        <v>0.694420829060511</v>
       </c>
       <c r="E468" t="n">
-        <v>0.88734762252949</v>
+        <v>0.887347622518784</v>
       </c>
       <c r="F468" t="s">
         <v>35</v>
@@ -9847,13 +9847,13 @@
         <v>11</v>
       </c>
       <c r="C469" t="n">
-        <v>0.901912609943775</v>
+        <v>0.901912609943267</v>
       </c>
       <c r="D469" t="n">
-        <v>0.716418556667839</v>
+        <v>0.716418556692948</v>
       </c>
       <c r="E469" t="n">
-        <v>0.942448348800662</v>
+        <v>0.942448348800032</v>
       </c>
       <c r="F469" t="s">
         <v>35</v>
@@ -9947,13 +9947,13 @@
         <v>7</v>
       </c>
       <c r="C474" t="n">
-        <v>14.7495054157065</v>
+        <v>15.0020932336929</v>
       </c>
       <c r="D474" t="n">
-        <v>12.451066504057</v>
+        <v>21.3080775948563</v>
       </c>
       <c r="E474" t="n">
-        <v>14.5587076942718</v>
+        <v>15.5285054554893</v>
       </c>
       <c r="F474" t="s">
         <v>35</v>
@@ -9967,13 +9967,13 @@
         <v>9</v>
       </c>
       <c r="C475" t="n">
-        <v>47.134044511699</v>
+        <v>46.8173420654089</v>
       </c>
       <c r="D475" t="n">
-        <v>142.066902353302</v>
+        <v>256.271394847335</v>
       </c>
       <c r="E475" t="n">
-        <v>60.9929550238722</v>
+        <v>86.5182049594584</v>
       </c>
       <c r="F475" t="s">
         <v>35</v>
@@ -9987,13 +9987,13 @@
         <v>10</v>
       </c>
       <c r="C476" t="n">
-        <v>1.00289224626026</v>
+        <v>1.03156894035952</v>
       </c>
       <c r="D476" t="n">
-        <v>0.786376638574969</v>
+        <v>0.755506624468554</v>
       </c>
       <c r="E476" t="n">
-        <v>0.895635352404437</v>
+        <v>0.865838788062979</v>
       </c>
       <c r="F476" t="s">
         <v>35</v>
@@ -10007,13 +10007,13 @@
         <v>11</v>
       </c>
       <c r="C477" t="n">
-        <v>0.912721829690778</v>
+        <v>0.913698105516565</v>
       </c>
       <c r="D477" t="n">
-        <v>0.497248730022642</v>
+        <v>0.528746983568798</v>
       </c>
       <c r="E477" t="n">
-        <v>0.924653767002624</v>
+        <v>0.888772107029482</v>
       </c>
       <c r="F477" t="s">
         <v>35</v>
@@ -10027,13 +10027,13 @@
         <v>7</v>
       </c>
       <c r="C478" t="n">
-        <v>18.740512981728</v>
+        <v>18.8332116412248</v>
       </c>
       <c r="D478" t="n">
-        <v>13.3597056800398</v>
+        <v>13.1069867710791</v>
       </c>
       <c r="E478" t="n">
-        <v>18.3255843281372</v>
+        <v>18.3917122807549</v>
       </c>
       <c r="F478" t="s">
         <v>35</v>
@@ -10047,13 +10047,13 @@
         <v>9</v>
       </c>
       <c r="C479" t="n">
-        <v>52.5599986180465</v>
+        <v>52.694909119305</v>
       </c>
       <c r="D479" t="n">
-        <v>108.54182746508</v>
+        <v>107.419964538279</v>
       </c>
       <c r="E479" t="n">
-        <v>58.7777126120617</v>
+        <v>58.7308835562971</v>
       </c>
       <c r="F479" t="s">
         <v>35</v>
@@ -10067,13 +10067,13 @@
         <v>10</v>
       </c>
       <c r="C480" t="n">
-        <v>0.772826554625869</v>
+        <v>0.776878003388264</v>
       </c>
       <c r="D480" t="n">
-        <v>1.60341311274443</v>
+        <v>1.59001969034055</v>
       </c>
       <c r="E480" t="n">
-        <v>0.966697957638855</v>
+        <v>0.976980289301362</v>
       </c>
       <c r="F480" t="s">
         <v>35</v>
@@ -10087,13 +10087,13 @@
         <v>11</v>
       </c>
       <c r="C481" t="n">
-        <v>0.886657063784344</v>
+        <v>0.886192417514817</v>
       </c>
       <c r="D481" t="n">
-        <v>0.631343915015183</v>
+        <v>0.612135425277727</v>
       </c>
       <c r="E481" t="n">
-        <v>0.920734271903727</v>
+        <v>0.92038634085185</v>
       </c>
       <c r="F481" t="s">
         <v>35</v>
@@ -10107,13 +10107,13 @@
         <v>7</v>
       </c>
       <c r="C482" t="n">
-        <v>6.69253735046123</v>
+        <v>6.6925484154805</v>
       </c>
       <c r="D482" t="n">
-        <v>5.45709620283293</v>
+        <v>5.45747180824796</v>
       </c>
       <c r="E482" t="n">
-        <v>6.59016973027344</v>
+        <v>6.59021117345257</v>
       </c>
       <c r="F482" t="s">
         <v>36</v>
@@ -10127,13 +10127,13 @@
         <v>9</v>
       </c>
       <c r="C483" t="n">
-        <v>54.4716661507205</v>
+        <v>54.4716167335129</v>
       </c>
       <c r="D483" t="n">
-        <v>53.4458803094789</v>
+        <v>53.4477475394771</v>
       </c>
       <c r="E483" t="n">
-        <v>54.3898207282561</v>
+        <v>54.3899291566168</v>
       </c>
       <c r="F483" t="s">
         <v>36</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="C484" t="n">
-        <v>1.11466179472909</v>
+        <v>1.11467747684012</v>
       </c>
       <c r="D484" t="n">
-        <v>2.77851671464062</v>
+        <v>2.77859904512676</v>
       </c>
       <c r="E484" t="n">
-        <v>1.15125443693943</v>
+        <v>1.15127335901683</v>
       </c>
       <c r="F484" t="s">
         <v>36</v>
@@ -10167,13 +10167,13 @@
         <v>11</v>
       </c>
       <c r="C485" t="n">
-        <v>0.825402828535913</v>
+        <v>0.825403079055558</v>
       </c>
       <c r="D485" t="n">
-        <v>0.595549729696771</v>
+        <v>0.595557221768996</v>
       </c>
       <c r="E485" t="n">
-        <v>0.827882715680108</v>
+        <v>0.827882203448038</v>
       </c>
       <c r="F485" t="s">
         <v>36</v>
@@ -10267,13 +10267,13 @@
         <v>7</v>
       </c>
       <c r="C490" t="n">
-        <v>5.59362140500042</v>
+        <v>5.59362089173604</v>
       </c>
       <c r="D490" t="n">
-        <v>9.85478530875562</v>
+        <v>9.854786411583</v>
       </c>
       <c r="E490" t="n">
-        <v>5.92223240100846</v>
+        <v>5.92223201205882</v>
       </c>
       <c r="F490" t="s">
         <v>36</v>
@@ -10287,13 +10287,13 @@
         <v>9</v>
       </c>
       <c r="C491" t="n">
-        <v>48.5199019157424</v>
+        <v>48.5198995209843</v>
       </c>
       <c r="D491" t="n">
-        <v>94.3344847037298</v>
+        <v>94.3344880566566</v>
       </c>
       <c r="E491" t="n">
-        <v>53.4681636777953</v>
+        <v>53.4681621268685</v>
       </c>
       <c r="F491" t="s">
         <v>36</v>
@@ -10307,13 +10307,13 @@
         <v>10</v>
       </c>
       <c r="C492" t="n">
-        <v>0.535548305890298</v>
+        <v>0.535548291207383</v>
       </c>
       <c r="D492" t="n">
-        <v>1.62790927884344</v>
+        <v>1.6279088147951</v>
       </c>
       <c r="E492" t="n">
-        <v>0.586594357641181</v>
+        <v>0.586594349321047</v>
       </c>
       <c r="F492" t="s">
         <v>36</v>
@@ -10327,13 +10327,13 @@
         <v>11</v>
       </c>
       <c r="C493" t="n">
-        <v>0.879439376656934</v>
+        <v>0.879439378704955</v>
       </c>
       <c r="D493" t="n">
-        <v>0.499072863767981</v>
+        <v>0.499072712174766</v>
       </c>
       <c r="E493" t="n">
-        <v>0.867211458029957</v>
+        <v>0.867211438988973</v>
       </c>
       <c r="F493" t="s">
         <v>36</v>
@@ -10427,13 +10427,13 @@
         <v>7</v>
       </c>
       <c r="C498" t="n">
-        <v>5.30773341077596</v>
+        <v>5.31583169993738</v>
       </c>
       <c r="D498" t="n">
-        <v>8.03689575423385</v>
+        <v>7.99480032604361</v>
       </c>
       <c r="E498" t="n">
-        <v>5.53606297154063</v>
+        <v>5.53997847678697</v>
       </c>
       <c r="F498" t="s">
         <v>36</v>
@@ -10447,13 +10447,13 @@
         <v>9</v>
       </c>
       <c r="C499" t="n">
-        <v>43.9912903643519</v>
+        <v>44.0029452196578</v>
       </c>
       <c r="D499" t="n">
-        <v>75.7767958900508</v>
+        <v>75.3408727233827</v>
       </c>
       <c r="E499" t="n">
-        <v>47.4708377958144</v>
+        <v>47.4228075298436</v>
       </c>
       <c r="F499" t="s">
         <v>36</v>
@@ -10467,13 +10467,13 @@
         <v>10</v>
       </c>
       <c r="C500" t="n">
-        <v>0.676689273589917</v>
+        <v>0.677655052281761</v>
       </c>
       <c r="D500" t="n">
-        <v>1.71679102192338</v>
+        <v>1.71315978244016</v>
       </c>
       <c r="E500" t="n">
-        <v>0.722950872324575</v>
+        <v>0.723529849762152</v>
       </c>
       <c r="F500" t="s">
         <v>36</v>
@@ -10487,13 +10487,13 @@
         <v>11</v>
       </c>
       <c r="C501" t="n">
-        <v>0.886621377206496</v>
+        <v>0.886553461736524</v>
       </c>
       <c r="D501" t="n">
-        <v>0.5521822205241</v>
+        <v>0.552881966827015</v>
       </c>
       <c r="E501" t="n">
-        <v>0.872526582739746</v>
+        <v>0.872565295868823</v>
       </c>
       <c r="F501" t="s">
         <v>36</v>
@@ -10507,13 +10507,13 @@
         <v>7</v>
       </c>
       <c r="C502" t="n">
-        <v>6.64536650165447</v>
+        <v>6.63439437358872</v>
       </c>
       <c r="D502" t="n">
-        <v>8.46238384448468</v>
+        <v>7.70609713150372</v>
       </c>
       <c r="E502" t="n">
-        <v>6.78596685158442</v>
+        <v>6.71766322406945</v>
       </c>
       <c r="F502" t="s">
         <v>36</v>
@@ -10527,13 +10527,13 @@
         <v>9</v>
       </c>
       <c r="C503" t="n">
-        <v>51.5755672723398</v>
+        <v>51.7639298645994</v>
       </c>
       <c r="D503" t="n">
-        <v>82.1407844550342</v>
+        <v>76.8884386836271</v>
       </c>
       <c r="E503" t="n">
-        <v>54.547772908948</v>
+        <v>54.1202324376587</v>
       </c>
       <c r="F503" t="s">
         <v>36</v>
@@ -10547,13 +10547,13 @@
         <v>10</v>
       </c>
       <c r="C504" t="n">
-        <v>0.614114009629613</v>
+        <v>0.612908746067779</v>
       </c>
       <c r="D504" t="n">
-        <v>2.05042639991059</v>
+        <v>1.6406201305508</v>
       </c>
       <c r="E504" t="n">
-        <v>0.773766039920173</v>
+        <v>0.747321450305816</v>
       </c>
       <c r="F504" t="s">
         <v>36</v>
@@ -10567,13 +10567,13 @@
         <v>11</v>
       </c>
       <c r="C505" t="n">
-        <v>0.862158983054282</v>
+        <v>0.862401333924762</v>
       </c>
       <c r="D505" t="n">
-        <v>0.524695650320036</v>
+        <v>0.434111057444901</v>
       </c>
       <c r="E505" t="n">
-        <v>0.857445754672386</v>
+        <v>0.859174876497563</v>
       </c>
       <c r="F505" t="s">
         <v>36</v>
@@ -10587,13 +10587,13 @@
         <v>7</v>
       </c>
       <c r="C506" t="n">
-        <v>2.04763997851512</v>
+        <v>2.04763997850641</v>
       </c>
       <c r="D506" t="n">
-        <v>90.609283800347</v>
+        <v>90.609283799521</v>
       </c>
       <c r="E506" t="n">
-        <v>10.0055449012187</v>
+        <v>10.0055449011412</v>
       </c>
       <c r="F506" t="s">
         <v>37</v>
@@ -10607,13 +10607,13 @@
         <v>9</v>
       </c>
       <c r="C507" t="n">
-        <v>0.164642207034186</v>
+        <v>0.164642207015377</v>
       </c>
       <c r="D507" t="n">
-        <v>4.79707488932621</v>
+        <v>4.7970748893266</v>
       </c>
       <c r="E507" t="n">
-        <v>1.41145381656539</v>
+        <v>1.41145381656323</v>
       </c>
       <c r="F507" t="s">
         <v>37</v>
@@ -10627,13 +10627,13 @@
         <v>10</v>
       </c>
       <c r="C508" t="n">
-        <v>0.0112675636164907</v>
+        <v>0.0112675636155174</v>
       </c>
       <c r="D508" t="n">
-        <v>4.08143890541046</v>
+        <v>4.08143890540322</v>
       </c>
       <c r="E508" t="n">
-        <v>0.0622139067225804</v>
+        <v>0.0622139067208569</v>
       </c>
       <c r="F508" t="s">
         <v>37</v>
@@ -10647,13 +10647,13 @@
         <v>11</v>
       </c>
       <c r="C509" t="n">
-        <v>0.999882363462281</v>
+        <v>0.999882363462289</v>
       </c>
       <c r="D509" t="n">
-        <v>0.0813416447941927</v>
+        <v>0.0813416447921703</v>
       </c>
       <c r="E509" t="n">
-        <v>0.99077798750367</v>
+        <v>0.990777987503721</v>
       </c>
       <c r="F509" t="s">
         <v>37</v>
@@ -10747,10 +10747,10 @@
         <v>7</v>
       </c>
       <c r="C514" t="n">
-        <v>47.6492950186812</v>
+        <v>47.6492950186814</v>
       </c>
       <c r="D514" t="n">
-        <v>74.573474396916</v>
+        <v>74.5734743969133</v>
       </c>
       <c r="E514" t="n">
         <v>49.9012493945024</v>
@@ -10767,13 +10767,13 @@
         <v>9</v>
       </c>
       <c r="C515" t="n">
-        <v>9.90474291040325</v>
+        <v>9.90474291040675</v>
       </c>
       <c r="D515" t="n">
-        <v>3.70896485137312</v>
+        <v>3.70896485137332</v>
       </c>
       <c r="E515" t="n">
-        <v>9.57137364162726</v>
+        <v>9.57137364163061</v>
       </c>
       <c r="F515" t="s">
         <v>37</v>
@@ -10787,13 +10787,13 @@
         <v>10</v>
       </c>
       <c r="C516" t="n">
-        <v>2.63610115422424</v>
+        <v>2.63610115422973</v>
       </c>
       <c r="D516" t="n">
-        <v>3.53851182829713</v>
+        <v>3.53851182830123</v>
       </c>
       <c r="E516" t="n">
-        <v>2.6599834776239</v>
+        <v>2.65998347762934</v>
       </c>
       <c r="F516" t="s">
         <v>37</v>
@@ -10807,13 +10807,13 @@
         <v>11</v>
       </c>
       <c r="C517" t="n">
-        <v>0.642916986519008</v>
+        <v>0.642916986518757</v>
       </c>
       <c r="D517" t="n">
-        <v>0.273574774474389</v>
+        <v>0.27357477447454</v>
       </c>
       <c r="E517" t="n">
-        <v>0.65294783531011</v>
+        <v>0.652947835309869</v>
       </c>
       <c r="F517" t="s">
         <v>37</v>
@@ -10907,13 +10907,13 @@
         <v>7</v>
       </c>
       <c r="C522" t="n">
-        <v>35.3599616256327</v>
+        <v>36.3324143275882</v>
       </c>
       <c r="D522" t="n">
-        <v>69.5909506424198</v>
+        <v>68.9370712211884</v>
       </c>
       <c r="E522" t="n">
-        <v>38.5856352603075</v>
+        <v>39.4160786212883</v>
       </c>
       <c r="F522" t="s">
         <v>37</v>
@@ -10927,13 +10927,13 @@
         <v>9</v>
       </c>
       <c r="C523" t="n">
-        <v>5.44146067852885</v>
+        <v>5.61849791934308</v>
       </c>
       <c r="D523" t="n">
-        <v>3.28998562885113</v>
+        <v>3.20965444051365</v>
       </c>
       <c r="E523" t="n">
-        <v>5.28897240675285</v>
+        <v>5.45138500669084</v>
       </c>
       <c r="F523" t="s">
         <v>37</v>
@@ -10947,13 +10947,13 @@
         <v>10</v>
       </c>
       <c r="C524" t="n">
-        <v>1.00544863473287</v>
+        <v>1.0487624675961</v>
       </c>
       <c r="D524" t="n">
-        <v>2.8820917268303</v>
+        <v>2.79683878290172</v>
       </c>
       <c r="E524" t="n">
-        <v>1.0485916271057</v>
+        <v>1.08848544194491</v>
       </c>
       <c r="F524" t="s">
         <v>37</v>
@@ -10967,13 +10967,13 @@
         <v>11</v>
       </c>
       <c r="C525" t="n">
-        <v>0.875369523877874</v>
+        <v>0.86622060651835</v>
       </c>
       <c r="D525" t="n">
-        <v>0.49850808138686</v>
+        <v>0.521610681003605</v>
       </c>
       <c r="E525" t="n">
-        <v>0.875548770254611</v>
+        <v>0.867020770348466</v>
       </c>
       <c r="F525" t="s">
         <v>37</v>
@@ -10987,13 +10987,13 @@
         <v>7</v>
       </c>
       <c r="C526" t="n">
-        <v>86.1456904712024</v>
+        <v>80.7202916853322</v>
       </c>
       <c r="D526" t="n">
-        <v>64.0199224138542</v>
+        <v>77.6698425358443</v>
       </c>
       <c r="E526" t="n">
-        <v>84.6650295869857</v>
+        <v>80.5627843456437</v>
       </c>
       <c r="F526" t="s">
         <v>37</v>
@@ -11007,13 +11007,13 @@
         <v>9</v>
       </c>
       <c r="C527" t="n">
-        <v>12.6079001070868</v>
+        <v>12.1926190974704</v>
       </c>
       <c r="D527" t="n">
-        <v>3.07613665802376</v>
+        <v>2.48058909832946</v>
       </c>
       <c r="E527" t="n">
-        <v>12.1442924916246</v>
+        <v>11.7341245501613</v>
       </c>
       <c r="F527" t="s">
         <v>37</v>
@@ -11027,13 +11027,13 @@
         <v>10</v>
       </c>
       <c r="C528" t="n">
-        <v>1.11720746310809</v>
+        <v>1.04069033041274</v>
       </c>
       <c r="D528" t="n">
-        <v>1.52584748411479</v>
+        <v>1.0527375947794</v>
       </c>
       <c r="E528" t="n">
-        <v>1.09654829578113</v>
+        <v>0.951201376934995</v>
       </c>
       <c r="F528" t="s">
         <v>37</v>
@@ -11047,13 +11047,13 @@
         <v>11</v>
       </c>
       <c r="C529" t="n">
-        <v>0.547845993226737</v>
+        <v>0.567958456957153</v>
       </c>
       <c r="D529" t="n">
-        <v>0.567893257350679</v>
+        <v>0.644073375441448</v>
       </c>
       <c r="E529" t="n">
-        <v>0.55585082386705</v>
+        <v>0.579827224702429</v>
       </c>
       <c r="F529" t="s">
         <v>37</v>
@@ -11067,13 +11067,13 @@
         <v>7</v>
       </c>
       <c r="C530" t="n">
-        <v>28.7362139287259</v>
+        <v>28.7362137857757</v>
       </c>
       <c r="D530" t="n">
-        <v>39.9168679002423</v>
+        <v>39.9168664562275</v>
       </c>
       <c r="E530" t="n">
-        <v>29.6711291114602</v>
+        <v>29.6711288591976</v>
       </c>
       <c r="F530" t="s">
         <v>38</v>
@@ -11087,13 +11087,13 @@
         <v>9</v>
       </c>
       <c r="C531" t="n">
-        <v>12.1117681164916</v>
+        <v>12.1117680304947</v>
       </c>
       <c r="D531" t="n">
-        <v>11.8629341096903</v>
+        <v>11.8629337856686</v>
       </c>
       <c r="E531" t="n">
-        <v>12.0875771635678</v>
+        <v>12.0875770589209</v>
       </c>
       <c r="F531" t="s">
         <v>38</v>
@@ -11107,13 +11107,13 @@
         <v>10</v>
       </c>
       <c r="C532" t="n">
-        <v>1.99859058864489</v>
+        <v>1.99859057942888</v>
       </c>
       <c r="D532" t="n">
-        <v>24.4241318934512</v>
+        <v>24.4241361409667</v>
       </c>
       <c r="E532" t="n">
-        <v>2.14938917439927</v>
+        <v>2.14938916166005</v>
       </c>
       <c r="F532" t="s">
         <v>38</v>
@@ -11127,13 +11127,13 @@
         <v>11</v>
       </c>
       <c r="C533" t="n">
-        <v>0.824796087352349</v>
+        <v>0.824796089392379</v>
       </c>
       <c r="D533" t="n">
-        <v>0.687252581658066</v>
+        <v>0.687252597436509</v>
       </c>
       <c r="E533" t="n">
-        <v>0.817828532479746</v>
+        <v>0.817828534568251</v>
       </c>
       <c r="F533" t="s">
         <v>38</v>
@@ -11227,13 +11227,13 @@
         <v>7</v>
       </c>
       <c r="C538" t="n">
-        <v>29.9119768998057</v>
+        <v>29.9119768998058</v>
       </c>
       <c r="D538" t="n">
-        <v>33.2467639763547</v>
+        <v>33.2467639763574</v>
       </c>
       <c r="E538" t="n">
-        <v>30.1911211601964</v>
+        <v>30.1911211601968</v>
       </c>
       <c r="F538" t="s">
         <v>38</v>
@@ -11247,13 +11247,13 @@
         <v>9</v>
       </c>
       <c r="C539" t="n">
-        <v>12.624719308969</v>
+        <v>12.6247193089681</v>
       </c>
       <c r="D539" t="n">
-        <v>10.0328389351745</v>
+        <v>10.0328389351728</v>
       </c>
       <c r="E539" t="n">
-        <v>12.4438537995249</v>
+        <v>12.4438537995239</v>
       </c>
       <c r="F539" t="s">
         <v>38</v>
@@ -11267,13 +11267,13 @@
         <v>10</v>
       </c>
       <c r="C540" t="n">
-        <v>1.97940269370221</v>
+        <v>1.97940269370162</v>
       </c>
       <c r="D540" t="n">
-        <v>4.03503468867236</v>
+        <v>4.03503468866821</v>
       </c>
       <c r="E540" t="n">
-        <v>2.01443961230515</v>
+        <v>2.01443961230449</v>
       </c>
       <c r="F540" t="s">
         <v>38</v>
@@ -11287,13 +11287,13 @@
         <v>11</v>
       </c>
       <c r="C541" t="n">
-        <v>0.819459448420084</v>
+        <v>0.81945944842011</v>
       </c>
       <c r="D541" t="n">
-        <v>0.582608509160534</v>
+        <v>0.582608509160554</v>
       </c>
       <c r="E541" t="n">
-        <v>0.81776863634587</v>
+        <v>0.817768636345898</v>
       </c>
       <c r="F541" t="s">
         <v>38</v>
@@ -11387,13 +11387,13 @@
         <v>7</v>
       </c>
       <c r="C546" t="n">
-        <v>28.09218222766</v>
+        <v>28.1157702258784</v>
       </c>
       <c r="D546" t="n">
-        <v>32.2242529076909</v>
+        <v>32.293199107089</v>
       </c>
       <c r="E546" t="n">
-        <v>28.4455458783152</v>
+        <v>28.4729476414793</v>
       </c>
       <c r="F546" t="s">
         <v>38</v>
@@ -11407,13 +11407,13 @@
         <v>9</v>
       </c>
       <c r="C547" t="n">
-        <v>10.8142636596302</v>
+        <v>10.7965896272685</v>
       </c>
       <c r="D547" t="n">
-        <v>9.53870539753244</v>
+        <v>9.55401378312554</v>
       </c>
       <c r="E547" t="n">
-        <v>10.7125957816296</v>
+        <v>10.6973225715757</v>
       </c>
       <c r="F547" t="s">
         <v>38</v>
@@ -11427,13 +11427,13 @@
         <v>10</v>
       </c>
       <c r="C548" t="n">
-        <v>1.6694608862566</v>
+        <v>1.65209977705584</v>
       </c>
       <c r="D548" t="n">
-        <v>4.86322183100034</v>
+        <v>4.85974007815058</v>
       </c>
       <c r="E548" t="n">
-        <v>1.71829375247821</v>
+        <v>1.70180079978472</v>
       </c>
       <c r="F548" t="s">
         <v>38</v>
@@ -11447,13 +11447,13 @@
         <v>11</v>
       </c>
       <c r="C549" t="n">
-        <v>0.858299024779638</v>
+        <v>0.858754443179761</v>
       </c>
       <c r="D549" t="n">
-        <v>0.694421086720255</v>
+        <v>0.695466273872854</v>
       </c>
       <c r="E549" t="n">
-        <v>0.854180627295563</v>
+        <v>0.854593461179398</v>
       </c>
       <c r="F549" t="s">
         <v>38</v>
@@ -11467,13 +11467,13 @@
         <v>7</v>
       </c>
       <c r="C550" t="n">
-        <v>47.4122568411693</v>
+        <v>47.0364549761483</v>
       </c>
       <c r="D550" t="n">
-        <v>38.7476259428656</v>
+        <v>30.8831204670349</v>
       </c>
       <c r="E550" t="n">
-        <v>46.7871992293313</v>
+        <v>45.8369950833146</v>
       </c>
       <c r="F550" t="s">
         <v>38</v>
@@ -11487,13 +11487,13 @@
         <v>9</v>
       </c>
       <c r="C551" t="n">
-        <v>13.7587628832038</v>
+        <v>13.5656450928533</v>
       </c>
       <c r="D551" t="n">
-        <v>8.82890799192645</v>
+        <v>7.78331667668001</v>
       </c>
       <c r="E551" t="n">
-        <v>13.4464130267622</v>
+        <v>13.2120507351786</v>
       </c>
       <c r="F551" t="s">
         <v>38</v>
@@ -11507,13 +11507,13 @@
         <v>10</v>
       </c>
       <c r="C552" t="n">
-        <v>0.973267440133469</v>
+        <v>0.948762377606738</v>
       </c>
       <c r="D552" t="n">
-        <v>2.60787009236322</v>
+        <v>2.77053654949474</v>
       </c>
       <c r="E552" t="n">
-        <v>1.09381417024917</v>
+        <v>1.06949362538777</v>
       </c>
       <c r="F552" t="s">
         <v>38</v>
@@ -11527,13 +11527,13 @@
         <v>11</v>
       </c>
       <c r="C553" t="n">
-        <v>0.799241742824679</v>
+        <v>0.80474930262643</v>
       </c>
       <c r="D553" t="n">
-        <v>0.719080312591129</v>
+        <v>0.84900935075844</v>
       </c>
       <c r="E553" t="n">
-        <v>0.79774533901014</v>
+        <v>0.805326993050619</v>
       </c>
       <c r="F553" t="s">
         <v>38</v>
@@ -11547,13 +11547,13 @@
         <v>7</v>
       </c>
       <c r="C554" t="n">
-        <v>24.3873645019489</v>
+        <v>24.3873644823019</v>
       </c>
       <c r="D554" t="n">
-        <v>25.8728917723007</v>
+        <v>25.8728926340662</v>
       </c>
       <c r="E554" t="n">
-        <v>24.5138246310633</v>
+        <v>24.5138246848456</v>
       </c>
       <c r="F554" t="s">
         <v>39</v>
@@ -11567,13 +11567,13 @@
         <v>9</v>
       </c>
       <c r="C555" t="n">
-        <v>40.4655196651536</v>
+        <v>40.4655192757807</v>
       </c>
       <c r="D555" t="n">
-        <v>60.8125170359712</v>
+        <v>60.812519684313</v>
       </c>
       <c r="E555" t="n">
-        <v>42.5386085371396</v>
+        <v>42.538608514443</v>
       </c>
       <c r="F555" t="s">
         <v>39</v>
@@ -11587,13 +11587,13 @@
         <v>10</v>
       </c>
       <c r="C556" t="n">
-        <v>1.04488865489291</v>
+        <v>1.04488862656118</v>
       </c>
       <c r="D556" t="n">
-        <v>2.11042720228084</v>
+        <v>2.11042709777904</v>
       </c>
       <c r="E556" t="n">
-        <v>1.12339281264691</v>
+        <v>1.12339278343862</v>
       </c>
       <c r="F556" t="s">
         <v>39</v>
@@ -11607,13 +11607,13 @@
         <v>11</v>
       </c>
       <c r="C557" t="n">
-        <v>0.778977225588441</v>
+        <v>0.778977226246044</v>
       </c>
       <c r="D557" t="n">
-        <v>0.276985523923227</v>
+        <v>0.276985515130682</v>
       </c>
       <c r="E557" t="n">
-        <v>0.755402550703185</v>
+        <v>0.755402548396587</v>
       </c>
       <c r="F557" t="s">
         <v>39</v>
@@ -11707,13 +11707,13 @@
         <v>7</v>
       </c>
       <c r="C562" t="n">
-        <v>25.4880239842476</v>
+        <v>25.4880239842477</v>
       </c>
       <c r="D562" t="n">
-        <v>32.0060283128429</v>
+        <v>32.0060283128497</v>
       </c>
       <c r="E562" t="n">
-        <v>25.9932073766004</v>
+        <v>25.993207376601</v>
       </c>
       <c r="F562" t="s">
         <v>39</v>
@@ -11727,13 +11727,13 @@
         <v>9</v>
       </c>
       <c r="C563" t="n">
-        <v>38.512059625372</v>
+        <v>38.5120596253734</v>
       </c>
       <c r="D563" t="n">
-        <v>80.1508906422142</v>
+        <v>80.1508906422464</v>
       </c>
       <c r="E563" t="n">
-        <v>43.1777221239262</v>
+        <v>43.1777221239319</v>
       </c>
       <c r="F563" t="s">
         <v>39</v>
@@ -11747,13 +11747,13 @@
         <v>10</v>
       </c>
       <c r="C564" t="n">
-        <v>0.898700796190907</v>
+        <v>0.898700796190898</v>
       </c>
       <c r="D564" t="n">
-        <v>1.18962020441001</v>
+        <v>1.18962020441002</v>
       </c>
       <c r="E564" t="n">
-        <v>0.929284136296276</v>
+        <v>0.92928413629628</v>
       </c>
       <c r="F564" t="s">
         <v>39</v>
@@ -11767,13 +11767,13 @@
         <v>11</v>
       </c>
       <c r="C565" t="n">
-        <v>0.801198358338448</v>
+        <v>0.801198358338437</v>
       </c>
       <c r="D565" t="n">
-        <v>0.73259466282366</v>
+        <v>0.732594662823658</v>
       </c>
       <c r="E565" t="n">
-        <v>0.783322388560529</v>
+        <v>0.783322388560496</v>
       </c>
       <c r="F565" t="s">
         <v>39</v>
@@ -11793,7 +11793,7 @@
         <v>23.6684553504423</v>
       </c>
       <c r="E566" t="n">
-        <v>22.624187427154</v>
+        <v>22.6241874271541</v>
       </c>
       <c r="F566" t="s">
         <v>39</v>
@@ -11810,10 +11810,10 @@
         <v>35.7922873203654</v>
       </c>
       <c r="D567" t="n">
-        <v>56.034216897152</v>
+        <v>56.0342168971522</v>
       </c>
       <c r="E567" t="n">
-        <v>37.7420737494856</v>
+        <v>37.7420737494857</v>
       </c>
       <c r="F567" t="s">
         <v>39</v>
@@ -11827,13 +11827,13 @@
         <v>10</v>
       </c>
       <c r="C568" t="n">
-        <v>0.810233154184918</v>
+        <v>0.810233154184919</v>
       </c>
       <c r="D568" t="n">
-        <v>0.993697916484944</v>
+        <v>0.993697916484939</v>
       </c>
       <c r="E568" t="n">
-        <v>0.826681640336666</v>
+        <v>0.826681640336667</v>
       </c>
       <c r="F568" t="s">
         <v>39</v>
@@ -11850,7 +11850,7 @@
         <v>0.827955424622026</v>
       </c>
       <c r="D569" t="n">
-        <v>0.458607867621</v>
+        <v>0.458607867620997</v>
       </c>
       <c r="E569" t="n">
         <v>0.813157424106699</v>
@@ -11867,13 +11867,13 @@
         <v>7</v>
       </c>
       <c r="C570" t="n">
-        <v>19.865791254912</v>
+        <v>19.8409694917058</v>
       </c>
       <c r="D570" t="n">
-        <v>24.4543302294648</v>
+        <v>23.6950487280369</v>
       </c>
       <c r="E570" t="n">
-        <v>20.2523445572539</v>
+        <v>20.1660522072943</v>
       </c>
       <c r="F570" t="s">
         <v>39</v>
@@ -11887,13 +11887,13 @@
         <v>9</v>
       </c>
       <c r="C571" t="n">
-        <v>35.0625113190953</v>
+        <v>34.8335045278275</v>
       </c>
       <c r="D571" t="n">
-        <v>57.7585717876548</v>
+        <v>56.0614127222335</v>
       </c>
       <c r="E571" t="n">
-        <v>37.4918092842144</v>
+        <v>37.0787014633725</v>
       </c>
       <c r="F571" t="s">
         <v>39</v>
@@ -11907,13 +11907,13 @@
         <v>10</v>
       </c>
       <c r="C572" t="n">
-        <v>0.834193828216113</v>
+        <v>0.83094004282385</v>
       </c>
       <c r="D572" t="n">
-        <v>1.02039202722809</v>
+        <v>0.993002732898914</v>
       </c>
       <c r="E572" t="n">
-        <v>0.848769807252491</v>
+        <v>0.842186415386468</v>
       </c>
       <c r="F572" t="s">
         <v>39</v>
@@ -11927,13 +11927,13 @@
         <v>11</v>
       </c>
       <c r="C573" t="n">
-        <v>0.829954321118808</v>
+        <v>0.832231865308485</v>
       </c>
       <c r="D573" t="n">
-        <v>0.651923536556631</v>
+        <v>0.655395163832425</v>
       </c>
       <c r="E573" t="n">
-        <v>0.81074980417299</v>
+        <v>0.814453490332424</v>
       </c>
       <c r="F573" t="s">
         <v>39</v>
@@ -11947,13 +11947,13 @@
         <v>7</v>
       </c>
       <c r="C574" t="n">
-        <v>29.0398300058965</v>
+        <v>29.3506264196456</v>
       </c>
       <c r="D574" t="n">
-        <v>24.5705457883931</v>
+        <v>14.2514218088648</v>
       </c>
       <c r="E574" t="n">
-        <v>28.6998998434132</v>
+        <v>28.1892714763897</v>
       </c>
       <c r="F574" t="s">
         <v>39</v>
@@ -11967,13 +11967,13 @@
         <v>9</v>
       </c>
       <c r="C575" t="n">
-        <v>41.4580242624041</v>
+        <v>41.1903531150685</v>
       </c>
       <c r="D575" t="n">
-        <v>54.7609304247243</v>
+        <v>31.6078945800453</v>
       </c>
       <c r="E575" t="n">
-        <v>42.6357989477497</v>
+        <v>40.5342425286277</v>
       </c>
       <c r="F575" t="s">
         <v>39</v>
@@ -11987,13 +11987,13 @@
         <v>10</v>
       </c>
       <c r="C576" t="n">
-        <v>0.846389480669743</v>
+        <v>0.841692799474547</v>
       </c>
       <c r="D576" t="n">
-        <v>0.908523141449439</v>
+        <v>0.428548821614637</v>
       </c>
       <c r="E576" t="n">
-        <v>0.9495428121029</v>
+        <v>0.847876399701065</v>
       </c>
       <c r="F576" t="s">
         <v>39</v>
@@ -12007,13 +12007,13 @@
         <v>11</v>
       </c>
       <c r="C577" t="n">
-        <v>0.771067391137175</v>
+        <v>0.774774441257545</v>
       </c>
       <c r="D577" t="n">
-        <v>0.652231986740101</v>
+        <v>0.779883855144254</v>
       </c>
       <c r="E577" t="n">
-        <v>0.773530340971008</v>
+        <v>0.78872910626954</v>
       </c>
       <c r="F577" t="s">
         <v>39</v>
@@ -12027,13 +12027,13 @@
         <v>7</v>
       </c>
       <c r="C578" t="n">
-        <v>18.4942733408769</v>
+        <v>18.4906666108922</v>
       </c>
       <c r="D578" t="n">
-        <v>28.7682027355851</v>
+        <v>28.7715450580292</v>
       </c>
       <c r="E578" t="n">
-        <v>19.3509582481861</v>
+        <v>19.3479305699006</v>
       </c>
       <c r="F578" t="s">
         <v>40</v>
@@ -12047,13 +12047,13 @@
         <v>9</v>
       </c>
       <c r="C579" t="n">
-        <v>120.636538637997</v>
+        <v>120.640506006714</v>
       </c>
       <c r="D579" t="n">
-        <v>220.6248165777</v>
+        <v>220.639091587807</v>
       </c>
       <c r="E579" t="n">
-        <v>131.892719410178</v>
+        <v>131.898039329215</v>
       </c>
       <c r="F579" t="s">
         <v>40</v>
@@ -12067,13 +12067,13 @@
         <v>10</v>
       </c>
       <c r="C580" t="n">
-        <v>1.43403191016247</v>
+        <v>1.43409424239122</v>
       </c>
       <c r="D580" t="n">
-        <v>5.6954019247621</v>
+        <v>5.7018587366167</v>
       </c>
       <c r="E580" t="n">
-        <v>1.6006942042734</v>
+        <v>1.60084346033729</v>
       </c>
       <c r="F580" t="s">
         <v>40</v>
@@ -12087,13 +12087,13 @@
         <v>11</v>
       </c>
       <c r="C581" t="n">
-        <v>0.853051732008176</v>
+        <v>0.853045670188969</v>
       </c>
       <c r="D581" t="n">
-        <v>0.151660846707767</v>
+        <v>0.15224709914765</v>
       </c>
       <c r="E581" t="n">
-        <v>0.815604263216677</v>
+        <v>0.815591768359847</v>
       </c>
       <c r="F581" t="s">
         <v>40</v>
@@ -12107,13 +12107,13 @@
         <v>7</v>
       </c>
       <c r="C582" t="n">
-        <v>13.6777508922897</v>
+        <v>13.67775089229</v>
       </c>
       <c r="D582" t="n">
-        <v>24.3534493856189</v>
+        <v>24.3534493856205</v>
       </c>
       <c r="E582" t="n">
-        <v>14.5004651793185</v>
+        <v>14.5004651793189</v>
       </c>
       <c r="F582" t="s">
         <v>40</v>
@@ -12127,13 +12127,13 @@
         <v>9</v>
       </c>
       <c r="C583" t="n">
-        <v>77.6283767749308</v>
+        <v>77.628376774927</v>
       </c>
       <c r="D583" t="n">
-        <v>130.94779797014</v>
+        <v>130.947797970134</v>
       </c>
       <c r="E583" t="n">
-        <v>82.9586250065035</v>
+        <v>82.9586250064995</v>
       </c>
       <c r="F583" t="s">
         <v>40</v>
@@ -12147,13 +12147,13 @@
         <v>10</v>
       </c>
       <c r="C584" t="n">
-        <v>0.641792476748962</v>
+        <v>0.641792476748847</v>
       </c>
       <c r="D584" t="n">
-        <v>2.59532255619703</v>
+        <v>2.59532255619678</v>
       </c>
       <c r="E584" t="n">
-        <v>0.698231104438142</v>
+        <v>0.698231104438022</v>
       </c>
       <c r="F584" t="s">
         <v>40</v>
@@ -12167,13 +12167,13 @@
         <v>11</v>
       </c>
       <c r="C585" t="n">
-        <v>0.934569227862264</v>
+        <v>0.934569227862271</v>
       </c>
       <c r="D585" t="n">
-        <v>0.881836598802238</v>
+        <v>0.881836598802251</v>
       </c>
       <c r="E585" t="n">
-        <v>0.921499528953858</v>
+        <v>0.921499528953867</v>
       </c>
       <c r="F585" t="s">
         <v>40</v>
@@ -12187,13 +12187,13 @@
         <v>7</v>
       </c>
       <c r="C586" t="n">
-        <v>13.8618392514492</v>
+        <v>13.8618392830841</v>
       </c>
       <c r="D586" t="n">
-        <v>20.2754584893313</v>
+        <v>20.2754603907653</v>
       </c>
       <c r="E586" t="n">
-        <v>14.3543996204455</v>
+        <v>14.3543997959197</v>
       </c>
       <c r="F586" t="s">
         <v>40</v>
@@ -12207,13 +12207,13 @@
         <v>9</v>
       </c>
       <c r="C587" t="n">
-        <v>82.4166952833546</v>
+        <v>82.4166952999851</v>
       </c>
       <c r="D587" t="n">
-        <v>136.013131485663</v>
+        <v>136.01313592703</v>
       </c>
       <c r="E587" t="n">
-        <v>87.7041660031484</v>
+        <v>87.704166546283</v>
       </c>
       <c r="F587" t="s">
         <v>40</v>
@@ -12227,13 +12227,13 @@
         <v>10</v>
       </c>
       <c r="C588" t="n">
-        <v>0.467552907621672</v>
+        <v>0.467552905113863</v>
       </c>
       <c r="D588" t="n">
-        <v>1.77404644672538</v>
+        <v>1.77404655542254</v>
       </c>
       <c r="E588" t="n">
-        <v>0.507350741157675</v>
+        <v>0.507350742727314</v>
       </c>
       <c r="F588" t="s">
         <v>40</v>
@@ -12247,13 +12247,13 @@
         <v>11</v>
       </c>
       <c r="C589" t="n">
-        <v>0.935416057578518</v>
+        <v>0.935416057223206</v>
       </c>
       <c r="D589" t="n">
-        <v>0.816356535625813</v>
+        <v>0.816356535701594</v>
       </c>
       <c r="E589" t="n">
-        <v>0.920373172159423</v>
+        <v>0.920373171054369</v>
       </c>
       <c r="F589" t="s">
         <v>40</v>
@@ -12347,13 +12347,13 @@
         <v>7</v>
       </c>
       <c r="C594" t="n">
-        <v>13.163808132975</v>
+        <v>13.1492329818037</v>
       </c>
       <c r="D594" t="n">
-        <v>19.7272635844111</v>
+        <v>18.3881692469424</v>
       </c>
       <c r="E594" t="n">
-        <v>13.7116866793087</v>
+        <v>13.5867481773672</v>
       </c>
       <c r="F594" t="s">
         <v>40</v>
@@ -12367,13 +12367,13 @@
         <v>9</v>
       </c>
       <c r="C595" t="n">
-        <v>79.6397493530118</v>
+        <v>79.4519922502174</v>
       </c>
       <c r="D595" t="n">
-        <v>143.149425053578</v>
+        <v>145.563990842087</v>
       </c>
       <c r="E595" t="n">
-        <v>86.7242142245345</v>
+        <v>86.8990325355122</v>
       </c>
       <c r="F595" t="s">
         <v>40</v>
@@ -12387,13 +12387,13 @@
         <v>10</v>
       </c>
       <c r="C596" t="n">
-        <v>0.705696574024768</v>
+        <v>0.690376757972654</v>
       </c>
       <c r="D596" t="n">
-        <v>2.72053652444767</v>
+        <v>2.64762513747882</v>
       </c>
       <c r="E596" t="n">
-        <v>0.76673732245239</v>
+        <v>0.748025580094582</v>
       </c>
       <c r="F596" t="s">
         <v>40</v>
@@ -12407,13 +12407,13 @@
         <v>11</v>
       </c>
       <c r="C597" t="n">
-        <v>0.935040981604201</v>
+        <v>0.935426073680727</v>
       </c>
       <c r="D597" t="n">
-        <v>0.887297940664464</v>
+        <v>0.844763549597409</v>
       </c>
       <c r="E597" t="n">
-        <v>0.919059351345893</v>
+        <v>0.918870960365436</v>
       </c>
       <c r="F597" t="s">
         <v>40</v>
@@ -12427,13 +12427,13 @@
         <v>7</v>
       </c>
       <c r="C598" t="n">
-        <v>27.2279664436224</v>
+        <v>25.850213132794</v>
       </c>
       <c r="D598" t="n">
-        <v>26.8382237805092</v>
+        <v>22.4938920980936</v>
       </c>
       <c r="E598" t="n">
-        <v>27.1976095242256</v>
+        <v>25.5916281288914</v>
       </c>
       <c r="F598" t="s">
         <v>40</v>
@@ -12447,13 +12447,13 @@
         <v>9</v>
       </c>
       <c r="C599" t="n">
-        <v>110.174226657261</v>
+        <v>108.601750122877</v>
       </c>
       <c r="D599" t="n">
-        <v>146.267431686201</v>
+        <v>137.726763797143</v>
       </c>
       <c r="E599" t="n">
-        <v>113.353694220842</v>
+        <v>111.109810215082</v>
       </c>
       <c r="F599" t="s">
         <v>40</v>
@@ -12467,13 +12467,13 @@
         <v>10</v>
       </c>
       <c r="C600" t="n">
-        <v>0.794014165698996</v>
+        <v>0.769662865182459</v>
       </c>
       <c r="D600" t="n">
-        <v>1.75024903512104</v>
+        <v>1.60061220559487</v>
       </c>
       <c r="E600" t="n">
-        <v>0.793393618796982</v>
+        <v>0.754500232933336</v>
       </c>
       <c r="F600" t="s">
         <v>40</v>
@@ -12487,13 +12487,13 @@
         <v>11</v>
       </c>
       <c r="C601" t="n">
-        <v>0.877392447474371</v>
+        <v>0.88197263502368</v>
       </c>
       <c r="D601" t="n">
-        <v>0.730285254440669</v>
+        <v>0.72542113493388</v>
       </c>
       <c r="E601" t="n">
-        <v>0.86387186671171</v>
+        <v>0.869076835843255</v>
       </c>
       <c r="F601" t="s">
         <v>40</v>
@@ -12507,13 +12507,13 @@
         <v>7</v>
       </c>
       <c r="C602" t="n">
-        <v>10.000055798653</v>
+        <v>10.0000498422663</v>
       </c>
       <c r="D602" t="n">
-        <v>19.5679336058804</v>
+        <v>19.5683509140995</v>
       </c>
       <c r="E602" t="n">
-        <v>10.7965005191999</v>
+        <v>10.7965298347758</v>
       </c>
       <c r="F602" t="s">
         <v>41</v>
@@ -12527,13 +12527,13 @@
         <v>9</v>
       </c>
       <c r="C603" t="n">
-        <v>161.507489703367</v>
+        <v>161.507522171051</v>
       </c>
       <c r="D603" t="n">
-        <v>200.024300056945</v>
+        <v>200.025950672829</v>
       </c>
       <c r="E603" t="n">
-        <v>165.053836898022</v>
+        <v>165.054032717163</v>
       </c>
       <c r="F603" t="s">
         <v>41</v>
@@ -12547,13 +12547,13 @@
         <v>10</v>
       </c>
       <c r="C604" t="n">
-        <v>0.466143945423665</v>
+        <v>0.466143742110422</v>
       </c>
       <c r="D604" t="n">
-        <v>4.38726625894705</v>
+        <v>4.38766210544065</v>
       </c>
       <c r="E604" t="n">
-        <v>0.519098053246487</v>
+        <v>0.519099450924066</v>
       </c>
       <c r="F604" t="s">
         <v>41</v>
@@ -12567,13 +12567,13 @@
         <v>11</v>
       </c>
       <c r="C605" t="n">
-        <v>0.977113830100644</v>
+        <v>0.977113815091513</v>
       </c>
       <c r="D605" t="n">
-        <v>0.944424430372488</v>
+        <v>0.94444233029977</v>
       </c>
       <c r="E605" t="n">
-        <v>0.974737962418427</v>
+        <v>0.97473791328208</v>
       </c>
       <c r="F605" t="s">
         <v>41</v>
@@ -12827,13 +12827,13 @@
         <v>7</v>
       </c>
       <c r="C618" t="n">
-        <v>8.67743639446565</v>
+        <v>8.69644044011817</v>
       </c>
       <c r="D618" t="n">
-        <v>6.51534215758794</v>
+        <v>6.01628069066831</v>
       </c>
       <c r="E618" t="n">
-        <v>8.49806825321425</v>
+        <v>8.47390022601183</v>
       </c>
       <c r="F618" t="s">
         <v>41</v>
@@ -12847,13 +12847,13 @@
         <v>9</v>
       </c>
       <c r="C619" t="n">
-        <v>126.963530780073</v>
+        <v>127.549153990957</v>
       </c>
       <c r="D619" t="n">
-        <v>58.2866871892588</v>
+        <v>55.1585431873207</v>
       </c>
       <c r="E619" t="n">
-        <v>122.718506213144</v>
+        <v>123.153992541475</v>
       </c>
       <c r="F619" t="s">
         <v>41</v>
@@ -12867,13 +12867,13 @@
         <v>10</v>
       </c>
       <c r="C620" t="n">
-        <v>0.353408553336177</v>
+        <v>0.352794628652863</v>
       </c>
       <c r="D620" t="n">
-        <v>0.63685511002368</v>
+        <v>0.579830548272903</v>
       </c>
       <c r="E620" t="n">
-        <v>0.354004597196216</v>
+        <v>0.351851036032468</v>
       </c>
       <c r="F620" t="s">
         <v>41</v>
@@ -12887,13 +12887,13 @@
         <v>11</v>
       </c>
       <c r="C621" t="n">
-        <v>0.985499637522756</v>
+        <v>0.985364452486005</v>
       </c>
       <c r="D621" t="n">
-        <v>0.966799224934315</v>
+        <v>0.968380797849279</v>
       </c>
       <c r="E621" t="n">
-        <v>0.985601151610877</v>
+        <v>0.985498018925171</v>
       </c>
       <c r="F621" t="s">
         <v>41</v>
@@ -12907,13 +12907,13 @@
         <v>7</v>
       </c>
       <c r="C622" t="n">
-        <v>33.9755916816829</v>
+        <v>34.3893811404573</v>
       </c>
       <c r="D622" t="n">
-        <v>12.6492730121316</v>
+        <v>9.65411088205439</v>
       </c>
       <c r="E622" t="n">
-        <v>32.3358447495819</v>
+        <v>32.4859190676127</v>
       </c>
       <c r="F622" t="s">
         <v>41</v>
@@ -12927,13 +12927,13 @@
         <v>9</v>
       </c>
       <c r="C623" t="n">
-        <v>362.467920896073</v>
+        <v>361.780552098674</v>
       </c>
       <c r="D623" t="n">
-        <v>104.018018029004</v>
+        <v>75.6260191739912</v>
       </c>
       <c r="E623" t="n">
-        <v>349.442486370068</v>
+        <v>348.219100830236</v>
       </c>
       <c r="F623" t="s">
         <v>41</v>
@@ -12947,13 +12947,13 @@
         <v>10</v>
       </c>
       <c r="C624" t="n">
-        <v>0.781776129905462</v>
+        <v>0.784254608486378</v>
       </c>
       <c r="D624" t="n">
-        <v>0.811156134380752</v>
+        <v>0.527828369119704</v>
       </c>
       <c r="E624" t="n">
-        <v>0.68940964905735</v>
+        <v>0.687275500701376</v>
       </c>
       <c r="F624" t="s">
         <v>41</v>
@@ -12967,13 +12967,13 @@
         <v>11</v>
       </c>
       <c r="C625" t="n">
-        <v>0.894068056153411</v>
+        <v>0.894743998159487</v>
       </c>
       <c r="D625" t="n">
-        <v>0.903383720132106</v>
+        <v>0.914355182006956</v>
       </c>
       <c r="E625" t="n">
-        <v>0.895254302004565</v>
+        <v>0.897272274543778</v>
       </c>
       <c r="F625" t="s">
         <v>41</v>
@@ -12987,13 +12987,13 @@
         <v>7</v>
       </c>
       <c r="C626" t="n">
-        <v>23.7563019893415</v>
+        <v>23.7563019077868</v>
       </c>
       <c r="D626" t="n">
-        <v>120.686638355881</v>
+        <v>120.686639914924</v>
       </c>
       <c r="E626" t="n">
-        <v>31.8338108799725</v>
+        <v>31.8338109351345</v>
       </c>
       <c r="F626" t="s">
         <v>42</v>
@@ -13007,13 +13007,13 @@
         <v>9</v>
       </c>
       <c r="C627" t="n">
-        <v>3465.99461399251</v>
+        <v>3465.99451644119</v>
       </c>
       <c r="D627" t="n">
-        <v>28043.2219780438</v>
+        <v>28043.2221409967</v>
       </c>
       <c r="E627" t="n">
-        <v>8749.10234991738</v>
+        <v>8749.10235801795</v>
       </c>
       <c r="F627" t="s">
         <v>42</v>
@@ -13027,13 +13027,13 @@
         <v>10</v>
       </c>
       <c r="C628" t="n">
-        <v>0.532092161445564</v>
+        <v>0.532092158290372</v>
       </c>
       <c r="D628" t="n">
-        <v>45.4197657760952</v>
+        <v>45.419764853864</v>
       </c>
       <c r="E628" t="n">
-        <v>1.10795139103445</v>
+        <v>1.10795139505691</v>
       </c>
       <c r="F628" t="s">
         <v>42</v>
@@ -13047,13 +13047,13 @@
         <v>11</v>
       </c>
       <c r="C629" t="n">
-        <v>0.844107848833612</v>
+        <v>0.844107857884632</v>
       </c>
       <c r="D629" t="n">
-        <v>0.093420441280519</v>
+        <v>0.0934204377741586</v>
       </c>
       <c r="E629" t="n">
-        <v>0.450584374381074</v>
+        <v>0.450584374574945</v>
       </c>
       <c r="F629" t="s">
         <v>42</v>
@@ -13147,13 +13147,13 @@
         <v>7</v>
       </c>
       <c r="C634" t="n">
-        <v>22.3839956023461</v>
+        <v>22.383995468843</v>
       </c>
       <c r="D634" t="n">
-        <v>54.2813995981818</v>
+        <v>54.2813965076714</v>
       </c>
       <c r="E634" t="n">
-        <v>24.8376409285672</v>
+        <v>24.8376405676025</v>
       </c>
       <c r="F634" t="s">
         <v>42</v>
@@ -13167,13 +13167,13 @@
         <v>9</v>
       </c>
       <c r="C635" t="n">
-        <v>4585.23221113886</v>
+        <v>4585.23218180452</v>
       </c>
       <c r="D635" t="n">
-        <v>43424.2463013843</v>
+        <v>43424.2325009888</v>
       </c>
       <c r="E635" t="n">
-        <v>12824.1392968959</v>
+        <v>12824.1356925961</v>
       </c>
       <c r="F635" t="s">
         <v>42</v>
@@ -13187,13 +13187,13 @@
         <v>10</v>
       </c>
       <c r="C636" t="n">
-        <v>0.544201663029796</v>
+        <v>0.544201655167488</v>
       </c>
       <c r="D636" t="n">
-        <v>0.739389744632589</v>
+        <v>0.7393897394333</v>
       </c>
       <c r="E636" t="n">
-        <v>0.621089649013673</v>
+        <v>0.621089625310276</v>
       </c>
       <c r="F636" t="s">
         <v>42</v>
@@ -13207,13 +13207,13 @@
         <v>11</v>
       </c>
       <c r="C637" t="n">
-        <v>0.766583014369087</v>
+        <v>0.766583013937115</v>
       </c>
       <c r="D637" t="n">
-        <v>0.398617524117753</v>
+        <v>0.398617566417308</v>
       </c>
       <c r="E637" t="n">
-        <v>0.618976971513298</v>
+        <v>0.618977043763322</v>
       </c>
       <c r="F637" t="s">
         <v>42</v>
@@ -13307,13 +13307,13 @@
         <v>7</v>
       </c>
       <c r="C642" t="n">
-        <v>21.594049111611</v>
+        <v>21.5524558509904</v>
       </c>
       <c r="D642" t="n">
-        <v>58.188104883899</v>
+        <v>58.0080405489167</v>
       </c>
       <c r="E642" t="n">
-        <v>24.408970030384</v>
+        <v>24.3567251269015</v>
       </c>
       <c r="F642" t="s">
         <v>42</v>
@@ -13327,13 +13327,13 @@
         <v>9</v>
       </c>
       <c r="C643" t="n">
-        <v>6347.6435116725</v>
+        <v>6304.45523869737</v>
       </c>
       <c r="D643" t="n">
-        <v>31012.8709752959</v>
+        <v>30949.6961968757</v>
       </c>
       <c r="E643" t="n">
-        <v>10544.0865328683</v>
+        <v>10505.8201791639</v>
       </c>
       <c r="F643" t="s">
         <v>42</v>
@@ -13347,13 +13347,13 @@
         <v>10</v>
       </c>
       <c r="C644" t="n">
-        <v>0.496407094278849</v>
+        <v>0.496553514392819</v>
       </c>
       <c r="D644" t="n">
-        <v>0.864150759691254</v>
+        <v>0.863603023146622</v>
       </c>
       <c r="E644" t="n">
-        <v>0.594355516216038</v>
+        <v>0.594599665454392</v>
       </c>
       <c r="F644" t="s">
         <v>42</v>
@@ -13367,13 +13367,13 @@
         <v>11</v>
       </c>
       <c r="C645" t="n">
-        <v>0.71671271459246</v>
+        <v>0.716886885507276</v>
       </c>
       <c r="D645" t="n">
-        <v>0.0939914612354513</v>
+        <v>0.0942248911751011</v>
       </c>
       <c r="E645" t="n">
-        <v>0.606356701365546</v>
+        <v>0.606398053777492</v>
       </c>
       <c r="F645" t="s">
         <v>42</v>
@@ -13387,13 +13387,13 @@
         <v>7</v>
       </c>
       <c r="C646" t="n">
-        <v>35.7348345631995</v>
+        <v>35.6035781943844</v>
       </c>
       <c r="D646" t="n">
-        <v>72.4375898236766</v>
+        <v>86.4937096314201</v>
       </c>
       <c r="E646" t="n">
-        <v>38.5581001900312</v>
+        <v>39.5181821837485</v>
       </c>
       <c r="F646" t="s">
         <v>42</v>
@@ -13407,13 +13407,13 @@
         <v>9</v>
       </c>
       <c r="C647" t="n">
-        <v>5264.90895102882</v>
+        <v>5262.93771368021</v>
       </c>
       <c r="D647" t="n">
-        <v>20829.9844638531</v>
+        <v>22033.1942913237</v>
       </c>
       <c r="E647" t="n">
-        <v>7678.72086583869</v>
+        <v>7931.62999752042</v>
       </c>
       <c r="F647" t="s">
         <v>42</v>
@@ -13427,13 +13427,13 @@
         <v>10</v>
       </c>
       <c r="C648" t="n">
-        <v>0.880835784529216</v>
+        <v>0.879990509864834</v>
       </c>
       <c r="D648" t="n">
-        <v>5.75477849697751</v>
+        <v>5.12660557338341</v>
       </c>
       <c r="E648" t="n">
-        <v>1.20133084034675</v>
+        <v>1.2080102420184</v>
       </c>
       <c r="F648" t="s">
         <v>42</v>
@@ -13447,13 +13447,13 @@
         <v>11</v>
       </c>
       <c r="C649" t="n">
-        <v>0.642559065256001</v>
+        <v>0.644735915868852</v>
       </c>
       <c r="D649" t="n">
-        <v>0.389247455391408</v>
+        <v>0.530221222584867</v>
       </c>
       <c r="E649" t="n">
-        <v>0.5367038950034</v>
+        <v>0.508224038796574</v>
       </c>
       <c r="F649" t="s">
         <v>42</v>
@@ -13467,13 +13467,13 @@
         <v>7</v>
       </c>
       <c r="C650" t="n">
-        <v>7.89312563754294</v>
+        <v>7.89312565735106</v>
       </c>
       <c r="D650" t="n">
-        <v>18.3367596547678</v>
+        <v>18.336759035296</v>
       </c>
       <c r="E650" t="n">
-        <v>8.76344952673325</v>
+        <v>8.76344949326808</v>
       </c>
       <c r="F650" t="s">
         <v>43</v>
@@ -13487,13 +13487,13 @@
         <v>9</v>
       </c>
       <c r="C651" t="n">
-        <v>1744.80504832682</v>
+        <v>1744.80505473833</v>
       </c>
       <c r="D651" t="n">
-        <v>5897.29503079513</v>
+        <v>5897.29478328713</v>
       </c>
       <c r="E651" t="n">
-        <v>2385.13717979181</v>
+        <v>2385.13713309303</v>
       </c>
       <c r="F651" t="s">
         <v>43</v>
@@ -13507,13 +13507,13 @@
         <v>10</v>
       </c>
       <c r="C652" t="n">
-        <v>0.453040912748173</v>
+        <v>0.453040920201582</v>
       </c>
       <c r="D652" t="n">
-        <v>1.15708698065221</v>
+        <v>1.15708696058528</v>
       </c>
       <c r="E652" t="n">
-        <v>0.523578429875149</v>
+        <v>0.523578433644186</v>
       </c>
       <c r="F652" t="s">
         <v>43</v>
@@ -13527,13 +13527,13 @@
         <v>11</v>
       </c>
       <c r="C653" t="n">
-        <v>0.892686561839956</v>
+        <v>0.892686561328646</v>
       </c>
       <c r="D653" t="n">
-        <v>0.175730729808734</v>
+        <v>0.175730735627079</v>
       </c>
       <c r="E653" t="n">
-        <v>0.816013166718478</v>
+        <v>0.816013167871071</v>
       </c>
       <c r="F653" t="s">
         <v>43</v>
@@ -13627,13 +13627,13 @@
         <v>7</v>
       </c>
       <c r="C658" t="n">
-        <v>5.97369327631321</v>
+        <v>5.97369296453511</v>
       </c>
       <c r="D658" t="n">
-        <v>15.7446351129404</v>
+        <v>15.7446372264705</v>
       </c>
       <c r="E658" t="n">
-        <v>6.7253407151431</v>
+        <v>6.72534058992712</v>
       </c>
       <c r="F658" t="s">
         <v>43</v>
@@ -13647,13 +13647,13 @@
         <v>9</v>
       </c>
       <c r="C659" t="n">
-        <v>1446.06894633548</v>
+        <v>1446.06902616797</v>
       </c>
       <c r="D659" t="n">
-        <v>5357.99967914712</v>
+        <v>5358.00000431914</v>
       </c>
       <c r="E659" t="n">
-        <v>2034.36424643221</v>
+        <v>2034.36436469429</v>
       </c>
       <c r="F659" t="s">
         <v>43</v>
@@ -13667,13 +13667,13 @@
         <v>10</v>
       </c>
       <c r="C660" t="n">
-        <v>0.321957383459956</v>
+        <v>0.321957415102438</v>
       </c>
       <c r="D660" t="n">
-        <v>1.08382697164125</v>
+        <v>1.08382704536342</v>
       </c>
       <c r="E660" t="n">
-        <v>0.380795520186255</v>
+        <v>0.380795561123691</v>
       </c>
       <c r="F660" t="s">
         <v>43</v>
@@ -13687,13 +13687,13 @@
         <v>11</v>
       </c>
       <c r="C661" t="n">
-        <v>0.927482462201828</v>
+        <v>0.927482454100375</v>
       </c>
       <c r="D661" t="n">
-        <v>0.337682252636359</v>
+        <v>0.33768230111971</v>
       </c>
       <c r="E661" t="n">
-        <v>0.874876692192604</v>
+        <v>0.874876681023379</v>
       </c>
       <c r="F661" t="s">
         <v>43</v>
@@ -13787,13 +13787,13 @@
         <v>7</v>
       </c>
       <c r="C666" t="n">
-        <v>5.64827239369183</v>
+        <v>5.65536494969227</v>
       </c>
       <c r="D666" t="n">
-        <v>13.3440784937447</v>
+        <v>13.3478182091789</v>
       </c>
       <c r="E666" t="n">
-        <v>6.289616234784</v>
+        <v>6.29642938352387</v>
       </c>
       <c r="F666" t="s">
         <v>43</v>
@@ -13807,13 +13807,13 @@
         <v>9</v>
       </c>
       <c r="C667" t="n">
-        <v>1347.88783984751</v>
+        <v>1346.32403559655</v>
       </c>
       <c r="D667" t="n">
-        <v>4263.7806428977</v>
+        <v>4302.76907811941</v>
       </c>
       <c r="E667" t="n">
-        <v>1783.37664705508</v>
+        <v>1790.08473864002</v>
       </c>
       <c r="F667" t="s">
         <v>43</v>
@@ -13827,13 +13827,13 @@
         <v>10</v>
       </c>
       <c r="C668" t="n">
-        <v>0.32534004384175</v>
+        <v>0.325086196094093</v>
       </c>
       <c r="D668" t="n">
-        <v>0.936044894265592</v>
+        <v>0.930568394811929</v>
       </c>
       <c r="E668" t="n">
-        <v>0.375965090722667</v>
+        <v>0.375654880170793</v>
       </c>
       <c r="F668" t="s">
         <v>43</v>
@@ -13847,13 +13847,13 @@
         <v>11</v>
       </c>
       <c r="C669" t="n">
-        <v>0.936247077977044</v>
+        <v>0.936398923634973</v>
       </c>
       <c r="D669" t="n">
-        <v>0.454677224231703</v>
+        <v>0.449144902025788</v>
       </c>
       <c r="E669" t="n">
-        <v>0.895527038017017</v>
+        <v>0.894993732528698</v>
       </c>
       <c r="F669" t="s">
         <v>43</v>
@@ -13867,13 +13867,13 @@
         <v>7</v>
       </c>
       <c r="C670" t="n">
-        <v>8.82562618848408</v>
+        <v>8.84818786377017</v>
       </c>
       <c r="D670" t="n">
-        <v>8.60636304160095</v>
+        <v>8.81347364034423</v>
       </c>
       <c r="E670" t="n">
-        <v>8.80876393167298</v>
+        <v>8.84551461646298</v>
       </c>
       <c r="F670" t="s">
         <v>43</v>
@@ -13887,13 +13887,13 @@
         <v>9</v>
       </c>
       <c r="C671" t="n">
-        <v>1957.8117472068</v>
+        <v>1960.235129887</v>
       </c>
       <c r="D671" t="n">
-        <v>2380.19777546893</v>
+        <v>2394.2646647076</v>
       </c>
       <c r="E671" t="n">
-        <v>1993.48594929374</v>
+        <v>1996.97385198719</v>
       </c>
       <c r="F671" t="s">
         <v>43</v>
@@ -13907,13 +13907,13 @@
         <v>10</v>
       </c>
       <c r="C672" t="n">
-        <v>0.455195394413186</v>
+        <v>0.457579612740933</v>
       </c>
       <c r="D672" t="n">
-        <v>0.714955475736477</v>
+        <v>0.672130295316521</v>
       </c>
       <c r="E672" t="n">
-        <v>0.503906751432708</v>
+        <v>0.498927311515786</v>
       </c>
       <c r="F672" t="s">
         <v>43</v>
@@ -13927,13 +13927,13 @@
         <v>11</v>
       </c>
       <c r="C673" t="n">
-        <v>0.870035318640761</v>
+        <v>0.870153421337356</v>
       </c>
       <c r="D673" t="n">
-        <v>0.621009706922279</v>
+        <v>0.604842081987597</v>
       </c>
       <c r="E673" t="n">
-        <v>0.868465581235771</v>
+        <v>0.867680262148501</v>
       </c>
       <c r="F673" t="s">
         <v>43</v>
@@ -13947,13 +13947,13 @@
         <v>7</v>
       </c>
       <c r="C674" t="n">
-        <v>63.2701841625204</v>
+        <v>63.270184161646</v>
       </c>
       <c r="D674" t="n">
-        <v>111.566134236844</v>
+        <v>111.566134254217</v>
       </c>
       <c r="E674" t="n">
-        <v>71.5520803103664</v>
+        <v>71.5520803095053</v>
       </c>
       <c r="F674" t="s">
         <v>44</v>
@@ -13967,13 +13967,13 @@
         <v>9</v>
       </c>
       <c r="C675" t="n">
-        <v>11.1371289200625</v>
+        <v>11.1371289151411</v>
       </c>
       <c r="D675" t="n">
-        <v>1.29558182201844</v>
+        <v>1.2955818220116</v>
       </c>
       <c r="E675" t="n">
-        <v>10.6655901503522</v>
+        <v>10.6655901456444</v>
       </c>
       <c r="F675" t="s">
         <v>44</v>
@@ -13987,13 +13987,13 @@
         <v>10</v>
       </c>
       <c r="C676" t="n">
-        <v>0.390563240015615</v>
+        <v>0.390563239617833</v>
       </c>
       <c r="D676" t="n">
-        <v>4.99437554547895</v>
+        <v>4.99437554418006</v>
       </c>
       <c r="E676" t="n">
-        <v>0.399462806852934</v>
+        <v>0.399462806451242</v>
       </c>
       <c r="F676" t="s">
         <v>44</v>
@@ -14007,13 +14007,13 @@
         <v>11</v>
       </c>
       <c r="C677" t="n">
-        <v>0.958041346555612</v>
+        <v>0.958041346562476</v>
       </c>
       <c r="D677" t="n">
-        <v>0.334243052931607</v>
+        <v>0.3342430527956</v>
       </c>
       <c r="E677" t="n">
-        <v>0.958589456095252</v>
+        <v>0.958589456102127</v>
       </c>
       <c r="F677" t="s">
         <v>44</v>
@@ -14105,13 +14105,13 @@
         <v>7</v>
       </c>
       <c r="C682" t="n">
-        <v>121.006529693965</v>
+        <v>121.006529693958</v>
       </c>
       <c r="D682" t="n">
-        <v>124.036615319464</v>
+        <v>124.036615319456</v>
       </c>
       <c r="E682" t="n">
-        <v>124.822331340269</v>
+        <v>124.822331340263</v>
       </c>
       <c r="F682" t="s">
         <v>44</v>
@@ -14125,13 +14125,13 @@
         <v>9</v>
       </c>
       <c r="C683" t="n">
-        <v>48.2501666395763</v>
+        <v>48.2501666395732</v>
       </c>
       <c r="D683" t="n">
-        <v>1.36956808768415</v>
+        <v>1.36956808768422</v>
       </c>
       <c r="E683" t="n">
-        <v>46.3586818105844</v>
+        <v>46.3586818105815</v>
       </c>
       <c r="F683" t="s">
         <v>44</v>
@@ -14145,13 +14145,13 @@
         <v>10</v>
       </c>
       <c r="C684" t="n">
-        <v>2.18647055087364</v>
+        <v>2.18647055087238</v>
       </c>
       <c r="D684" t="n">
-        <v>11.0171495783153</v>
+        <v>11.0171495783285</v>
       </c>
       <c r="E684" t="n">
-        <v>2.19387369488861</v>
+        <v>2.19387369488735</v>
       </c>
       <c r="F684" t="s">
         <v>44</v>
@@ -14165,13 +14165,13 @@
         <v>11</v>
       </c>
       <c r="C685" t="n">
-        <v>0.337125035325843</v>
+        <v>0.337125035325914</v>
       </c>
       <c r="D685" t="n">
-        <v>0.0745971572930077</v>
+        <v>0.0745971572929958</v>
       </c>
       <c r="E685" t="n">
-        <v>0.344196238905878</v>
+        <v>0.344196238905948</v>
       </c>
       <c r="F685" t="s">
         <v>44</v>
@@ -14265,13 +14265,13 @@
         <v>7</v>
       </c>
       <c r="C690" t="n">
-        <v>98.6797175800367</v>
+        <v>94.6419570546678</v>
       </c>
       <c r="D690" t="n">
-        <v>133.666689314477</v>
+        <v>119.785382934837</v>
       </c>
       <c r="E690" t="n">
-        <v>104.893165950145</v>
+        <v>100.477862443735</v>
       </c>
       <c r="F690" t="s">
         <v>44</v>
@@ -14285,13 +14285,13 @@
         <v>9</v>
       </c>
       <c r="C691" t="n">
-        <v>22.5871234530326</v>
+        <v>21.5107797075064</v>
       </c>
       <c r="D691" t="n">
-        <v>1.41722918712796</v>
+        <v>1.3501171967764</v>
       </c>
       <c r="E691" t="n">
-        <v>21.6222335840346</v>
+        <v>20.5918521182068</v>
       </c>
       <c r="F691" t="s">
         <v>44</v>
@@ -14305,13 +14305,13 @@
         <v>10</v>
       </c>
       <c r="C692" t="n">
-        <v>1.93605243771142</v>
+        <v>1.91043870384398</v>
       </c>
       <c r="D692" t="n">
-        <v>12.3929921525301</v>
+        <v>9.78790271478564</v>
       </c>
       <c r="E692" t="n">
-        <v>1.95274918765526</v>
+        <v>1.92649944652256</v>
       </c>
       <c r="F692" t="s">
         <v>44</v>
@@ -14325,13 +14325,13 @@
         <v>11</v>
       </c>
       <c r="C693" t="n">
-        <v>0.756242966007162</v>
+        <v>0.782852319644819</v>
       </c>
       <c r="D693" t="n">
-        <v>0.243409319661405</v>
+        <v>0.061072078630598</v>
       </c>
       <c r="E693" t="n">
-        <v>0.759773394829377</v>
+        <v>0.786023628409502</v>
       </c>
       <c r="F693" t="s">
         <v>44</v>
@@ -14348,7 +14348,7 @@
         <v>#NUM!</v>
       </c>
       <c r="D694" t="n">
-        <v>194.720458733709</v>
+        <v>188.205525384661</v>
       </c>
       <c r="E694" t="e">
         <v>#NUM!</v>
@@ -14365,13 +14365,13 @@
         <v>9</v>
       </c>
       <c r="C695" t="n">
-        <v>57.4899430845551</v>
+        <v>57.396871226781</v>
       </c>
       <c r="D695" t="n">
-        <v>17.4848902021771</v>
+        <v>10.6764574028614</v>
       </c>
       <c r="E695" t="n">
-        <v>55.4477752837157</v>
+        <v>55.2242143368452</v>
       </c>
       <c r="F695" t="s">
         <v>44</v>
@@ -14385,13 +14385,13 @@
         <v>10</v>
       </c>
       <c r="C696" t="n">
-        <v>1.72917331850556</v>
+        <v>1.72283256851985</v>
       </c>
       <c r="D696" t="n">
-        <v>1.3520100377015</v>
+        <v>1.3994705361737</v>
       </c>
       <c r="E696" t="n">
-        <v>0.858107806991901</v>
+        <v>0.862605744994606</v>
       </c>
       <c r="F696" t="s">
         <v>44</v>
@@ -14405,13 +14405,13 @@
         <v>11</v>
       </c>
       <c r="C697" t="n">
-        <v>0.328319904981652</v>
+        <v>0.332506558456472</v>
       </c>
       <c r="D697" t="n">
-        <v>0.402550230902758</v>
+        <v>0.265576087211568</v>
       </c>
       <c r="E697" t="n">
-        <v>0.33095756267949</v>
+        <v>0.338345165103758</v>
       </c>
       <c r="F697" t="s">
         <v>44</v>
@@ -14425,13 +14425,13 @@
         <v>7</v>
       </c>
       <c r="C698" t="n">
-        <v>21.8815000080463</v>
+        <v>21.8815000052948</v>
       </c>
       <c r="D698" t="n">
-        <v>26.0555405362799</v>
+        <v>26.0555405110061</v>
       </c>
       <c r="E698" t="n">
-        <v>22.2378888506215</v>
+        <v>22.2378888459962</v>
       </c>
       <c r="F698" t="s">
         <v>45</v>
@@ -14445,13 +14445,13 @@
         <v>9</v>
       </c>
       <c r="C699" t="n">
-        <v>8.74130683772689</v>
+        <v>8.74130683392756</v>
       </c>
       <c r="D699" t="n">
-        <v>7.15045537729743</v>
+        <v>7.1504553695372</v>
       </c>
       <c r="E699" t="n">
-        <v>8.61990666446295</v>
+        <v>8.61990666038207</v>
       </c>
       <c r="F699" t="s">
         <v>45</v>
@@ -14465,13 +14465,13 @@
         <v>10</v>
       </c>
       <c r="C700" t="n">
-        <v>2.19996373308916</v>
+        <v>2.19996373210633</v>
       </c>
       <c r="D700" t="n">
-        <v>1.78758111982536</v>
+        <v>1.78758112477888</v>
       </c>
       <c r="E700" t="n">
-        <v>2.14480727588242</v>
+        <v>2.14480727563598</v>
       </c>
       <c r="F700" t="s">
         <v>45</v>
@@ -14485,13 +14485,13 @@
         <v>11</v>
       </c>
       <c r="C701" t="n">
-        <v>0.38456793417754</v>
+        <v>0.384567934594496</v>
       </c>
       <c r="D701" t="n">
-        <v>0.0690832078563789</v>
+        <v>0.0690832089801277</v>
       </c>
       <c r="E701" t="n">
-        <v>0.37736569265741</v>
+        <v>0.377365693186805</v>
       </c>
       <c r="F701" t="s">
         <v>45</v>
@@ -14585,13 +14585,13 @@
         <v>7</v>
       </c>
       <c r="C706" t="n">
-        <v>25.3712213195231</v>
+        <v>25.3712213195241</v>
       </c>
       <c r="D706" t="n">
-        <v>29.2044413185475</v>
+        <v>29.2044413185334</v>
       </c>
       <c r="E706" t="n">
-        <v>25.6785038133403</v>
+        <v>25.6785038133402</v>
       </c>
       <c r="F706" t="s">
         <v>45</v>
@@ -14605,13 +14605,13 @@
         <v>9</v>
       </c>
       <c r="C707" t="n">
-        <v>9.4776317948963</v>
+        <v>9.47763179489616</v>
       </c>
       <c r="D707" t="n">
-        <v>8.64396637000967</v>
+        <v>8.64396637000405</v>
       </c>
       <c r="E707" t="n">
-        <v>9.41762638528284</v>
+        <v>9.41762638528231</v>
       </c>
       <c r="F707" t="s">
         <v>45</v>
@@ -14625,13 +14625,13 @@
         <v>10</v>
       </c>
       <c r="C708" t="n">
-        <v>1.98855313830054</v>
+        <v>1.98855313830325</v>
       </c>
       <c r="D708" t="n">
-        <v>1.99635624029299</v>
+        <v>1.99635624029603</v>
       </c>
       <c r="E708" t="n">
-        <v>1.98988180535368</v>
+        <v>1.98988180535639</v>
       </c>
       <c r="F708" t="s">
         <v>45</v>
@@ -14645,13 +14645,13 @@
         <v>11</v>
       </c>
       <c r="C709" t="n">
-        <v>0.284126010502879</v>
+        <v>0.284126010502806</v>
       </c>
       <c r="D709" t="n">
-        <v>0.00737789540579587</v>
+        <v>0.00737789540579145</v>
       </c>
       <c r="E709" t="n">
-        <v>0.267405724905805</v>
+        <v>0.267405724905777</v>
       </c>
       <c r="F709" t="s">
         <v>45</v>
@@ -14745,13 +14745,13 @@
         <v>7</v>
       </c>
       <c r="C714" t="n">
-        <v>21.9522816618154</v>
+        <v>21.9434645850837</v>
       </c>
       <c r="D714" t="n">
-        <v>24.6446430630726</v>
+        <v>24.2494421528437</v>
       </c>
       <c r="E714" t="n">
-        <v>22.1964759999751</v>
+        <v>22.1554545918566</v>
       </c>
       <c r="F714" t="s">
         <v>45</v>
@@ -14765,13 +14765,13 @@
         <v>9</v>
       </c>
       <c r="C715" t="n">
-        <v>8.6353083624111</v>
+        <v>8.64586068245589</v>
       </c>
       <c r="D715" t="n">
-        <v>7.03345537743943</v>
+        <v>6.9168909256052</v>
       </c>
       <c r="E715" t="n">
-        <v>8.51410550738698</v>
+        <v>8.51598420473111</v>
       </c>
       <c r="F715" t="s">
         <v>45</v>
@@ -14785,13 +14785,13 @@
         <v>10</v>
       </c>
       <c r="C716" t="n">
-        <v>2.18781886403453</v>
+        <v>2.16891819096406</v>
       </c>
       <c r="D716" t="n">
-        <v>2.16524201581262</v>
+        <v>1.97500054830459</v>
       </c>
       <c r="E716" t="n">
-        <v>2.16642665327541</v>
+        <v>2.13053936318418</v>
       </c>
       <c r="F716" t="s">
         <v>45</v>
@@ -14805,13 +14805,13 @@
         <v>11</v>
       </c>
       <c r="C717" t="n">
-        <v>0.380781894778415</v>
+        <v>0.379128874986925</v>
       </c>
       <c r="D717" t="n">
-        <v>0.0960615564761138</v>
+        <v>0.123107273411533</v>
       </c>
       <c r="E717" t="n">
-        <v>0.374622267090216</v>
+        <v>0.374203220436882</v>
       </c>
       <c r="F717" t="s">
         <v>45</v>
@@ -14825,13 +14825,13 @@
         <v>7</v>
       </c>
       <c r="C718" t="n">
-        <v>28.7944180987541</v>
+        <v>28.7839766552414</v>
       </c>
       <c r="D718" t="n">
-        <v>45.0038944348788</v>
+        <v>47.950948573381</v>
       </c>
       <c r="E718" t="n">
-        <v>30.0661598320207</v>
+        <v>30.2828294709212</v>
       </c>
       <c r="F718" t="s">
         <v>45</v>
@@ -14845,13 +14845,13 @@
         <v>9</v>
       </c>
       <c r="C719" t="n">
-        <v>10.4418791419132</v>
+        <v>10.4568255307898</v>
       </c>
       <c r="D719" t="n">
-        <v>14.5392444313716</v>
+        <v>16.1151329697938</v>
       </c>
       <c r="E719" t="n">
-        <v>10.8197865727438</v>
+        <v>11.0042104471879</v>
       </c>
       <c r="F719" t="s">
         <v>45</v>
@@ -14865,13 +14865,13 @@
         <v>10</v>
       </c>
       <c r="C720" t="n">
-        <v>0.922762113118481</v>
+        <v>0.924127469915577</v>
       </c>
       <c r="D720" t="n">
-        <v>4.39143483195116</v>
+        <v>5.80476776361284</v>
       </c>
       <c r="E720" t="n">
-        <v>1.39482168253801</v>
+        <v>1.4047447483676</v>
       </c>
       <c r="F720" t="s">
         <v>45</v>
@@ -14885,13 +14885,13 @@
         <v>11</v>
       </c>
       <c r="C721" t="n">
-        <v>0.257248230869986</v>
+        <v>0.259485414875235</v>
       </c>
       <c r="D721" t="n">
-        <v>0.00893132648937898</v>
+        <v>0.0339937301720044</v>
       </c>
       <c r="E721" t="n">
-        <v>0.211256446683246</v>
+        <v>0.203104890709538</v>
       </c>
       <c r="F721" t="s">
         <v>45</v>
@@ -14905,13 +14905,13 @@
         <v>7</v>
       </c>
       <c r="C722" t="n">
-        <v>74.5496741343836</v>
+        <v>74.5496851936315</v>
       </c>
       <c r="D722" t="n">
-        <v>110.266147459967</v>
+        <v>110.266160827828</v>
       </c>
       <c r="E722" t="n">
-        <v>84.6958849417133</v>
+        <v>84.6958950184202</v>
       </c>
       <c r="F722" t="s">
         <v>46</v>
@@ -14925,13 +14925,13 @@
         <v>9</v>
       </c>
       <c r="C723" t="n">
-        <v>15.2746204381008</v>
+        <v>15.2746280532596</v>
       </c>
       <c r="D723" t="n">
-        <v>1.1616936479167</v>
+        <v>1.16169368178109</v>
       </c>
       <c r="E723" t="n">
-        <v>14.6283586323962</v>
+        <v>14.6283659216303</v>
       </c>
       <c r="F723" t="s">
         <v>46</v>
@@ -14945,13 +14945,13 @@
         <v>10</v>
       </c>
       <c r="C724" t="n">
-        <v>0.488392192209328</v>
+        <v>0.488392706043816</v>
       </c>
       <c r="D724" t="n">
-        <v>0.996046981902479</v>
+        <v>0.996047043641688</v>
       </c>
       <c r="E724" t="n">
-        <v>0.491617963045089</v>
+        <v>0.49161847692678</v>
       </c>
       <c r="F724" t="s">
         <v>46</v>
@@ -14965,13 +14965,13 @@
         <v>11</v>
       </c>
       <c r="C725" t="n">
-        <v>0.905496914189569</v>
+        <v>0.905496976415222</v>
       </c>
       <c r="D725" t="n">
-        <v>0.0707847487965082</v>
+        <v>0.0707847726569275</v>
       </c>
       <c r="E725" t="n">
-        <v>0.908251910116717</v>
+        <v>0.908251970000418</v>
       </c>
       <c r="F725" t="s">
         <v>46</v>
@@ -15221,13 +15221,13 @@
         <v>7</v>
       </c>
       <c r="C738" t="n">
-        <v>101.074088967889</v>
+        <v>97.5962904261957</v>
       </c>
       <c r="D738" t="n">
-        <v>136.194624406831</v>
+        <v>144.361763915872</v>
       </c>
       <c r="E738" t="n">
-        <v>107.828913997597</v>
+        <v>104.627526090114</v>
       </c>
       <c r="F738" t="s">
         <v>46</v>
@@ -15241,13 +15241,13 @@
         <v>9</v>
       </c>
       <c r="C739" t="n">
-        <v>36.2214801333837</v>
+        <v>33.8090269399893</v>
       </c>
       <c r="D739" t="n">
-        <v>0.713096871704566</v>
+        <v>0.902537866902892</v>
       </c>
       <c r="E739" t="n">
-        <v>34.6801128120371</v>
+        <v>32.3708573406662</v>
       </c>
       <c r="F739" t="s">
         <v>46</v>
@@ -15261,13 +15261,13 @@
         <v>10</v>
       </c>
       <c r="C740" t="n">
-        <v>5.2770341134594</v>
+        <v>4.32710414626166</v>
       </c>
       <c r="D740" t="n">
-        <v>4.54848658204521</v>
+        <v>2.26292011131944</v>
       </c>
       <c r="E740" t="n">
-        <v>5.27927375022824</v>
+        <v>4.31519776772578</v>
       </c>
       <c r="F740" t="s">
         <v>46</v>
@@ -15281,13 +15281,13 @@
         <v>11</v>
       </c>
       <c r="C741" t="n">
-        <v>0.220729862901934</v>
+        <v>0.348220211837567</v>
       </c>
       <c r="D741" t="n">
-        <v>0.180397218639742</v>
+        <v>0.160193324493098</v>
       </c>
       <c r="E741" t="n">
-        <v>0.242159472979757</v>
+        <v>0.367732360754143</v>
       </c>
       <c r="F741" t="s">
         <v>46</v>
@@ -15301,13 +15301,13 @@
         <v>7</v>
       </c>
       <c r="C742" t="n">
-        <v>138.282730455631</v>
+        <v>135.840061989337</v>
       </c>
       <c r="D742" t="n">
-        <v>198.506266898282</v>
+        <v>197.608927852252</v>
       </c>
       <c r="E742" t="n">
-        <v>143.030212728275</v>
+        <v>140.775441836311</v>
       </c>
       <c r="F742" t="s">
         <v>46</v>
@@ -15321,13 +15321,13 @@
         <v>9</v>
       </c>
       <c r="C743" t="n">
-        <v>52.1250056928413</v>
+        <v>52.2541282777115</v>
       </c>
       <c r="D743" t="n">
-        <v>11.3841262354717</v>
+        <v>10.441919190037</v>
       </c>
       <c r="E743" t="n">
-        <v>50.1784955459815</v>
+        <v>50.287577405782</v>
       </c>
       <c r="F743" t="s">
         <v>46</v>
@@ -15341,13 +15341,13 @@
         <v>10</v>
       </c>
       <c r="C744" t="n">
-        <v>1.19602587273968</v>
+        <v>1.18082074302505</v>
       </c>
       <c r="D744" t="n">
-        <v>1.09287589351031</v>
+        <v>0.843016536111196</v>
       </c>
       <c r="E744" t="n">
-        <v>1.47077824797111</v>
+        <v>1.39908637917265</v>
       </c>
       <c r="F744" t="s">
         <v>46</v>
@@ -15361,13 +15361,13 @@
         <v>11</v>
       </c>
       <c r="C745" t="n">
-        <v>0.0251195955469296</v>
+        <v>0.0292077405751921</v>
       </c>
       <c r="D745" t="n">
-        <v>0.00279117393445031</v>
+        <v>0.0240445436380271</v>
       </c>
       <c r="E745" t="n">
-        <v>0.036136580507384</v>
+        <v>0.0379232141950686</v>
       </c>
       <c r="F745" t="s">
         <v>46</v>
@@ -15381,13 +15381,13 @@
         <v>7</v>
       </c>
       <c r="C746" t="n">
-        <v>1.01852488634407</v>
+        <v>1.01852488634797</v>
       </c>
       <c r="D746" t="n">
-        <v>19.1212716506196</v>
+        <v>19.1212716505614</v>
       </c>
       <c r="E746" t="n">
-        <v>2.55639397860138</v>
+        <v>2.55639397859999</v>
       </c>
       <c r="F746" t="s">
         <v>47</v>
@@ -15401,13 +15401,13 @@
         <v>9</v>
       </c>
       <c r="C747" t="n">
-        <v>3.57147057122859</v>
+        <v>3.57147057363787</v>
       </c>
       <c r="D747" t="n">
-        <v>8.3042518094478</v>
+        <v>8.30425180944199</v>
       </c>
       <c r="E747" t="n">
-        <v>4.18839432480129</v>
+        <v>4.18839432667995</v>
       </c>
       <c r="F747" t="s">
         <v>47</v>
@@ -15421,13 +15421,13 @@
         <v>10</v>
       </c>
       <c r="C748" t="n">
-        <v>0.0330635079809155</v>
+        <v>0.0330635079925863</v>
       </c>
       <c r="D748" t="n">
-        <v>1.5075795229427</v>
+        <v>1.5075795229213</v>
       </c>
       <c r="E748" t="n">
-        <v>0.0571203829957798</v>
+        <v>0.0571203830077393</v>
       </c>
       <c r="F748" t="s">
         <v>47</v>
@@ -15441,13 +15441,13 @@
         <v>11</v>
       </c>
       <c r="C749" t="n">
-        <v>0.999231291650089</v>
+        <v>0.99923129165022</v>
       </c>
       <c r="D749" t="n">
-        <v>0.01743581358724</v>
+        <v>0.0174358135886194</v>
       </c>
       <c r="E749" t="n">
-        <v>0.998341670138835</v>
+        <v>0.998341670138915</v>
       </c>
       <c r="F749" t="s">
         <v>47</v>
@@ -15541,13 +15541,13 @@
         <v>7</v>
       </c>
       <c r="C754" t="n">
-        <v>24.4036401129978</v>
+        <v>24.403640113</v>
       </c>
       <c r="D754" t="n">
-        <v>13.2262787166151</v>
+        <v>13.2262787166578</v>
       </c>
       <c r="E754" t="n">
-        <v>23.5440787032514</v>
+        <v>23.5440787032567</v>
       </c>
       <c r="F754" t="s">
         <v>47</v>
@@ -15561,13 +15561,13 @@
         <v>9</v>
       </c>
       <c r="C755" t="n">
-        <v>81.0342052462198</v>
+        <v>81.0342052462363</v>
       </c>
       <c r="D755" t="n">
-        <v>5.2943447112519</v>
+        <v>5.29434471127941</v>
       </c>
       <c r="E755" t="n">
-        <v>77.8690218981678</v>
+        <v>77.8690218981837</v>
       </c>
       <c r="F755" t="s">
         <v>47</v>
@@ -15581,13 +15581,13 @@
         <v>10</v>
       </c>
       <c r="C756" t="n">
-        <v>2.84491234246177</v>
+        <v>2.84491234246869</v>
       </c>
       <c r="D756" t="n">
-        <v>0.843772661376035</v>
+        <v>0.843772661376405</v>
       </c>
       <c r="E756" t="n">
-        <v>2.68234585825962</v>
+        <v>2.68234585826491</v>
       </c>
       <c r="F756" t="s">
         <v>47</v>
@@ -15601,13 +15601,13 @@
         <v>11</v>
       </c>
       <c r="C757" t="n">
-        <v>0.0924970261694893</v>
+        <v>0.0924970261686534</v>
       </c>
       <c r="D757" t="n">
-        <v>0.347827834287012</v>
+        <v>0.347827834286155</v>
       </c>
       <c r="E757" t="n">
-        <v>0.0873602033717531</v>
+        <v>0.0873602033708447</v>
       </c>
       <c r="F757" t="s">
         <v>47</v>
@@ -15701,13 +15701,13 @@
         <v>7</v>
       </c>
       <c r="C762" t="n">
-        <v>23.1472713151434</v>
+        <v>23.1251214406932</v>
       </c>
       <c r="D762" t="n">
-        <v>10.0045560340318</v>
+        <v>9.85908116925354</v>
       </c>
       <c r="E762" t="n">
-        <v>22.0293495603058</v>
+        <v>21.9967007072284</v>
       </c>
       <c r="F762" t="s">
         <v>47</v>
@@ -15721,13 +15721,13 @@
         <v>9</v>
       </c>
       <c r="C763" t="n">
-        <v>78.8100909890966</v>
+        <v>79.4241414793941</v>
       </c>
       <c r="D763" t="n">
-        <v>3.9099173846891</v>
+        <v>3.87630180601468</v>
       </c>
       <c r="E763" t="n">
-        <v>75.3905216162053</v>
+        <v>75.9776619182829</v>
       </c>
       <c r="F763" t="s">
         <v>47</v>
@@ -15741,13 +15741,13 @@
         <v>10</v>
       </c>
       <c r="C764" t="n">
-        <v>2.14558480502146</v>
+        <v>2.15053305598156</v>
       </c>
       <c r="D764" t="n">
-        <v>0.707546065933654</v>
+        <v>0.679795410844383</v>
       </c>
       <c r="E764" t="n">
-        <v>2.05155180808395</v>
+        <v>2.05237498230059</v>
       </c>
       <c r="F764" t="s">
         <v>47</v>
@@ -15761,13 +15761,13 @@
         <v>11</v>
       </c>
       <c r="C765" t="n">
-        <v>0.428613888607033</v>
+        <v>0.390521709564485</v>
       </c>
       <c r="D765" t="n">
-        <v>0.625180986286758</v>
+        <v>0.62248075509897</v>
       </c>
       <c r="E765" t="n">
-        <v>0.423665045887279</v>
+        <v>0.386029847716095</v>
       </c>
       <c r="F765" t="s">
         <v>47</v>
@@ -15781,13 +15781,13 @@
         <v>7</v>
       </c>
       <c r="C766" t="n">
-        <v>42.6828485932797</v>
+        <v>48.5685855772973</v>
       </c>
       <c r="D766" t="n">
-        <v>66.2725029311157</v>
+        <v>87.6498362994409</v>
       </c>
       <c r="E766" t="n">
-        <v>44.493084255689</v>
+        <v>51.5735138474725</v>
       </c>
       <c r="F766" t="s">
         <v>47</v>
@@ -15801,13 +15801,13 @@
         <v>9</v>
       </c>
       <c r="C767" t="n">
-        <v>86.7352717702064</v>
+        <v>87.4041838489685</v>
       </c>
       <c r="D767" t="n">
-        <v>25.6047337316772</v>
+        <v>29.3513588419635</v>
       </c>
       <c r="E767" t="n">
-        <v>83.6343408978958</v>
+        <v>84.3679190724133</v>
       </c>
       <c r="F767" t="s">
         <v>47</v>
@@ -15821,13 +15821,13 @@
         <v>10</v>
       </c>
       <c r="C768" t="n">
-        <v>1.21677679014252</v>
+        <v>1.2542941128315</v>
       </c>
       <c r="D768" t="n">
-        <v>0.75306143654388</v>
+        <v>0.882620294739937</v>
       </c>
       <c r="E768" t="n">
-        <v>1.82942501749294</v>
+        <v>1.73392254484749</v>
       </c>
       <c r="F768" t="s">
         <v>47</v>
@@ -15841,13 +15841,13 @@
         <v>11</v>
       </c>
       <c r="C769" t="n">
-        <v>0.000600879638029355</v>
+        <v>0.00862108319023408</v>
       </c>
       <c r="D769" t="n">
-        <v>0.535042559087938</v>
+        <v>0.404421222569307</v>
       </c>
       <c r="E769" t="n">
-        <v>0.00102307913022737</v>
+        <v>0.00941605308020558</v>
       </c>
       <c r="F769" t="s">
         <v>47</v>
@@ -15861,13 +15861,13 @@
         <v>7</v>
       </c>
       <c r="C770" t="n">
-        <v>16.241952423165</v>
+        <v>16.24197644869</v>
       </c>
       <c r="D770" t="n">
-        <v>18.7180373342835</v>
+        <v>18.7180728541705</v>
       </c>
       <c r="E770" t="n">
-        <v>16.4450100611845</v>
+        <v>16.4450350484747</v>
       </c>
       <c r="F770" t="s">
         <v>48</v>
@@ -15881,13 +15881,13 @@
         <v>9</v>
       </c>
       <c r="C771" t="n">
-        <v>48.2418290183243</v>
+        <v>48.2417786860285</v>
       </c>
       <c r="D771" t="n">
-        <v>20.7518361369209</v>
+        <v>20.7518091636642</v>
       </c>
       <c r="E771" t="n">
-        <v>46.5739808195638</v>
+        <v>46.5739319907034</v>
       </c>
       <c r="F771" t="s">
         <v>48</v>
@@ -15901,13 +15901,13 @@
         <v>10</v>
       </c>
       <c r="C772" t="n">
-        <v>1.18228742784224</v>
+        <v>1.18227694574025</v>
       </c>
       <c r="D772" t="n">
-        <v>2.10660403136051</v>
+        <v>2.1066659218765</v>
       </c>
       <c r="E772" t="n">
-        <v>1.20364966706867</v>
+        <v>1.2036404030113</v>
       </c>
       <c r="F772" t="s">
         <v>48</v>
@@ -15921,13 +15921,13 @@
         <v>11</v>
       </c>
       <c r="C773" t="n">
-        <v>0.80650864739386</v>
+        <v>0.806508611367844</v>
       </c>
       <c r="D773" t="n">
-        <v>0.192973352876702</v>
+        <v>0.192980704443949</v>
       </c>
       <c r="E773" t="n">
-        <v>0.823079017729665</v>
+        <v>0.823079028992077</v>
       </c>
       <c r="F773" t="s">
         <v>48</v>
@@ -16021,13 +16021,13 @@
         <v>7</v>
       </c>
       <c r="C778" t="n">
-        <v>13.8847476552377</v>
+        <v>13.8849658113467</v>
       </c>
       <c r="D778" t="n">
-        <v>17.5449282359564</v>
+        <v>17.5408409490639</v>
       </c>
       <c r="E778" t="n">
-        <v>14.1725958269243</v>
+        <v>14.1724828493422</v>
       </c>
       <c r="F778" t="s">
         <v>48</v>
@@ -16041,13 +16041,13 @@
         <v>9</v>
       </c>
       <c r="C779" t="n">
-        <v>41.2598356841282</v>
+        <v>41.2606419097331</v>
       </c>
       <c r="D779" t="n">
-        <v>20.5456726493536</v>
+        <v>20.5416432474072</v>
       </c>
       <c r="E779" t="n">
-        <v>40.0511943928984</v>
+        <v>40.0518006623471</v>
       </c>
       <c r="F779" t="s">
         <v>48</v>
@@ -16061,13 +16061,13 @@
         <v>10</v>
       </c>
       <c r="C780" t="n">
-        <v>0.660389217427071</v>
+        <v>0.660391122572139</v>
       </c>
       <c r="D780" t="n">
-        <v>1.06363944995845</v>
+        <v>1.06337868630626</v>
       </c>
       <c r="E780" t="n">
-        <v>0.6680239228077</v>
+        <v>0.668018499241957</v>
       </c>
       <c r="F780" t="s">
         <v>48</v>
@@ -16081,13 +16081,13 @@
         <v>11</v>
       </c>
       <c r="C781" t="n">
-        <v>0.859273420942685</v>
+        <v>0.859267822776364</v>
       </c>
       <c r="D781" t="n">
-        <v>0.52213075071898</v>
+        <v>0.52207058565052</v>
       </c>
       <c r="E781" t="n">
-        <v>0.869694654470498</v>
+        <v>0.869690987366609</v>
       </c>
       <c r="F781" t="s">
         <v>48</v>
@@ -16181,13 +16181,13 @@
         <v>7</v>
       </c>
       <c r="C786" t="n">
-        <v>13.6060510091698</v>
+        <v>13.6080749213698</v>
       </c>
       <c r="D786" t="n">
-        <v>18.3516468060807</v>
+        <v>18.3251448137443</v>
       </c>
       <c r="E786" t="n">
-        <v>14.0100477640445</v>
+        <v>14.0096952464408</v>
       </c>
       <c r="F786" t="s">
         <v>48</v>
@@ -16201,13 +16201,13 @@
         <v>9</v>
       </c>
       <c r="C787" t="n">
-        <v>39.4689801212483</v>
+        <v>39.5023713085201</v>
       </c>
       <c r="D787" t="n">
-        <v>20.2740841453893</v>
+        <v>20.2391164313534</v>
       </c>
       <c r="E787" t="n">
-        <v>38.2424595881377</v>
+        <v>38.2725038129124</v>
       </c>
       <c r="F787" t="s">
         <v>48</v>
@@ -16221,13 +16221,13 @@
         <v>10</v>
       </c>
       <c r="C788" t="n">
-        <v>0.836093922849565</v>
+        <v>0.835294920181446</v>
       </c>
       <c r="D788" t="n">
-        <v>1.34207493262015</v>
+        <v>1.3377984438536</v>
       </c>
       <c r="E788" t="n">
-        <v>0.846740101214315</v>
+        <v>0.845836803120427</v>
       </c>
       <c r="F788" t="s">
         <v>48</v>
@@ -16241,13 +16241,13 @@
         <v>11</v>
       </c>
       <c r="C789" t="n">
-        <v>0.869588693343382</v>
+        <v>0.86942434640944</v>
       </c>
       <c r="D789" t="n">
-        <v>0.624385400417103</v>
+        <v>0.626099753585607</v>
       </c>
       <c r="E789" t="n">
-        <v>0.879497494570376</v>
+        <v>0.879346726700028</v>
       </c>
       <c r="F789" t="s">
         <v>48</v>
@@ -16261,13 +16261,13 @@
         <v>7</v>
       </c>
       <c r="C790" t="n">
-        <v>21.6246106900817</v>
+        <v>21.6344781763459</v>
       </c>
       <c r="D790" t="n">
-        <v>49.6776349544864</v>
+        <v>30.2591354907038</v>
       </c>
       <c r="E790" t="n">
-        <v>23.7910585479646</v>
+        <v>22.3052382222646</v>
       </c>
       <c r="F790" t="s">
         <v>48</v>
@@ -16281,13 +16281,13 @@
         <v>9</v>
       </c>
       <c r="C791" t="n">
-        <v>54.8390638703924</v>
+        <v>54.8819112433429</v>
       </c>
       <c r="D791" t="n">
-        <v>60.7742945767897</v>
+        <v>40.4039264769725</v>
       </c>
       <c r="E791" t="n">
-        <v>55.3264889124416</v>
+        <v>53.9112637253594</v>
       </c>
       <c r="F791" t="s">
         <v>48</v>
@@ -16301,13 +16301,13 @@
         <v>10</v>
       </c>
       <c r="C792" t="n">
-        <v>0.977129207857646</v>
+        <v>0.978008443803872</v>
       </c>
       <c r="D792" t="n">
-        <v>2.42649787162774</v>
+        <v>1.20492828607471</v>
       </c>
       <c r="E792" t="n">
-        <v>0.876841216252887</v>
+        <v>0.825840655956387</v>
       </c>
       <c r="F792" t="s">
         <v>48</v>
@@ -16321,13 +16321,13 @@
         <v>11</v>
       </c>
       <c r="C793" t="n">
-        <v>0.765459377631343</v>
+        <v>0.766239725567495</v>
       </c>
       <c r="D793" t="n">
-        <v>0.945264973503894</v>
+        <v>0.82963454539243</v>
       </c>
       <c r="E793" t="n">
-        <v>0.760852804811646</v>
+        <v>0.774784236308828</v>
       </c>
       <c r="F793" t="s">
         <v>48</v>
@@ -16341,13 +16341,13 @@
         <v>7</v>
       </c>
       <c r="C794" t="n">
-        <v>14.1930614675944</v>
+        <v>14.1930614571481</v>
       </c>
       <c r="D794" t="n">
-        <v>25.7951045955058</v>
+        <v>25.7951040757375</v>
       </c>
       <c r="E794" t="n">
-        <v>15.1667974754508</v>
+        <v>15.1667974225718</v>
       </c>
       <c r="F794" t="s">
         <v>49</v>
@@ -16361,13 +16361,13 @@
         <v>9</v>
       </c>
       <c r="C795" t="n">
-        <v>44.6752343561706</v>
+        <v>44.6752343851291</v>
       </c>
       <c r="D795" t="n">
-        <v>34.8713772454694</v>
+        <v>34.8713770301034</v>
       </c>
       <c r="E795" t="n">
-        <v>43.9454964251297</v>
+        <v>43.9454964376924</v>
       </c>
       <c r="F795" t="s">
         <v>49</v>
@@ -16381,13 +16381,13 @@
         <v>10</v>
       </c>
       <c r="C796" t="n">
-        <v>1.19301032013302</v>
+        <v>1.19301032099618</v>
       </c>
       <c r="D796" t="n">
-        <v>2.81634057508948</v>
+        <v>2.81634048347568</v>
       </c>
       <c r="E796" t="n">
-        <v>1.21304947328195</v>
+        <v>1.21304947245927</v>
       </c>
       <c r="F796" t="s">
         <v>49</v>
@@ -16401,13 +16401,13 @@
         <v>11</v>
       </c>
       <c r="C797" t="n">
-        <v>0.803319999161684</v>
+        <v>0.80331999923216</v>
       </c>
       <c r="D797" t="n">
-        <v>0.138049660196578</v>
+        <v>0.138049661126041</v>
       </c>
       <c r="E797" t="n">
-        <v>0.841018392572907</v>
+        <v>0.841018392570262</v>
       </c>
       <c r="F797" t="s">
         <v>49</v>
@@ -16501,13 +16501,13 @@
         <v>7</v>
       </c>
       <c r="C802" t="n">
-        <v>12.5661698597069</v>
+        <v>12.5661698573688</v>
       </c>
       <c r="D802" t="n">
-        <v>52.6869856320303</v>
+        <v>52.6869856646814</v>
       </c>
       <c r="E802" t="n">
-        <v>15.6640466998769</v>
+        <v>15.6640467002293</v>
       </c>
       <c r="F802" t="s">
         <v>49</v>
@@ -16521,13 +16521,13 @@
         <v>9</v>
       </c>
       <c r="C803" t="n">
-        <v>40.8522564807206</v>
+        <v>40.8522564755207</v>
       </c>
       <c r="D803" t="n">
-        <v>50.954783240498</v>
+        <v>50.9547832795392</v>
       </c>
       <c r="E803" t="n">
-        <v>41.7250443678044</v>
+        <v>41.7250443667797</v>
       </c>
       <c r="F803" t="s">
         <v>49</v>
@@ -16541,13 +16541,13 @@
         <v>10</v>
       </c>
       <c r="C804" t="n">
-        <v>0.651416681383834</v>
+        <v>0.651416681312485</v>
       </c>
       <c r="D804" t="n">
-        <v>2.42350800923104</v>
+        <v>2.42350800856534</v>
       </c>
       <c r="E804" t="n">
-        <v>0.708677726262871</v>
+        <v>0.708677726256792</v>
       </c>
       <c r="F804" t="s">
         <v>49</v>
@@ -16561,13 +16561,13 @@
         <v>11</v>
       </c>
       <c r="C805" t="n">
-        <v>0.854699004176855</v>
+        <v>0.85469900421431</v>
       </c>
       <c r="D805" t="n">
-        <v>0.679307662339061</v>
+        <v>0.679307663230822</v>
       </c>
       <c r="E805" t="n">
-        <v>0.871568437810209</v>
+        <v>0.871568437816517</v>
       </c>
       <c r="F805" t="s">
         <v>49</v>
@@ -16661,13 +16661,13 @@
         <v>7</v>
       </c>
       <c r="C810" t="n">
-        <v>11.8560908567695</v>
+        <v>11.8967569417449</v>
       </c>
       <c r="D810" t="n">
-        <v>44.8780636482294</v>
+        <v>44.2571845097811</v>
       </c>
       <c r="E810" t="n">
-        <v>14.620802146126</v>
+        <v>14.6063525360916</v>
       </c>
       <c r="F810" t="s">
         <v>49</v>
@@ -16681,13 +16681,13 @@
         <v>9</v>
       </c>
       <c r="C811" t="n">
-        <v>37.616127958297</v>
+        <v>37.679472297334</v>
       </c>
       <c r="D811" t="n">
-        <v>42.687840465235</v>
+        <v>42.6859392960828</v>
       </c>
       <c r="E811" t="n">
-        <v>38.073058191125</v>
+        <v>38.130165288055</v>
       </c>
       <c r="F811" t="s">
         <v>49</v>
@@ -16701,13 +16701,13 @@
         <v>10</v>
       </c>
       <c r="C812" t="n">
-        <v>0.853358755109888</v>
+        <v>0.858768199488681</v>
       </c>
       <c r="D812" t="n">
-        <v>2.92479514632425</v>
+        <v>2.8647034248186</v>
       </c>
       <c r="E812" t="n">
-        <v>0.914274253012998</v>
+        <v>0.918103365324329</v>
       </c>
       <c r="F812" t="s">
         <v>49</v>
@@ -16721,13 +16721,13 @@
         <v>11</v>
       </c>
       <c r="C813" t="n">
-        <v>0.859980939563706</v>
+        <v>0.85951067914607</v>
       </c>
       <c r="D813" t="n">
-        <v>0.608851844708362</v>
+        <v>0.590781202043455</v>
       </c>
       <c r="E813" t="n">
-        <v>0.882430260752599</v>
+        <v>0.881993871018678</v>
       </c>
       <c r="F813" t="s">
         <v>49</v>
@@ -16741,13 +16741,13 @@
         <v>7</v>
       </c>
       <c r="C814" t="n">
-        <v>15.6336774361733</v>
+        <v>15.9946534913457</v>
       </c>
       <c r="D814" t="n">
-        <v>53.7078065575815</v>
+        <v>50.2268820094321</v>
       </c>
       <c r="E814" t="n">
-        <v>18.5685351040853</v>
+        <v>18.6368550327225</v>
       </c>
       <c r="F814" t="s">
         <v>49</v>
@@ -16761,13 +16761,13 @@
         <v>9</v>
       </c>
       <c r="C815" t="n">
-        <v>53.6923816513437</v>
+        <v>53.9223306801374</v>
       </c>
       <c r="D815" t="n">
-        <v>75.5786338451966</v>
+        <v>66.4787387520755</v>
       </c>
       <c r="E815" t="n">
-        <v>55.6904168888441</v>
+        <v>54.9975174325913</v>
       </c>
       <c r="F815" t="s">
         <v>49</v>
@@ -16781,13 +16781,13 @@
         <v>10</v>
       </c>
       <c r="C816" t="n">
-        <v>0.877195551595265</v>
+        <v>0.887210794833109</v>
       </c>
       <c r="D816" t="n">
-        <v>2.19179294175973</v>
+        <v>2.31675216748303</v>
       </c>
       <c r="E816" t="n">
-        <v>0.796185326007489</v>
+        <v>0.802404724022393</v>
       </c>
       <c r="F816" t="s">
         <v>49</v>
@@ -16801,13 +16801,13 @@
         <v>11</v>
       </c>
       <c r="C817" t="n">
-        <v>0.785905151311388</v>
+        <v>0.784633152721864</v>
       </c>
       <c r="D817" t="n">
-        <v>0.641581323857156</v>
+        <v>0.602170562017088</v>
       </c>
       <c r="E817" t="n">
-        <v>0.79227331486382</v>
+        <v>0.797189886915738</v>
       </c>
       <c r="F817" t="s">
         <v>49</v>
@@ -16821,13 +16821,13 @@
         <v>7</v>
       </c>
       <c r="C818" t="n">
-        <v>11.5804404861869</v>
+        <v>11.5804405020339</v>
       </c>
       <c r="D818" t="n">
-        <v>19.34251587532</v>
+        <v>19.3425164376076</v>
       </c>
       <c r="E818" t="n">
-        <v>12.232868771347</v>
+        <v>12.2328688327275</v>
       </c>
       <c r="F818" t="s">
         <v>50</v>
@@ -16841,13 +16841,13 @@
         <v>9</v>
       </c>
       <c r="C819" t="n">
-        <v>37.7544633885708</v>
+        <v>37.7544634105064</v>
       </c>
       <c r="D819" t="n">
-        <v>35.0462861865691</v>
+        <v>35.0462871083787</v>
       </c>
       <c r="E819" t="n">
-        <v>37.5431352134416</v>
+        <v>37.5431353056004</v>
       </c>
       <c r="F819" t="s">
         <v>50</v>
@@ -16861,13 +16861,13 @@
         <v>10</v>
       </c>
       <c r="C820" t="n">
-        <v>1.37707892754582</v>
+        <v>1.37707894789786</v>
       </c>
       <c r="D820" t="n">
-        <v>6.3200892083132</v>
+        <v>6.32008937272664</v>
       </c>
       <c r="E820" t="n">
-        <v>1.46731117291721</v>
+        <v>1.46731119777228</v>
       </c>
       <c r="F820" t="s">
         <v>50</v>
@@ -16881,13 +16881,13 @@
         <v>11</v>
       </c>
       <c r="C821" t="n">
-        <v>0.669859177573086</v>
+        <v>0.669859178578273</v>
       </c>
       <c r="D821" t="n">
-        <v>0.330253815253439</v>
+        <v>0.330253814674527</v>
       </c>
       <c r="E821" t="n">
-        <v>0.694438801333468</v>
+        <v>0.694438801701175</v>
       </c>
       <c r="F821" t="s">
         <v>50</v>
@@ -16981,13 +16981,13 @@
         <v>7</v>
       </c>
       <c r="C826" t="n">
-        <v>12.2902404643304</v>
+        <v>12.2902404643872</v>
       </c>
       <c r="D826" t="n">
-        <v>11.301582339066</v>
+        <v>11.3015823391949</v>
       </c>
       <c r="E826" t="n">
-        <v>12.2193874842901</v>
+        <v>12.2193874843525</v>
       </c>
       <c r="F826" t="s">
         <v>50</v>
@@ -17001,13 +17001,13 @@
         <v>9</v>
       </c>
       <c r="C827" t="n">
-        <v>37.8895442573571</v>
+        <v>37.8895442573931</v>
       </c>
       <c r="D827" t="n">
-        <v>24.0980451844274</v>
+        <v>24.0980451842223</v>
       </c>
       <c r="E827" t="n">
-        <v>37.0152650158106</v>
+        <v>37.0152650158344</v>
       </c>
       <c r="F827" t="s">
         <v>50</v>
@@ -17021,13 +17021,13 @@
         <v>10</v>
       </c>
       <c r="C828" t="n">
-        <v>1.05146955394049</v>
+        <v>1.05146955398465</v>
       </c>
       <c r="D828" t="n">
-        <v>1.51145309348018</v>
+        <v>1.51145309357356</v>
       </c>
       <c r="E828" t="n">
-        <v>1.0540264303168</v>
+        <v>1.05402643036191</v>
       </c>
       <c r="F828" t="s">
         <v>50</v>
@@ -17041,13 +17041,13 @@
         <v>11</v>
       </c>
       <c r="C829" t="n">
-        <v>0.668939831461973</v>
+        <v>0.668939831459178</v>
       </c>
       <c r="D829" t="n">
-        <v>0.463856918678482</v>
+        <v>0.463856918659898</v>
       </c>
       <c r="E829" t="n">
-        <v>0.695858757001913</v>
+        <v>0.695858757000019</v>
       </c>
       <c r="F829" t="s">
         <v>50</v>
@@ -17141,13 +17141,13 @@
         <v>7</v>
       </c>
       <c r="C834" t="n">
-        <v>10.5645271549954</v>
+        <v>10.583215926647</v>
       </c>
       <c r="D834" t="n">
-        <v>18.4911782749867</v>
+        <v>18.5178106081214</v>
       </c>
       <c r="E834" t="n">
-        <v>11.2306905056175</v>
+        <v>11.2500413306128</v>
       </c>
       <c r="F834" t="s">
         <v>50</v>
@@ -17161,13 +17161,13 @@
         <v>9</v>
       </c>
       <c r="C835" t="n">
-        <v>32.621325436947</v>
+        <v>32.588994629114</v>
       </c>
       <c r="D835" t="n">
-        <v>32.5231523242155</v>
+        <v>32.5985786956869</v>
       </c>
       <c r="E835" t="n">
-        <v>32.6209007625014</v>
+        <v>32.5975643511406</v>
       </c>
       <c r="F835" t="s">
         <v>50</v>
@@ -17181,13 +17181,13 @@
         <v>10</v>
       </c>
       <c r="C836" t="n">
-        <v>1.03403846792417</v>
+        <v>1.02663421194087</v>
       </c>
       <c r="D836" t="n">
-        <v>2.6209839260905</v>
+        <v>2.55637727040058</v>
       </c>
       <c r="E836" t="n">
-        <v>1.08061089204719</v>
+        <v>1.07220708729902</v>
       </c>
       <c r="F836" t="s">
         <v>50</v>
@@ -17201,13 +17201,13 @@
         <v>11</v>
       </c>
       <c r="C837" t="n">
-        <v>0.750797843187324</v>
+        <v>0.751226620234163</v>
       </c>
       <c r="D837" t="n">
-        <v>0.705177148926205</v>
+        <v>0.709912871788632</v>
       </c>
       <c r="E837" t="n">
-        <v>0.766757401113023</v>
+        <v>0.766924814204579</v>
       </c>
       <c r="F837" t="s">
         <v>50</v>
@@ -17221,13 +17221,13 @@
         <v>7</v>
       </c>
       <c r="C838" t="n">
-        <v>13.5173104148506</v>
+        <v>13.535677101013</v>
       </c>
       <c r="D838" t="n">
-        <v>33.3649664660024</v>
+        <v>31.5176217295995</v>
       </c>
       <c r="E838" t="n">
-        <v>15.0491349501613</v>
+        <v>14.9239994572505</v>
       </c>
       <c r="F838" t="s">
         <v>50</v>
@@ -17241,13 +17241,13 @@
         <v>9</v>
       </c>
       <c r="C839" t="n">
-        <v>39.1200426415196</v>
+        <v>39.3508330223735</v>
       </c>
       <c r="D839" t="n">
-        <v>63.8591588181134</v>
+        <v>60.7820996063654</v>
       </c>
       <c r="E839" t="n">
-        <v>41.5606738836329</v>
+        <v>41.4058971919436</v>
       </c>
       <c r="F839" t="s">
         <v>50</v>
@@ -17261,13 +17261,13 @@
         <v>10</v>
       </c>
       <c r="C840" t="n">
-        <v>0.838367516156165</v>
+        <v>0.839270750325753</v>
       </c>
       <c r="D840" t="n">
-        <v>3.00723152248388</v>
+        <v>2.7226787523845</v>
       </c>
       <c r="E840" t="n">
-        <v>0.96350485483661</v>
+        <v>0.931684584456507</v>
       </c>
       <c r="F840" t="s">
         <v>50</v>
@@ -17281,13 +17281,13 @@
         <v>11</v>
       </c>
       <c r="C841" t="n">
-        <v>0.674869377099325</v>
+        <v>0.674694460663026</v>
       </c>
       <c r="D841" t="n">
-        <v>0.826527889710191</v>
+        <v>0.778053329375674</v>
       </c>
       <c r="E841" t="n">
-        <v>0.642533220331183</v>
+        <v>0.647435185469139</v>
       </c>
       <c r="F841" t="s">
         <v>50</v>
@@ -17301,13 +17301,13 @@
         <v>7</v>
       </c>
       <c r="C842" t="n">
-        <v>16.4823390326141</v>
+        <v>16.4823912894298</v>
       </c>
       <c r="D842" t="n">
-        <v>12.1328007680681</v>
+        <v>12.1342196431794</v>
       </c>
       <c r="E842" t="n">
-        <v>16.1204589140056</v>
+        <v>16.1206250464583</v>
       </c>
       <c r="F842" t="s">
         <v>51</v>
@@ -17321,13 +17321,13 @@
         <v>9</v>
       </c>
       <c r="C843" t="n">
-        <v>51.2590329456128</v>
+        <v>51.2588097648651</v>
       </c>
       <c r="D843" t="n">
-        <v>32.7089578798709</v>
+        <v>32.7087455909791</v>
       </c>
       <c r="E843" t="n">
-        <v>49.9754270354222</v>
+        <v>49.9752072118234</v>
       </c>
       <c r="F843" t="s">
         <v>51</v>
@@ -17341,13 +17341,13 @@
         <v>10</v>
       </c>
       <c r="C844" t="n">
-        <v>1.47249418901537</v>
+        <v>1.47245721574964</v>
       </c>
       <c r="D844" t="n">
-        <v>2.57413255915861</v>
+        <v>2.5745769028284</v>
       </c>
       <c r="E844" t="n">
-        <v>1.50161904856541</v>
+        <v>1.5015976300637</v>
       </c>
       <c r="F844" t="s">
         <v>51</v>
@@ -17361,13 +17361,13 @@
         <v>11</v>
       </c>
       <c r="C845" t="n">
-        <v>0.705156826939212</v>
+        <v>0.70515419269365</v>
       </c>
       <c r="D845" t="n">
-        <v>0.778705349080338</v>
+        <v>0.778537125037824</v>
       </c>
       <c r="E845" t="n">
-        <v>0.701378662566274</v>
+        <v>0.701374571553522</v>
       </c>
       <c r="F845" t="s">
         <v>51</v>
@@ -17461,13 +17461,13 @@
         <v>7</v>
       </c>
       <c r="C850" t="n">
-        <v>13.5820652465447</v>
+        <v>13.5820665258575</v>
       </c>
       <c r="D850" t="n">
-        <v>22.6113978702791</v>
+        <v>22.6113958049438</v>
       </c>
       <c r="E850" t="n">
-        <v>14.2732919895525</v>
+        <v>14.2732930115731</v>
       </c>
       <c r="F850" t="s">
         <v>51</v>
@@ -17481,13 +17481,13 @@
         <v>9</v>
       </c>
       <c r="C851" t="n">
-        <v>47.1124011958455</v>
+        <v>47.1124082134115</v>
       </c>
       <c r="D851" t="n">
-        <v>53.8726996085173</v>
+        <v>53.8726988062654</v>
       </c>
       <c r="E851" t="n">
-        <v>47.6589415604629</v>
+        <v>47.6589478944854</v>
       </c>
       <c r="F851" t="s">
         <v>51</v>
@@ -17501,13 +17501,13 @@
         <v>10</v>
       </c>
       <c r="C852" t="n">
-        <v>0.653183714445035</v>
+        <v>0.653183977065059</v>
       </c>
       <c r="D852" t="n">
-        <v>1.47412964210709</v>
+        <v>1.47412981189558</v>
       </c>
       <c r="E852" t="n">
-        <v>0.684254356192143</v>
+        <v>0.684254616639203</v>
       </c>
       <c r="F852" t="s">
         <v>51</v>
@@ -17521,13 +17521,13 @@
         <v>11</v>
       </c>
       <c r="C853" t="n">
-        <v>0.801155608005363</v>
+        <v>0.801155555103982</v>
       </c>
       <c r="D853" t="n">
-        <v>0.658684531378349</v>
+        <v>0.658684441384191</v>
       </c>
       <c r="E853" t="n">
-        <v>0.784160991721825</v>
+        <v>0.784160939343503</v>
       </c>
       <c r="F853" t="s">
         <v>51</v>
@@ -17621,13 +17621,13 @@
         <v>7</v>
       </c>
       <c r="C858" t="n">
-        <v>12.887859449442</v>
+        <v>12.7395446638808</v>
       </c>
       <c r="D858" t="n">
-        <v>16.8810647666051</v>
+        <v>17.1987085790613</v>
       </c>
       <c r="E858" t="n">
-        <v>13.2169799491173</v>
+        <v>13.1074964517827</v>
       </c>
       <c r="F858" t="s">
         <v>51</v>
@@ -17641,13 +17641,13 @@
         <v>9</v>
       </c>
       <c r="C859" t="n">
-        <v>39.3922819543857</v>
+        <v>39.1737257526309</v>
       </c>
       <c r="D859" t="n">
-        <v>41.8953617177484</v>
+        <v>42.4666532605846</v>
       </c>
       <c r="E859" t="n">
-        <v>39.5990475364877</v>
+        <v>39.450633686401</v>
       </c>
       <c r="F859" t="s">
         <v>51</v>
@@ -17661,13 +17661,13 @@
         <v>10</v>
       </c>
       <c r="C860" t="n">
-        <v>0.739599549834635</v>
+        <v>0.720789787900698</v>
       </c>
       <c r="D860" t="n">
-        <v>1.52012934364784</v>
+        <v>1.50506618940089</v>
       </c>
       <c r="E860" t="n">
-        <v>0.770782218982312</v>
+        <v>0.752343885728856</v>
       </c>
       <c r="F860" t="s">
         <v>51</v>
@@ -17681,13 +17681,13 @@
         <v>11</v>
       </c>
       <c r="C861" t="n">
-        <v>0.823574934531391</v>
+        <v>0.825768206442909</v>
       </c>
       <c r="D861" t="n">
-        <v>0.854194282161391</v>
+        <v>0.8398812548297</v>
       </c>
       <c r="E861" t="n">
-        <v>0.812262226742119</v>
+        <v>0.814028722478881</v>
       </c>
       <c r="F861" t="s">
         <v>51</v>
@@ -17701,13 +17701,13 @@
         <v>7</v>
       </c>
       <c r="C862" t="n">
-        <v>14.6136239396173</v>
+        <v>14.8931783688233</v>
       </c>
       <c r="D862" t="n">
-        <v>15.3071388557188</v>
+        <v>23.5564147798677</v>
       </c>
       <c r="E862" t="n">
-        <v>14.6640358841363</v>
+        <v>15.556682327744</v>
       </c>
       <c r="F862" t="s">
         <v>51</v>
@@ -17721,13 +17721,13 @@
         <v>9</v>
       </c>
       <c r="C863" t="n">
-        <v>40.3807940582174</v>
+        <v>40.5312744391199</v>
       </c>
       <c r="D863" t="n">
-        <v>36.1181581301045</v>
+        <v>51.682094636921</v>
       </c>
       <c r="E863" t="n">
-        <v>40.0635311273815</v>
+        <v>41.4875098558095</v>
       </c>
       <c r="F863" t="s">
         <v>51</v>
@@ -17741,13 +17741,13 @@
         <v>10</v>
       </c>
       <c r="C864" t="n">
-        <v>0.612651507041723</v>
+        <v>0.622258049967133</v>
       </c>
       <c r="D864" t="n">
-        <v>0.932591560817268</v>
+        <v>1.26176891360451</v>
       </c>
       <c r="E864" t="n">
-        <v>0.72032667808391</v>
+        <v>0.713998503148529</v>
       </c>
       <c r="F864" t="s">
         <v>51</v>
@@ -17761,13 +17761,13 @@
         <v>11</v>
       </c>
       <c r="C865" t="n">
-        <v>0.839978328506367</v>
+        <v>0.839836814818103</v>
       </c>
       <c r="D865" t="n">
-        <v>0.810553440684841</v>
+        <v>0.732138884545462</v>
       </c>
       <c r="E865" t="n">
-        <v>0.833085887698498</v>
+        <v>0.82404057051761</v>
       </c>
       <c r="F865" t="s">
         <v>51</v>
@@ -17781,13 +17781,13 @@
         <v>7</v>
       </c>
       <c r="C866" t="n">
-        <v>29.9157290974948</v>
+        <v>29.9157428375495</v>
       </c>
       <c r="D866" t="n">
-        <v>36.5966715617679</v>
+        <v>36.5967239633526</v>
       </c>
       <c r="E866" t="n">
-        <v>30.4726212726701</v>
+        <v>30.4726382344854</v>
       </c>
       <c r="F866" t="s">
         <v>52</v>
@@ -17801,13 +17801,13 @@
         <v>9</v>
       </c>
       <c r="C867" t="n">
-        <v>1842.1517549524</v>
+        <v>1842.15298313497</v>
       </c>
       <c r="D867" t="n">
-        <v>2345.14285151485</v>
+        <v>2345.1451182428</v>
       </c>
       <c r="E867" t="n">
-        <v>1889.1884596587</v>
+        <v>1889.18979193979</v>
       </c>
       <c r="F867" t="s">
         <v>52</v>
@@ -17821,13 +17821,13 @@
         <v>10</v>
       </c>
       <c r="C868" t="n">
-        <v>0.709866724648756</v>
+        <v>0.709868657670956</v>
       </c>
       <c r="D868" t="n">
-        <v>1.58105478537743</v>
+        <v>1.58105873639204</v>
       </c>
       <c r="E868" t="n">
-        <v>0.775687979710745</v>
+        <v>0.775690150029373</v>
       </c>
       <c r="F868" t="s">
         <v>52</v>
@@ -17841,13 +17841,13 @@
         <v>11</v>
       </c>
       <c r="C869" t="n">
-        <v>0.761033971787209</v>
+        <v>0.761033845643417</v>
       </c>
       <c r="D869" t="n">
-        <v>0.872745931957562</v>
+        <v>0.872747077266056</v>
       </c>
       <c r="E869" t="n">
-        <v>0.765095251419575</v>
+        <v>0.765095152661346</v>
       </c>
       <c r="F869" t="s">
         <v>52</v>
@@ -17941,13 +17941,13 @@
         <v>7</v>
       </c>
       <c r="C874" t="n">
-        <v>17.6049203652846</v>
+        <v>17.604920377094</v>
       </c>
       <c r="D874" t="n">
-        <v>42.9721790736204</v>
+        <v>42.9721791799771</v>
       </c>
       <c r="E874" t="n">
-        <v>19.5564590446326</v>
+        <v>19.5564590637148</v>
       </c>
       <c r="F874" t="s">
         <v>52</v>
@@ -17961,13 +17961,13 @@
         <v>9</v>
       </c>
       <c r="C875" t="n">
-        <v>1266.74759251608</v>
+        <v>1266.74759096428</v>
       </c>
       <c r="D875" t="n">
-        <v>2996.95703695929</v>
+        <v>2996.95704872585</v>
       </c>
       <c r="E875" t="n">
-        <v>1473.82331662307</v>
+        <v>1473.82331723247</v>
       </c>
       <c r="F875" t="s">
         <v>52</v>
@@ -17981,13 +17981,13 @@
         <v>10</v>
       </c>
       <c r="C876" t="n">
-        <v>0.399613928524563</v>
+        <v>0.399613928090796</v>
       </c>
       <c r="D876" t="n">
-        <v>0.73283865022009</v>
+        <v>0.732838651900126</v>
       </c>
       <c r="E876" t="n">
-        <v>0.455156579997687</v>
+        <v>0.455156579970844</v>
       </c>
       <c r="F876" t="s">
         <v>52</v>
@@ -18001,13 +18001,13 @@
         <v>11</v>
       </c>
       <c r="C877" t="n">
-        <v>0.87921805688083</v>
+        <v>0.87921805718056</v>
       </c>
       <c r="D877" t="n">
-        <v>0.898576092109544</v>
+        <v>0.898576092086224</v>
       </c>
       <c r="E877" t="n">
-        <v>0.860506132936495</v>
+        <v>0.860506132972164</v>
       </c>
       <c r="F877" t="s">
         <v>52</v>
@@ -18101,13 +18101,13 @@
         <v>7</v>
       </c>
       <c r="C882" t="n">
-        <v>18.2193263245381</v>
+        <v>18.2982859670868</v>
       </c>
       <c r="D882" t="n">
-        <v>29.9960031483834</v>
+        <v>29.9772849867081</v>
       </c>
       <c r="E882" t="n">
-        <v>19.2009192932608</v>
+        <v>19.2717389669253</v>
       </c>
       <c r="F882" t="s">
         <v>52</v>
@@ -18121,13 +18121,13 @@
         <v>9</v>
       </c>
       <c r="C883" t="n">
-        <v>1276.97328581963</v>
+        <v>1278.97741728765</v>
       </c>
       <c r="D883" t="n">
-        <v>1692.6823041909</v>
+        <v>1666.6918690172</v>
       </c>
       <c r="E883" t="n">
-        <v>1316.63909626554</v>
+        <v>1315.65895179576</v>
       </c>
       <c r="F883" t="s">
         <v>52</v>
@@ -18141,13 +18141,13 @@
         <v>10</v>
       </c>
       <c r="C884" t="n">
-        <v>0.450733475642573</v>
+        <v>0.453427651167947</v>
       </c>
       <c r="D884" t="n">
-        <v>0.773353235348874</v>
+        <v>0.766923299531452</v>
       </c>
       <c r="E884" t="n">
-        <v>0.488219708956178</v>
+        <v>0.489975477246546</v>
       </c>
       <c r="F884" t="s">
         <v>52</v>
@@ -18161,13 +18161,13 @@
         <v>11</v>
       </c>
       <c r="C885" t="n">
-        <v>0.880674551671385</v>
+        <v>0.880402649919147</v>
       </c>
       <c r="D885" t="n">
-        <v>0.913425678162786</v>
+        <v>0.920284616454028</v>
       </c>
       <c r="E885" t="n">
-        <v>0.880528823230716</v>
+        <v>0.880849137171271</v>
       </c>
       <c r="F885" t="s">
         <v>52</v>
@@ -18181,13 +18181,13 @@
         <v>7</v>
       </c>
       <c r="C886" t="n">
-        <v>46.7146396008852</v>
+        <v>45.4681636921762</v>
       </c>
       <c r="D886" t="n">
-        <v>36.1686822128785</v>
+        <v>89.141027046777</v>
       </c>
       <c r="E886" t="n">
-        <v>45.9034999598082</v>
+        <v>48.8275352639788</v>
       </c>
       <c r="F886" t="s">
         <v>52</v>
@@ -18201,13 +18201,13 @@
         <v>9</v>
       </c>
       <c r="C887" t="n">
-        <v>2028.99773506513</v>
+        <v>2016.21115993704</v>
       </c>
       <c r="D887" t="n">
-        <v>2446.53782918407</v>
+        <v>4215.35964081924</v>
       </c>
       <c r="E887" t="n">
-        <v>2064.11535667632</v>
+        <v>2262.57079550923</v>
       </c>
       <c r="F887" t="s">
         <v>52</v>
@@ -18221,13 +18221,13 @@
         <v>10</v>
       </c>
       <c r="C888" t="n">
-        <v>0.842369339674384</v>
+        <v>0.823501180096432</v>
       </c>
       <c r="D888" t="n">
-        <v>1.03290131930467</v>
+        <v>1.57276332645274</v>
       </c>
       <c r="E888" t="n">
-        <v>0.9043868825767</v>
+        <v>0.935046757363466</v>
       </c>
       <c r="F888" t="s">
         <v>52</v>
@@ -18241,13 +18241,13 @@
         <v>11</v>
       </c>
       <c r="C889" t="n">
-        <v>0.695196273551787</v>
+        <v>0.700537146382356</v>
       </c>
       <c r="D889" t="n">
-        <v>0.771390243566532</v>
+        <v>0.548727322603843</v>
       </c>
       <c r="E889" t="n">
-        <v>0.696389878830072</v>
+        <v>0.643641552561341</v>
       </c>
       <c r="F889" t="s">
         <v>52</v>
